--- a/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
+++ b/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
@@ -1019,7 +1019,7 @@
         <v>0.9879520000000001</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1664</v>
+        <v>1651.435028248588</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>0.990196</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>1683</v>
+        <v>1665.511627906977</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>2110</v>
+        <v>1747.513661202186</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -1250,7 +1250,11 @@
           <t>Garden</t>
         </is>
       </c>
-      <c r="K13" s="7" t="n"/>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Rent: HD mix-wtd $1,748 vs CoStar ask $2,110</t>
+        </is>
+      </c>
       <c r="M13">
         <f>IFERROR(VALUE(RIGHT(E13,4))*4+MATCH(LEFT(E13,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
@@ -1277,7 +1281,7 @@
         <v>0.989011</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>1189</v>
+        <v>1165.555555555556</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
@@ -1363,7 +1367,7 @@
         <v>0.948148</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>2229</v>
+        <v>2164.319806763285</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
@@ -1493,7 +1497,7 @@
         <v>0.945833</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>1689</v>
+        <v>1624.407772304324</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -1585,7 +1589,7 @@
         <v>0.763889</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>1707</v>
+        <v>1735.469387755102</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -1631,7 +1635,7 @@
         <v>0.990196</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>1898</v>
+        <v>1884.446808510638</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -1673,7 +1677,7 @@
         <v>0.933333</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>2070</v>
+        <v>1995</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -1715,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>2595</v>
+        <v>2489.375</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -1757,7 +1761,7 @@
         <v>0.969697</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>1762</v>
+        <v>1739.209026472431</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -1850,10 +1854,10 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>0.803571</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>1742</v>
+        <v>1747.513661202186</v>
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
@@ -1870,7 +1874,7 @@
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>Units: CoStar 336 vs RealPage 96; Year built: 2018/2024; Units: CoStar 336 vs RealPage 36; Year built: 2021/2024; Units: CoStar 336 vs RealPage 64; Year built: 1993/2024; Units: CoStar 336 vs RealPage 336; Year built: 2024/2027; Occ: CoStar 80% vs RealPage 11%; Verify rent/occ w/ HelloData</t>
+          <t>Units: CoStar 336 vs RealPage 96; Year built: 2018/2024; Units: CoStar 336 vs RealPage 36; Year built: 2021/2024; Units: CoStar 336 vs RealPage 64; Year built: 1993/2024; Units: CoStar 336 vs RealPage 336; Year built: 2024/2027; Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
         </is>
       </c>
       <c r="M29">
@@ -1896,10 +1900,10 @@
         </is>
       </c>
       <c r="F30" s="17" t="n">
-        <v>0.277487</v>
+        <v>0.4764397905759162</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>1716</v>
+        <v>1994.484728234728</v>
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
@@ -1916,7 +1920,7 @@
       </c>
       <c r="K30" s="15" t="inlineStr">
         <is>
-          <t>Occ: CoStar 28% vs RealPage 84%; Rent: CoStar ask $1,716 vs RealPage eff $2,004; Verify rent/occ w/ HelloData</t>
+          <t>Occ: CoStar 28% vs RealPage 84%; Rent: CoStar ask $1,716 vs RealPage eff $2,004; Rent: HD mix-wtd $1,994 vs CoStar ask $1,716; Occ: HD ~48% (CoStar/RP showed 28%); HD (90d): occ ~48% (units leased), ~22 leases/mo</t>
         </is>
       </c>
       <c r="M30">
@@ -1990,10 +1994,10 @@
         </is>
       </c>
       <c r="F32" s="17" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>1862</v>
+        <v>1833.726076373041</v>
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
@@ -2010,7 +2014,7 @@
       </c>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>Units: CoStar 156 vs RealPage 128; Year built: 2026/2027; Occ: CoStar 25% vs RealPage 18%; Rent: CoStar ask $1,862 vs RealPage eff $1,684; Verify rent/occ w/ HelloData</t>
+          <t>Units: CoStar 156 vs RealPage 128; Year built: 2026/2027; Occ: CoStar 25% vs RealPage 18%; Rent: CoStar ask $1,862 vs RealPage eff $1,684; Occ: HD ~100% (CoStar/RP showed 25%); HD (90d): occ ~100% (units leased), ~20 leases/mo</t>
         </is>
       </c>
       <c r="M32">
@@ -2939,7 +2943,7 @@
     <row r="59">
       <c r="B59" s="36" t="inlineStr">
         <is>
-          <t>* 5-Mile radius. Rent ($) = market asking. Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
+          <t>* 5-Mile radius. Rent ($) = HelloData mix-weighted asking where covered, else market asking (CoStar). Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
       </c>
     </row>
@@ -3891,10 +3895,10 @@
         <v>1835</v>
       </c>
       <c r="H23" s="56" t="n">
-        <v>1801</v>
+        <v>1777</v>
       </c>
       <c r="I23" s="56">
-        <f>IFERROR('Cash Flow (Annual)'!$F$4,1868)</f>
+        <f>IFERROR('Cash Flow (Annual)'!$F$4,1735)</f>
         <v/>
       </c>
       <c r="J23" s="57">
@@ -4052,10 +4056,10 @@
         <v>1835</v>
       </c>
       <c r="H25" s="56" t="n">
-        <v>1669</v>
+        <v>1619</v>
       </c>
       <c r="I25" s="56">
-        <f>IFERROR('Cash Flow (Annual)'!$F$5,1689)</f>
+        <f>IFERROR('Cash Flow (Annual)'!$F$5,1578)</f>
         <v/>
       </c>
       <c r="J25" s="57">
@@ -5211,7 +5215,7 @@
       </c>
       <c r="E66" s="79" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>HD</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5227,7 @@
       </c>
       <c r="E67" s="79" t="inlineStr">
         <is>
-          <t>HD occ + CoStar rents</t>
+          <t>HD</t>
         </is>
       </c>
     </row>
@@ -5510,8 +5514,12 @@
       <c r="L3" s="82" t="n">
         <v>1841</v>
       </c>
-      <c r="M3" s="82" t="n"/>
-      <c r="N3" s="82" t="n"/>
+      <c r="M3" s="82" t="n">
+        <v>1739.209026472431</v>
+      </c>
+      <c r="N3" s="82" t="n">
+        <v>1663.812235275689</v>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -5564,8 +5572,12 @@
         <v>2595</v>
       </c>
       <c r="L4" s="82" t="n"/>
-      <c r="M4" s="82" t="n"/>
-      <c r="N4" s="82" t="n"/>
+      <c r="M4" s="82" t="n">
+        <v>2489.375</v>
+      </c>
+      <c r="N4" s="82" t="n">
+        <v>2395.895833333333</v>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -5614,8 +5626,12 @@
         <v>2070</v>
       </c>
       <c r="L5" s="82" t="n"/>
-      <c r="M5" s="82" t="n"/>
-      <c r="N5" s="82" t="n"/>
+      <c r="M5" s="82" t="n">
+        <v>1995</v>
+      </c>
+      <c r="N5" s="82" t="n">
+        <v>1995</v>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -5664,8 +5680,12 @@
         <v>1898</v>
       </c>
       <c r="L6" s="82" t="n"/>
-      <c r="M6" s="82" t="n"/>
-      <c r="N6" s="82" t="n"/>
+      <c r="M6" s="82" t="n">
+        <v>1884.446808510638</v>
+      </c>
+      <c r="N6" s="82" t="n">
+        <v>1884.446808510638</v>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -5718,8 +5738,12 @@
       <c r="L7" s="82" t="n">
         <v>1754</v>
       </c>
-      <c r="M7" s="82" t="n"/>
-      <c r="N7" s="82" t="n"/>
+      <c r="M7" s="82" t="n">
+        <v>1624.407772304324</v>
+      </c>
+      <c r="N7" s="82" t="n">
+        <v>1573.192255062945</v>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -5834,8 +5858,12 @@
       <c r="L9" s="82" t="n">
         <v>1691</v>
       </c>
-      <c r="M9" s="82" t="n"/>
-      <c r="N9" s="82" t="n"/>
+      <c r="M9" s="82" t="n">
+        <v>1735.469387755102</v>
+      </c>
+      <c r="N9" s="82" t="n">
+        <v>1735.469387755102</v>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -5942,8 +5970,12 @@
       <c r="L11" s="82" t="n">
         <v>2243</v>
       </c>
-      <c r="M11" s="82" t="n"/>
-      <c r="N11" s="82" t="n"/>
+      <c r="M11" s="82" t="n">
+        <v>2164.319806763285</v>
+      </c>
+      <c r="N11" s="82" t="n">
+        <v>2140.342028985508</v>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -6046,8 +6078,12 @@
         <v>1189</v>
       </c>
       <c r="L13" s="82" t="n"/>
-      <c r="M13" s="82" t="n"/>
-      <c r="N13" s="82" t="n"/>
+      <c r="M13" s="82" t="n">
+        <v>1165.555555555556</v>
+      </c>
+      <c r="N13" s="82" t="n">
+        <v>1156.326599326599</v>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -6146,8 +6182,12 @@
       <c r="L15" s="82" t="n">
         <v>1661</v>
       </c>
-      <c r="M15" s="82" t="n"/>
-      <c r="N15" s="82" t="n"/>
+      <c r="M15" s="82" t="n">
+        <v>1665.511627906977</v>
+      </c>
+      <c r="N15" s="82" t="n">
+        <v>1665.511627906977</v>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -6198,14 +6238,22 @@
         <v>2110</v>
       </c>
       <c r="L16" s="82" t="n"/>
-      <c r="M16" s="82" t="n"/>
-      <c r="N16" s="82" t="n"/>
+      <c r="M16" s="82" t="n">
+        <v>1747.513661202186</v>
+      </c>
+      <c r="N16" s="82" t="n">
+        <v>1747.513661202186</v>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>CoStar</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rent: HD mix-wtd $1,748 vs CoStar ask $2,110</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6252,8 +6300,12 @@
       <c r="L17" s="82" t="n">
         <v>1641</v>
       </c>
-      <c r="M17" s="82" t="n"/>
-      <c r="N17" s="82" t="n"/>
+      <c r="M17" s="82" t="n">
+        <v>1651.435028248588</v>
+      </c>
+      <c r="N17" s="82" t="n">
+        <v>1651.435028248588</v>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -6542,15 +6594,21 @@
       <c r="I23" s="81" t="n">
         <v>0.18</v>
       </c>
-      <c r="J23" s="81" t="n"/>
+      <c r="J23" s="81" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" s="82" t="n">
         <v>1862</v>
       </c>
       <c r="L23" s="82" t="n">
         <v>1684</v>
       </c>
-      <c r="M23" s="82" t="n"/>
-      <c r="N23" s="82" t="n"/>
+      <c r="M23" s="82" t="n">
+        <v>1833.726076373041</v>
+      </c>
+      <c r="N23" s="82" t="n">
+        <v>1813.154621177544</v>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -6558,7 +6616,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Units: CoStar 156 vs RealPage 128; Year built: 2026/2027; Occ: CoStar 25% vs RealPage 18%; Rent: CoStar ask $1,862 vs RealPage eff $1,684; Verify rent/occ w/ HelloData</t>
+          <t>Units: CoStar 156 vs RealPage 128; Year built: 2026/2027; Occ: CoStar 25% vs RealPage 18%; Rent: CoStar ask $1,862 vs RealPage eff $1,684; Occ: HD ~100% (CoStar/RP showed 25%); HD (90d): occ ~100% (units leased), ~20 leases/mo</t>
         </is>
       </c>
     </row>
@@ -6701,15 +6759,21 @@
       <c r="I26" s="81" t="n">
         <v>0.113</v>
       </c>
-      <c r="J26" s="81" t="n"/>
+      <c r="J26" s="81" t="n">
+        <v>0.119047619047619</v>
+      </c>
       <c r="K26" s="82" t="n">
         <v>1742</v>
       </c>
       <c r="L26" s="82" t="n">
         <v>1677</v>
       </c>
-      <c r="M26" s="82" t="n"/>
-      <c r="N26" s="82" t="n"/>
+      <c r="M26" s="82" t="n">
+        <v>1747.513661202186</v>
+      </c>
+      <c r="N26" s="82" t="n">
+        <v>1747.513661202186</v>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -6717,7 +6781,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Units: CoStar 336 vs RealPage 96; Year built: 2018/2024; Units: CoStar 336 vs RealPage 36; Year built: 2021/2024; Units: CoStar 336 vs RealPage 64; Year built: 1993/2024; Units: CoStar 336 vs RealPage 336; Year built: 2024/2027; Occ: CoStar 80% vs RealPage 11%; Verify rent/occ w/ HelloData</t>
+          <t>Units: CoStar 336 vs RealPage 96; Year built: 2018/2024; Units: CoStar 336 vs RealPage 36; Year built: 2021/2024; Units: CoStar 336 vs RealPage 64; Year built: 1993/2024; Units: CoStar 336 vs RealPage 336; Year built: 2024/2027; Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
         </is>
       </c>
     </row>
@@ -6759,15 +6823,21 @@
       <c r="I27" s="81" t="n">
         <v>0.838</v>
       </c>
-      <c r="J27" s="81" t="n"/>
+      <c r="J27" s="81" t="n">
+        <v>0.4764397905759162</v>
+      </c>
       <c r="K27" s="82" t="n">
         <v>1716</v>
       </c>
       <c r="L27" s="82" t="n">
         <v>2004</v>
       </c>
-      <c r="M27" s="82" t="n"/>
-      <c r="N27" s="82" t="n"/>
+      <c r="M27" s="82" t="n">
+        <v>1994.484728234728</v>
+      </c>
+      <c r="N27" s="82" t="n">
+        <v>1994.484728234728</v>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -6775,7 +6845,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Occ: CoStar 28% vs RealPage 84%; Rent: CoStar ask $1,716 vs RealPage eff $2,004; Verify rent/occ w/ HelloData</t>
+          <t>Occ: CoStar 28% vs RealPage 84%; Rent: CoStar ask $1,716 vs RealPage eff $2,004; Rent: HD mix-wtd $1,994 vs CoStar ask $1,716; Occ: HD ~48% (CoStar/RP showed 28%); HD (90d): occ ~48% (units leased), ~22 leases/mo</t>
         </is>
       </c>
     </row>

--- a/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
+++ b/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M59"/>
+  <dimension ref="B2:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Units: CoStar 476 vs RealPage 164; Year built: 2022/2027; Delivery quarter estimated; RealPage-only — not in CoStar's 5-mi series</t>
+          <t>Delivery quarter estimated; RealPage-only — not in CoStar's 5-mi series</t>
         </is>
       </c>
       <c r="M7">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>Units: CoStar 336 vs RealPage 96; Year built: 2018/2024; Units: CoStar 336 vs RealPage 36; Year built: 2021/2024; Units: CoStar 336 vs RealPage 64; Year built: 1993/2024; Units: CoStar 336 vs RealPage 336; Year built: 2024/2027; Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
+          <t>Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
         </is>
       </c>
       <c r="M29">
@@ -2074,7 +2074,7 @@
       <c r="B35" s="20" t="n"/>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>UNDER CONSTRUCTION (1 properties, 350 units)</t>
+          <t>UNDER CONSTRUCTION (2 properties, 716 units)</t>
         </is>
       </c>
     </row>
@@ -2084,15 +2084,15 @@
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>Union 93</t>
+          <t>South Ridge II</t>
         </is>
       </c>
       <c r="D36" s="24" t="n">
-        <v>350</v>
+        <v>164</v>
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>Q3 2026</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F36" s="25" t="n"/>
@@ -2103,15 +2103,15 @@
       </c>
       <c r="H36" s="23" t="inlineStr">
         <is>
-          <t>Grey Owl Holdings Llc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="27" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K36" s="23" t="n"/>
@@ -2120,54 +2120,54 @@
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="28" t="n"/>
-      <c r="C38" s="29" t="inlineStr">
-        <is>
-          <t>PROPOSED (18 properties, 4,022 units)</t>
-        </is>
+    <row r="37">
+      <c r="B37" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>Vanguard Village</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="n">
+        <v>552</v>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="n"/>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="n"/>
+      <c r="M37">
+        <f>IFERROR(VALUE(RIGHT(E37,4))*4+MATCH(LEFT(E37,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="30" t="n">
-        <v>28</v>
-      </c>
-      <c r="C39" s="31" t="inlineStr">
-        <is>
-          <t>Victory Flats</t>
-        </is>
-      </c>
-      <c r="D39" s="32" t="n">
-        <v>301</v>
-      </c>
-      <c r="E39" s="30" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="F39" s="33" t="n"/>
-      <c r="G39" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="31" t="inlineStr">
-        <is>
-          <t>Welltower Inc.</t>
-        </is>
-      </c>
-      <c r="I39" s="35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J39" s="30" t="inlineStr">
-        <is>
-          <t>Townhome</t>
-        </is>
-      </c>
-      <c r="K39" s="31" t="n"/>
-      <c r="M39">
-        <f>IFERROR(VALUE(RIGHT(E39,4))*4+MATCH(LEFT(E39,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>PROPOSED (12 properties, 3,014 units)</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2176,15 +2176,15 @@
       </c>
       <c r="C40" s="31" t="inlineStr">
         <is>
-          <t>The Hummingbird</t>
+          <t>Union 93</t>
         </is>
       </c>
       <c r="D40" s="32" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="F40" s="33" t="n"/>
@@ -2195,11 +2195,11 @@
       </c>
       <c r="H40" s="31" t="inlineStr">
         <is>
-          <t>Shannon Robnett Industries</t>
+          <t>Grey Owl Holdings Llc</t>
         </is>
       </c>
       <c r="I40" s="35" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J40" s="30" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="K40" s="31" t="inlineStr">
         <is>
-          <t>Units: CoStar 200 vs RealPage 170</t>
+          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
         </is>
       </c>
       <c r="M40">
@@ -2222,15 +2222,15 @@
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>The Gateway at Ten Mile</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="D41" s="32" t="n">
-        <v>390</v>
+        <v>301</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F41" s="33" t="n"/>
@@ -2241,18 +2241,22 @@
       </c>
       <c r="H41" s="31" t="inlineStr">
         <is>
-          <t>TGI Corp</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="I41" s="35" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J41" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K41" s="31" t="n"/>
+          <t>Townhome</t>
+        </is>
+      </c>
+      <c r="K41" s="31" t="inlineStr">
+        <is>
+          <t>Diligence: proposed</t>
+        </is>
+      </c>
       <c r="M41">
         <f>IFERROR(VALUE(RIGHT(E41,4))*4+MATCH(LEFT(E41,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
@@ -2264,15 +2268,15 @@
       </c>
       <c r="C42" s="31" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>138</v>
+        <v>390</v>
       </c>
       <c r="E42" s="30" t="inlineStr">
         <is>
-          <t>Q1 2029</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F42" s="33" t="n"/>
@@ -2283,18 +2287,22 @@
       </c>
       <c r="H42" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TGI Corp</t>
         </is>
       </c>
       <c r="I42" s="35" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J42" s="30" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K42" s="31" t="n"/>
+      <c r="K42" s="31" t="inlineStr">
+        <is>
+          <t>Diligence: proposed</t>
+        </is>
+      </c>
       <c r="M42">
         <f>IFERROR(VALUE(RIGHT(E42,4))*4+MATCH(LEFT(E42,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
@@ -2306,15 +2314,15 @@
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>The 10</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>559</v>
+        <v>138</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="F43" s="33" t="n"/>
@@ -2329,16 +2337,16 @@
         </is>
       </c>
       <c r="I43" s="35" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J43" s="30" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K43" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M43">
@@ -2384,7 +2392,7 @@
       </c>
       <c r="K44" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M44">
@@ -2430,7 +2438,7 @@
       </c>
       <c r="K45" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M45">
@@ -2476,7 +2484,7 @@
       </c>
       <c r="K46" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M46">
@@ -2522,7 +2530,7 @@
       </c>
       <c r="K47" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M47">
@@ -2536,11 +2544,11 @@
       </c>
       <c r="C48" s="31" t="inlineStr">
         <is>
-          <t>Madison Town Square</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
@@ -2559,16 +2567,16 @@
         </is>
       </c>
       <c r="I48" s="35" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J48" s="30" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K48" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M48">
@@ -2582,11 +2590,11 @@
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>Centrepoint</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="E49" s="30" t="inlineStr">
         <is>
@@ -2601,20 +2609,20 @@
       </c>
       <c r="H49" s="31" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I49" s="35" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K49" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M49">
@@ -2628,11 +2636,11 @@
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
@@ -2651,7 +2659,7 @@
         </is>
       </c>
       <c r="I50" s="35" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J50" s="30" t="inlineStr">
         <is>
@@ -2660,7 +2668,7 @@
       </c>
       <c r="K50" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M50">
@@ -2674,11 +2682,11 @@
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Meridian OZ Apartments</t>
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
@@ -2693,20 +2701,20 @@
       </c>
       <c r="H51" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Peak Capital Investments Llc</t>
         </is>
       </c>
       <c r="I51" s="35" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J51" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K51" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M51">
@@ -2714,234 +2722,8 @@
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="30" t="n">
-        <v>41</v>
-      </c>
-      <c r="C52" s="31" t="inlineStr">
-        <is>
-          <t>10975 West Lake Hazel Road</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="n">
-        <v>130</v>
-      </c>
-      <c r="E52" s="30" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F52" s="33" t="n"/>
-      <c r="G52" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J52" s="30" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K52" s="31" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
-      <c r="M52">
-        <f>IFERROR(VALUE(RIGHT(E52,4))*4+MATCH(LEFT(E52,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="30" t="n">
-        <v>42</v>
-      </c>
-      <c r="C53" s="31" t="inlineStr">
-        <is>
-          <t>Villas at Twelve Oaks East</t>
-        </is>
-      </c>
-      <c r="D53" s="32" t="n">
-        <v>64</v>
-      </c>
-      <c r="E53" s="30" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F53" s="33" t="n"/>
-      <c r="G53" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J53" s="30" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K53" s="31" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
-      <c r="M53">
-        <f>IFERROR(VALUE(RIGHT(E53,4))*4+MATCH(LEFT(E53,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="54">
-      <c r="B54" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="C54" s="31" t="inlineStr">
-        <is>
-          <t>Cole Road</t>
-        </is>
-      </c>
-      <c r="D54" s="32" t="n">
-        <v>61</v>
-      </c>
-      <c r="E54" s="30" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F54" s="33" t="n"/>
-      <c r="G54" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J54" s="30" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K54" s="31" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
-      <c r="M54">
-        <f>IFERROR(VALUE(RIGHT(E54,4))*4+MATCH(LEFT(E54,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="30" t="n">
-        <v>44</v>
-      </c>
-      <c r="C55" s="31" t="inlineStr">
-        <is>
-          <t>Meridian OZ Apartments</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="n">
-        <v>60</v>
-      </c>
-      <c r="E55" s="30" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F55" s="33" t="n"/>
-      <c r="G55" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="31" t="inlineStr">
-        <is>
-          <t>Peak Capital Investments Llc</t>
-        </is>
-      </c>
-      <c r="I55" s="35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J55" s="30" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K55" s="31" t="n"/>
-      <c r="M55">
-        <f>IFERROR(VALUE(RIGHT(E55,4))*4+MATCH(LEFT(E55,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="30" t="n">
-        <v>45</v>
-      </c>
-      <c r="C56" s="31" t="inlineStr">
-        <is>
-          <t>Promenade Cottages I</t>
-        </is>
-      </c>
-      <c r="D56" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="E56" s="30" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F56" s="33" t="n"/>
-      <c r="G56" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J56" s="30" t="inlineStr">
-        <is>
-          <t>Townhome</t>
-        </is>
-      </c>
-      <c r="K56" s="31" t="inlineStr">
-        <is>
-          <t>Units: CoStar 90 vs RealPage 90; RealPage pipeline (not yet in CoStar); RealPage only (sub-50 unit)</t>
-        </is>
-      </c>
-      <c r="M56">
-        <f>IFERROR(VALUE(RIGHT(E56,4))*4+MATCH(LEFT(E56,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="36" t="inlineStr">
+      <c r="B54" s="36" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Rent ($) = HelloData mix-weighted asking where covered, else market asking (CoStar). Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
@@ -2950,12 +2732,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="C38:K38"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C28:K28"/>
+    <mergeCell ref="C39:K39"/>
+    <mergeCell ref="B54:K54"/>
     <mergeCell ref="C35:K35"/>
-    <mergeCell ref="B59:K59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3072,15 +2854,15 @@
         </is>
       </c>
       <c r="R5" s="43">
-        <f>'Competitive Analysis'!C36</f>
+        <f>'Competitive Analysis'!C37</f>
         <v/>
       </c>
       <c r="S5" s="44">
-        <f>'Competitive Analysis'!D36</f>
+        <f>'Competitive Analysis'!D37</f>
         <v/>
       </c>
       <c r="T5" s="45">
-        <f>'Competitive Analysis'!E36</f>
+        <f>'Competitive Analysis'!E37</f>
         <v/>
       </c>
       <c r="V5">
@@ -3101,6 +2883,26 @@
       <c r="C6" s="46" t="n">
         <v>0.95</v>
       </c>
+      <c r="R6" s="43">
+        <f>'Competitive Analysis'!C36</f>
+        <v/>
+      </c>
+      <c r="S6" s="44">
+        <f>'Competitive Analysis'!D36</f>
+        <v/>
+      </c>
+      <c r="T6" s="45">
+        <f>'Competitive Analysis'!E36</f>
+        <v/>
+      </c>
+      <c r="V6">
+        <f>IFERROR(VALUE(RIGHT(T6,4))*4+MATCH(LEFT(T6,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W6">
+        <f>IF(V6="","",IF(V6&lt;=$Z$1,0,MAX(1,INT((V6-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="14.4" customHeight="1">
       <c r="B7" s="38" t="inlineStr">
@@ -3113,11 +2915,6 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="R7" s="37" t="inlineStr">
-        <is>
-          <t>PROPOSED PIPELINE (scenario toggle)</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="14.4" customHeight="1">
       <c r="B8" s="38" t="inlineStr">
@@ -3128,24 +2925,9 @@
       <c r="C8" s="47" t="n">
         <v>425</v>
       </c>
-      <c r="R8" s="41" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="S8" s="41" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="T8" s="41" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="U8" s="41" t="inlineStr">
-        <is>
-          <t>Built In</t>
+      <c r="R8" s="37" t="inlineStr">
+        <is>
+          <t>PROPOSED PIPELINE (scenario toggle)</t>
         </is>
       </c>
     </row>
@@ -3158,31 +2940,25 @@
       <c r="C9" s="47" t="n">
         <v>850</v>
       </c>
-      <c r="R9" s="43" t="inlineStr">
-        <is>
-          <t>The 10</t>
-        </is>
-      </c>
-      <c r="S9" s="44" t="n">
-        <v>559</v>
-      </c>
-      <c r="T9" s="48" t="inlineStr"/>
-      <c r="U9" s="48" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V9">
-        <f>IFERROR(VALUE(RIGHT(T9,4))*4+MATCH(LEFT(T9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W9">
-        <f>IF(V9="","",IF(V9&lt;=$Z$1,0,MAX(1,INT((V9-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>IF(U9="All",1,IF(U9="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U9="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
-        <v/>
+      <c r="R9" s="41" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S9" s="41" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T9" s="41" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="U9" s="41" t="inlineStr">
+        <is>
+          <t>Built In</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="14.4" customHeight="1">
@@ -3270,13 +3046,17 @@
     <row r="12" ht="14.4" customHeight="1">
       <c r="R12" s="43" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>Union 93</t>
         </is>
       </c>
       <c r="S12" s="44" t="n">
-        <v>322</v>
-      </c>
-      <c r="T12" s="48" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="T12" s="48" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
       <c r="U12" s="48" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3298,17 +3078,13 @@
     <row r="13" ht="14.4" customHeight="1">
       <c r="R13" s="43" t="inlineStr">
         <is>
-          <t>Victory Flats</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="S13" s="44" t="n">
-        <v>301</v>
-      </c>
-      <c r="T13" s="48" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="T13" s="48" t="inlineStr"/>
       <c r="U13" s="48" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3330,13 +3106,17 @@
     <row r="14" ht="14.4" customHeight="1">
       <c r="R14" s="43" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="S14" s="44" t="n">
-        <v>275</v>
-      </c>
-      <c r="T14" s="48" t="inlineStr"/>
+        <v>301</v>
+      </c>
+      <c r="T14" s="48" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
       <c r="U14" s="48" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3358,11 +3138,11 @@
     <row r="15" ht="14.4" customHeight="1">
       <c r="R15" s="43" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="S15" s="44" t="n">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="T15" s="48" t="inlineStr"/>
       <c r="U15" s="48" t="inlineStr">
@@ -3386,11 +3166,11 @@
     <row r="16" ht="14.4" customHeight="1">
       <c r="R16" s="43" t="inlineStr">
         <is>
-          <t>Madison Town Square</t>
+          <t>Cobalt Point</t>
         </is>
       </c>
       <c r="S16" s="44" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="T16" s="48" t="inlineStr"/>
       <c r="U16" s="48" t="inlineStr">
@@ -3484,11 +3264,11 @@
       </c>
       <c r="R17" s="43" t="inlineStr">
         <is>
-          <t>Centrepoint</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="S17" s="44" t="n">
-        <v>213</v>
+        <v>156</v>
       </c>
       <c r="T17" s="48" t="inlineStr"/>
       <c r="U17" s="48" t="inlineStr">
@@ -3571,17 +3351,13 @@
       </c>
       <c r="R18" s="43" t="inlineStr">
         <is>
-          <t>The Hummingbird</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="S18" s="44" t="n">
-        <v>200</v>
-      </c>
-      <c r="T18" s="48" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="T18" s="48" t="inlineStr"/>
       <c r="U18" s="48" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3625,42 +3401,46 @@
         <v>450</v>
       </c>
       <c r="I19" s="52">
-        <f>SUMIFS('Competitive Analysis'!$D$5:$D$56,'Competitive Analysis'!$M$5:$M$56,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$56,"&lt;="&amp;8105)</f>
+        <f>SUMIFS('Competitive Analysis'!$D$5:$D$51,'Competitive Analysis'!$M$5:$M$51,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$51,"&lt;="&amp;8105)</f>
         <v/>
       </c>
       <c r="J19" s="53">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,1)+SUMIFS($S$9:$S$26,$W$9:$W$26,1,$X$9:$X$26,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,1)+SUMIFS($S$10:$S$21,$W$10:$W$21,1,$X$10:$X$21,1)</f>
         <v/>
       </c>
       <c r="K19" s="53">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,2)+SUMIFS($S$9:$S$26,$W$9:$W$26,2,$X$9:$X$26,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,2)+SUMIFS($S$10:$S$21,$W$10:$W$21,2,$X$10:$X$21,1)</f>
         <v/>
       </c>
       <c r="L19" s="53">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,3)+SUMIFS($S$9:$S$26,$W$9:$W$26,3,$X$9:$X$26,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,3)+SUMIFS($S$10:$S$21,$W$10:$W$21,3,$X$10:$X$21,1)</f>
         <v/>
       </c>
       <c r="M19" s="53">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,4)+SUMIFS($S$9:$S$26,$W$9:$W$26,4,$X$9:$X$26,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,4)+SUMIFS($S$10:$S$21,$W$10:$W$21,4,$X$10:$X$21,1)</f>
         <v/>
       </c>
       <c r="N19" s="53">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,5)+SUMIFS($S$9:$S$26,$W$9:$W$26,5,$X$9:$X$26,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,5)+SUMIFS($S$10:$S$21,$W$10:$W$21,5,$X$10:$X$21,1)</f>
         <v/>
       </c>
       <c r="O19" s="53">
-        <f>SUMIFS($S$5:$S$5,$W$5:$W$5,6)+SUMIFS($S$9:$S$26,$W$9:$W$26,6,$X$9:$X$26,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,6)+SUMIFS($S$10:$S$21,$W$10:$W$21,6,$X$10:$X$21,1)</f>
         <v/>
       </c>
       <c r="R19" s="43" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="S19" s="44" t="n">
-        <v>156</v>
-      </c>
-      <c r="T19" s="48" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="T19" s="48" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
       <c r="U19" s="48" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3732,17 +3512,13 @@
       </c>
       <c r="R20" s="43" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="S20" s="44" t="n">
-        <v>138</v>
-      </c>
-      <c r="T20" s="48" t="inlineStr">
-        <is>
-          <t>Q1 2029</t>
-        </is>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="T20" s="48" t="inlineStr"/>
       <c r="U20" s="48" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3815,11 +3591,11 @@
       </c>
       <c r="R21" s="43" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Meridian OZ Apartments</t>
         </is>
       </c>
       <c r="S21" s="44" t="n">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="T21" s="48" t="inlineStr"/>
       <c r="U21" s="48" t="inlineStr">
@@ -3846,32 +3622,6 @@
           <t>SUBJECT (Seasons at Meridian)</t>
         </is>
       </c>
-      <c r="R22" s="43" t="inlineStr">
-        <is>
-          <t>10975 West Lake Hazel Road</t>
-        </is>
-      </c>
-      <c r="S22" s="44" t="n">
-        <v>130</v>
-      </c>
-      <c r="T22" s="48" t="inlineStr"/>
-      <c r="U22" s="48" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V22">
-        <f>IFERROR(VALUE(RIGHT(T22,4))*4+MATCH(LEFT(T22,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W22">
-        <f>IF(V22="","",IF(V22&lt;=$Z$1,0,MAX(1,INT((V22-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>IF(U22="All",1,IF(U22="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U22="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
-        <v/>
-      </c>
     </row>
     <row r="23" ht="14.4" customHeight="1">
       <c r="B23" s="38" t="inlineStr">
@@ -3923,32 +3673,6 @@
       </c>
       <c r="O23" s="57">
         <f>IFERROR('Cash Flow (Annual)'!$P$4,"")</f>
-        <v/>
-      </c>
-      <c r="R23" s="43" t="inlineStr">
-        <is>
-          <t>Villas at Twelve Oaks East</t>
-        </is>
-      </c>
-      <c r="S23" s="44" t="n">
-        <v>64</v>
-      </c>
-      <c r="T23" s="48" t="inlineStr"/>
-      <c r="U23" s="48" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V23">
-        <f>IFERROR(VALUE(RIGHT(T23,4))*4+MATCH(LEFT(T23,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W23">
-        <f>IF(V23="","",IF(V23&lt;=$Z$1,0,MAX(1,INT((V23-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>IF(U23="All",1,IF(U23="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U23="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
         <v/>
       </c>
     </row>
@@ -4007,32 +3731,6 @@
         <f>IFERROR(O23/N23-1,"")</f>
         <v/>
       </c>
-      <c r="R24" s="43" t="inlineStr">
-        <is>
-          <t>Cole Road</t>
-        </is>
-      </c>
-      <c r="S24" s="44" t="n">
-        <v>61</v>
-      </c>
-      <c r="T24" s="48" t="inlineStr"/>
-      <c r="U24" s="48" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V24">
-        <f>IFERROR(VALUE(RIGHT(T24,4))*4+MATCH(LEFT(T24,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W24">
-        <f>IF(V24="","",IF(V24&lt;=$Z$1,0,MAX(1,INT((V24-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>IF(U24="All",1,IF(U24="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U24="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
-        <v/>
-      </c>
     </row>
     <row r="25" ht="14.4" customHeight="1">
       <c r="B25" s="38" t="inlineStr">
@@ -4084,32 +3782,6 @@
       </c>
       <c r="O25" s="57">
         <f>IFERROR('Cash Flow (Annual)'!$P$5,"")</f>
-        <v/>
-      </c>
-      <c r="R25" s="43" t="inlineStr">
-        <is>
-          <t>Meridian OZ Apartments</t>
-        </is>
-      </c>
-      <c r="S25" s="44" t="n">
-        <v>60</v>
-      </c>
-      <c r="T25" s="48" t="inlineStr"/>
-      <c r="U25" s="48" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V25">
-        <f>IFERROR(VALUE(RIGHT(T25,4))*4+MATCH(LEFT(T25,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W25">
-        <f>IF(V25="","",IF(V25&lt;=$Z$1,0,MAX(1,INT((V25-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>IF(U25="All",1,IF(U25="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U25="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
         <v/>
       </c>
     </row>
@@ -4166,32 +3838,6 @@
       </c>
       <c r="O26" s="60">
         <f>IFERROR(O25/N25-1,"")</f>
-        <v/>
-      </c>
-      <c r="R26" s="43" t="inlineStr">
-        <is>
-          <t>Promenade Cottages I</t>
-        </is>
-      </c>
-      <c r="S26" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="T26" s="48" t="inlineStr"/>
-      <c r="U26" s="48" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V26">
-        <f>IFERROR(VALUE(RIGHT(T26,4))*4+MATCH(LEFT(T26,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W26">
-        <f>IF(V26="","",IF(V26&lt;=$Z$1,0,MAX(1,INT((V26-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>IF(U26="All",1,IF(U26="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U26="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
         <v/>
       </c>
     </row>
@@ -5239,7 +4885,7 @@
       </c>
       <c r="E68" s="79" t="inlineStr">
         <is>
-          <t>350 / 552</t>
+          <t>716 / 552</t>
         </is>
       </c>
     </row>
@@ -5302,7 +4948,7 @@
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bear only,Bear+Base,All,None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5316,7 +4962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6504,7 +6150,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Units: CoStar 476 vs RealPage 164; Year built: 2022/2027; Delivery quarter estimated; RealPage-only — not in CoStar's 5-mi series</t>
+          <t>Delivery quarter estimated; RealPage-only — not in CoStar's 5-mi series</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6427,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Units: CoStar 336 vs RealPage 96; Year built: 2018/2024; Units: CoStar 336 vs RealPage 36; Year built: 2021/2024; Units: CoStar 336 vs RealPage 64; Year built: 1993/2024; Units: CoStar 336 vs RealPage 336; Year built: 2024/2027; Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
+          <t>Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
         </is>
       </c>
     </row>
@@ -6852,23 +6498,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Union 93</t>
+          <t>Vanguard Village</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>221-225 E Broadway Ave</t>
+          <t>1085 S 10 Mile Rd</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>350</v>
+        <v>552</v>
       </c>
       <c r="D28" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Q3 2026</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -6881,11 +6527,15 @@
       <c r="J28" s="81" t="n"/>
       <c r="K28" s="82" t="n"/>
       <c r="L28" s="82" t="n"/>
-      <c r="M28" s="82" t="n"/>
-      <c r="N28" s="82" t="n"/>
+      <c r="M28" s="82" t="n">
+        <v>1747.513661202186</v>
+      </c>
+      <c r="N28" s="82" t="n">
+        <v>1747.513661202186</v>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -6893,28 +6543,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>South Ridge II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11101 W Overland Rd</t>
+          <t>1703 S Grand Frk Wy</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="D29" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Q1 2029</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
       <c r="H29" s="81" t="n"/>
@@ -6926,7 +6576,7 @@
       <c r="N29" s="82" t="n"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>RealPage</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -6934,23 +6584,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>The Gateway at Ten Mile</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2954 W Franklin Rd</t>
+          <t>11101 W Overland Rd</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>390</v>
+        <v>138</v>
       </c>
       <c r="D30" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -6970,28 +6620,32 @@
           <t>CoStar</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Diligence: proposed</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>The Hummingbird</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>60 N Cole Rd</t>
+          <t>2954 W Franklin Rd</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>200</v>
+        <v>390</v>
       </c>
       <c r="D31" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7008,12 +6662,12 @@
       <c r="N31" s="82" t="n"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Units: CoStar 200 vs RealPage 170</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
@@ -7056,21 +6710,33 @@
           <t>CoStar+RealPage</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Diligence: proposed</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>Union 93</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1475 E Franklin Rd</t>
+          <t>221-225 E Broadway Ave</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60</v>
+        <v>350</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -7089,21 +6755,25 @@
           <t>CoStar+RealPage</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cole Road</t>
+          <t>Meridian OZ Apartments</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>709 N Cole Rd</t>
+          <t>1475 E Franklin Rd</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -7119,28 +6789,28 @@
       <c r="N34" s="82" t="n"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>The 10</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>75 S Ten Mile Rd</t>
+          <t>580 N Cole Rd</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>559</v>
+        <v>136</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -7161,23 +6831,23 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>580 N Cole Rd</t>
+          <t>E Fairview Ave &amp; N Records Way</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>136</v>
+        <v>472</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -7198,23 +6868,23 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Madison Town Square</t>
+          <t>Cobalt Point</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>460 N Milwaukee St</t>
+          <t>S Cobalt Point Way &amp; E Copper Point Dr</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -7235,23 +6905,23 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Centrepoint</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3100 N Centrepoint Way</t>
+          <t>1005 E Fairview Ave</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -7263,8 +6933,12 @@
       <c r="J38" s="81" t="n"/>
       <c r="K38" s="82" t="n"/>
       <c r="L38" s="82" t="n"/>
-      <c r="M38" s="82" t="n"/>
-      <c r="N38" s="82" t="n"/>
+      <c r="M38" s="82" t="n">
+        <v>1837.580964685616</v>
+      </c>
+      <c r="N38" s="82" t="n">
+        <v>1837.580964685616</v>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7272,23 +6946,23 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>E Fairview Ave &amp; N Records Way</t>
+          <t>12548 W Overland Rd</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>472</v>
+        <v>156</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -7309,23 +6983,23 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Villas at Twelve Oaks East</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>115 S Linder Rd</t>
+          <t>12565 W Fairview Ave</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64</v>
+        <v>275</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -7346,23 +7020,23 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10975 West Lake Hazel Road</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10975 W Lake Hazel Rd</t>
+          <t>Amity Ave &amp; Meridian Rd</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -7383,192 +7057,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Cobalt Point</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>S Cobalt Point Way &amp; E Copper Point Dr</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>264</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="H42" s="81" t="n"/>
-      <c r="I42" s="81" t="n"/>
-      <c r="J42" s="81" t="n"/>
-      <c r="K42" s="82" t="n"/>
-      <c r="L42" s="82" t="n"/>
-      <c r="M42" s="82" t="n"/>
-      <c r="N42" s="82" t="n"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Promenade Cottages I</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>403 E Fairview Ave</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>30</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="H43" s="81" t="n"/>
-      <c r="I43" s="81" t="n"/>
-      <c r="J43" s="81" t="n"/>
-      <c r="K43" s="82" t="n"/>
-      <c r="L43" s="82" t="n"/>
-      <c r="M43" s="82" t="n"/>
-      <c r="N43" s="82" t="n"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Units: CoStar 90 vs RealPage 90; RealPage pipeline (not yet in CoStar); RealPage only (sub-50 unit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>12548 West Overland Road</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>12548 W Overland Rd</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>156</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="H44" s="81" t="n"/>
-      <c r="I44" s="81" t="n"/>
-      <c r="J44" s="81" t="n"/>
-      <c r="K44" s="82" t="n"/>
-      <c r="L44" s="82" t="n"/>
-      <c r="M44" s="82" t="n"/>
-      <c r="N44" s="82" t="n"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>12565 West Fairview Avenue</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>12565 W Fairview Ave</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>275</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="H45" s="81" t="n"/>
-      <c r="I45" s="81" t="n"/>
-      <c r="J45" s="81" t="n"/>
-      <c r="K45" s="82" t="n"/>
-      <c r="L45" s="82" t="n"/>
-      <c r="M45" s="82" t="n"/>
-      <c r="N45" s="82" t="n"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Syringa Crossing</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Amity Ave &amp; Meridian Rd</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>322</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="H46" s="81" t="n"/>
-      <c r="I46" s="81" t="n"/>
-      <c r="J46" s="81" t="n"/>
-      <c r="K46" s="82" t="n"/>
-      <c r="L46" s="82" t="n"/>
-      <c r="M46" s="82" t="n"/>
-      <c r="N46" s="82" t="n"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -7643,243 +7132,770 @@
     <row r="4">
       <c r="B4" s="43" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>The 10</t>
         </is>
       </c>
       <c r="C4" s="84" t="n"/>
       <c r="D4" s="84" t="n"/>
-      <c r="E4" s="43" t="n"/>
+      <c r="E4" s="43" t="inlineStr">
+        <is>
+          <t>withdrawn - superseded by The Gateway at Ten Mile</t>
+        </is>
+      </c>
       <c r="F4" s="43" t="n"/>
       <c r="G4" s="43" t="inlineStr">
         <is>
-          <t>Land-use dossier SM-155: CUP H-2022-0073 for 60 units (30x1BR + 30x2BR) at ~25 du/ac in R-40 at Franklin &amp; Locust Grove; final approval unconfirmed, not built. Keep as proposed; timing unknown.</t>
+          <t>Original 559-unit 'The 10' (Elk Ventures, 2021) never proceeded; the site was re-entitled as The Gateway at Ten Mile (H-2024-0010) for 390 units, approved Nov 2024. Removed to avoid double-counting the same site as two deals — the Gateway row carries the live entitlement.</t>
         </is>
       </c>
       <c r="H4" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2023/01/23/meridian-oz-apartments/</t>
+          <t>https://boisedev.com/news/2024/11/20/the-gateway-at-10-mile-meridian/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="43" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
-        </is>
-      </c>
-      <c r="C5" s="84" t="n"/>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
       <c r="D5" s="84" t="n"/>
-      <c r="E5" s="43" t="n"/>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>Land-use dossier SM-12: Hawkins Companies' proposal on E Amity Rd near S Meridian Rd (~400 homes + grocery) is contested — Meridian council skeptical, application remanded (Apr 2026). Delivery timing highly uncertain; treat as Bear-case supply.</t>
+          <t>Brighton Corporation's 'Records': 472 urban-style units (84 studio/208 1BR/168 2BR/12 3BR) on ~10 ac at the NE corner of Fairview Ave &amp; Records Way adjacent to CarMax, proposed Feb 2022, two phases; Brighton's leasing site lists it 'coming soon' but no construction start could be independently confirmed.</t>
         </is>
       </c>
       <c r="H5" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2026/04/09/meridian-skeptical-of-project-proposing-400-homes-grocery-store</t>
+          <t>https://www.brighton.co/brighton-place/records-way-the-village-at-meridian/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Centrepoint</t>
+        </is>
+      </c>
+      <c r="C6" s="84" t="n"/>
+      <c r="D6" s="84" t="n"/>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>withdrawn - entitlements terminated (financing)</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="43" t="inlineStr">
+        <is>
+          <t>A 2024 CUP/DA modification approved a 239-unit deed-restricted affordable/workforce development at Centrepoint Way near Eagle &amp; Ustick (earlier iterations 215-295 units), but per the Meridian staff report the applicant terminated entitlements and withdrew due to state-level financing complications — dead. Its parcel (S1105110111) reverts to latent land-use supply.</t>
+        </is>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2024/05/30/centrepoint-apartments-meridian-village/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="83" t="inlineStr">
-        <is>
-          <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>Cobalt Point</t>
+        </is>
+      </c>
+      <c r="C7" s="84" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D7" s="84" t="n"/>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="43" t="inlineStr">
+        <is>
+          <t>264 units on ~13 ac east of E Copper Point Dr &amp; S Cobalt Point Way (Silverstone Park area near Eagle/Overland — NOT Ten Mile Crossing as RealPage implies), application prepared by The Land Group (BoiseDev June 2022); a marketing domain is indexed but the current stage could not be verified.</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2022/06/13/cobalt-point-meridian/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="50" t="inlineStr">
-        <is>
-          <t>Property / Site</t>
-        </is>
-      </c>
-      <c r="C8" s="50" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D8" s="50" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="E8" s="50" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F8" s="50" t="inlineStr">
-        <is>
-          <t>Leasing Pace</t>
-        </is>
-      </c>
-      <c r="G8" s="50" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="H8" s="50" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Madison Town Square</t>
+        </is>
+      </c>
+      <c r="C8" s="84" t="n"/>
+      <c r="D8" s="84" t="n"/>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>dead - plan pulled June 2024; site for sale</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="43" t="inlineStr">
+        <is>
+          <t>Madison Capital Group (MCG Boise Owner LLC) bought the old Sears at 460 N Milwaukee in 2021 and proposed 251 units, but pulled its design-review request and the plan was reported dead June 2024; site listed for sale at $8M (later $7.5M), still unsold.</t>
+        </is>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2024/06/04/boise-sears-sale/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>Emblem Meridian (Quarterra) / Artisan Victory Market site</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="C9" s="84" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D9" s="84" t="n"/>
-      <c r="E9" s="43" t="n"/>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-76: ~12-ac BPS Eagle Road LLC assemblage on S Eagle Rd. 'Artisan Victory Market' (H-2022-0066) approved 2023 for 131 build-to-rent units + commercial but never built; superseded by Quarterra's 'Emblem Meridian' ~250-unit concept (pre-application June 2026). Closest large latent MF site to the subject (~1 mi).</t>
+          <t>Hawkins Companies' plan at Amity &amp; Meridian Rd is still in hearings: P&amp;Z recommended denial April 2026, and on June 17 2026 City Council unanimously remanded the revised plan (more office/retail, fewer homes) back to P&amp;Z — no final approval; the 322-unit count may shrink. Bear-case supply only. Land-use dossier SM-12 covers the adjacent block.</t>
         </is>
       </c>
       <c r="H9" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2026/06/10/meridian-emblem-victory-eagle-homes-apartment/</t>
+          <t>https://boisedev.com/news/2026/06/17/a-developer-made-changes-to-a-proposed-400-home-mixed-use-project-meridian-gives-commission-another-vote-on-it/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>Tanner Creek apartments (Waltman/Johnson Ln)</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="C10" s="84" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>136</t>
         </is>
       </c>
       <c r="D10" s="84" t="n"/>
-      <c r="E10" s="43" t="n"/>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-15: Tanner Creek (heard Nov 2023; moved forward) — 83 SF homes + 45 townhomes + 280 phased apartments on ~38 ac, paired with ~30-ac Hawkins commercial between I-84 and Waltman Ln. Residential now being built by CBH Homes; the 280-unit apartment component is latent supply not yet in CoStar/RealPage pipeline.</t>
+          <t>136-unit five-story mixed-use (retail/self-storage/apartments) approved May 2021 as Boise's first Housing Bonus Ordinance project; the building permit submitted Sept 2022 was still 'in corrections' Jan 2023 and the 2.13-ac site is now listed for sale — stalled. Distinct from the delivered 191-unit Denton Apartments (Pacific Companies, Curtis Rd, opened Dec 2025).</t>
         </is>
       </c>
       <c r="H10" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2023/11/28/plans-for-two-large-developments-off-i-84-and-meridian-rd-move-forward/</t>
+          <t>https://boisedev.com/news/2021/05/04/five-story-apartment-building-coming-to-lot-across-from-boise-town-square/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="43" t="inlineStr">
         <is>
-          <t>Graycliff Estates R-40 block</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="C11" s="84" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>275</t>
         </is>
       </c>
       <c r="D11" s="84" t="n"/>
-      <c r="E11" s="43" t="n"/>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-3: Graycliff Estates (Star Development) approved preliminary plat of ~200 SF homes PLUS 224 apartments (R-40 high-density block) on ~52 ac; SF portion building since 2021. The 224-unit apartment block remains unbuilt latent supply.</t>
+          <t>275 units in 4-5 story buildings over a ground-floor garage proposed on the 4.7-ac stalled AutoNation USA dealership site (AutoNation still owner; PivotNorth architect); early application / neighborhood-meeting stage per April 2025 reporting — no approval, permit, or construction as of July 2026. Sits on land-use developable parcel S1109110516.</t>
         </is>
       </c>
       <c r="H11" s="43" t="inlineStr">
         <is>
-          <t>https://www.weknowboise.com/graycliff-estates.php</t>
+          <t>https://boisedev.com/news/2025/04/23/boise-fairview-apartments/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="43" t="inlineStr">
         <is>
-          <t>Touchmark Meadow Lake Village expansion</t>
-        </is>
-      </c>
-      <c r="C12" s="84" t="n"/>
+          <t>12548 West Overland Road</t>
+        </is>
+      </c>
+      <c r="C12" s="84" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
       <c r="D12" s="84" t="n"/>
-      <c r="E12" s="43" t="n"/>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-9: ~64 undeveloped ac of Touchmark's ~121-ac senior community. July 2025 development-modification agreement + rezone + PUD in progress to a broader 'Touchmark Mixed Use' (mixed housing types). Senior-oriented, but adds rental housing capacity 1.5 mi from subject.</t>
+          <t>Hook Family Trust (San Clemente CA) won PUD approval ~March 2024 to replace Overland RV Storage with five 4-story buildings, 156 units (84 1BR/72 2BR) + ~6,000 sf retail; as of mid-2026 the RV storage still operates and the entitled site is marketed for sale on LoopNet — no construction start.</t>
         </is>
       </c>
       <c r="H12" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2025/07/14/touchmark-meridian-meadowlake-mixed-use/</t>
+          <t>https://boisedev.com/news/2023/11/29/hook-trust-boise/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="43" t="inlineStr">
         <is>
-          <t>Ten Mile Crossing residual HDR parcels</t>
+          <t>10975 West Lake Hazel Road</t>
         </is>
       </c>
       <c r="C13" s="84" t="n"/>
       <c r="D13" s="84" t="n"/>
-      <c r="E13" s="43" t="n"/>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>exclude - unverifiable / likely misidentified</t>
+        </is>
+      </c>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-4: residential portion (R-15/R-8) of Brighton's Ten Mile Crossing at SW Overland &amp; Ten Mile — partially built (Cortland South Meridian + CBH SF); remaining High-Density Residential parcels planned/dormant, including an 8.6-ac and a 14.4-ac R-15 vacant parcel (highest-interest sites in the land-use ranking).</t>
+          <t>No development application found at this address (an 11.85-ac parcel with a 1994 single-family home per county records); the nearest real deal — PEG Companies' 118-unit proposal at Five Mile &amp; Lake Hazel — was denied twice by Ada County commissioners (2022 and May 2024). RealPage entry cannot be tied to any live project.</t>
         </is>
       </c>
       <c r="H13" s="43" t="inlineStr">
         <is>
-          <t>https://www.brighton.co/brighton-place/ten-mile-crossing/</t>
+          <t>https://boisedev.com/news/2024/05/22/southwest-boise-commercial/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="43" t="inlineStr">
         <is>
-          <t>Brighton Apex R-15 parcel (Lake Hazel)</t>
+          <t>Cole Road</t>
         </is>
       </c>
       <c r="C14" s="84" t="n"/>
       <c r="D14" s="84" t="n"/>
-      <c r="E14" s="43" t="n"/>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>exclude - existing 1978-82 asset (76u Ridgeline Apartments); not new supply</t>
+        </is>
+      </c>
       <c r="F14" s="43" t="n"/>
       <c r="G14" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-61: 15.1-ac R-15 (med-high-density) parcel on E Lake Hazel Rd inside Brighton's approved Apex/Pinnacle master-plan footprint; adjacent phases actively building. Latent MF-capable ground in the fast-growing S Meridian corridor.</t>
+          <t>709 N Cole Rd is the EXISTING 76-unit Ridgeline Apartments (built 1978-1982), marketed for sale by Berkadia — a misidentified pipeline entry; no evidence of any new 61-unit multifamily proposal or rezone at this address.</t>
         </is>
       </c>
       <c r="H14" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2024/12/20/brighton-pinnacle-costco-meridian/</t>
+          <t>https://properties.berkadia.com/cole-road-469858/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="43" t="inlineStr">
         <is>
-          <t>Outer Banks Subdivision (TM Creek / Cobalt Dr)</t>
+          <t>Villas at Twelve Oaks East</t>
         </is>
       </c>
       <c r="C15" s="84" t="n"/>
       <c r="D15" s="84" t="n"/>
-      <c r="E15" s="43" t="n"/>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>exclude - likely duplicate of existing built Twelve Oaks community</t>
+        </is>
+      </c>
       <c r="F15" s="43" t="n"/>
       <c r="G15" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-1: Ten Mile/I-84 high-density employment/mixed-use core (TMISAP) with heavy MF already delivered (Flats/Lofts/Cortland at Ten Mile). Outer Banks Subdivision approved 2021; balance of the ~198-ac district planned — further MF phases likely alongside the tracked Cobalt Point / The 10 pipeline deals.</t>
+          <t>Could not confirm a distinct 64-unit 'East' phase at 115 S Linder Rd; Meridian records show only ZV-2021-0055 'Twelve Oaks Apartments' and the existing CBH Twelve Oaks (~106u) is built and leasing — the RealPage entry likely duplicates or misidentifies it.</t>
         </is>
       </c>
       <c r="H15" s="43" t="inlineStr">
+        <is>
+          <t>https://weblink.meridiancity.org/WebLink/Browse.aspx?id=244917&amp;dbid=0&amp;repo=MeridianCity&amp;cr=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Promenade Cottages I</t>
+        </is>
+      </c>
+      <c r="C16" s="84" t="n"/>
+      <c r="D16" s="84" t="n"/>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>not multifamily - for-sale townhomes/cottages</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="43" t="inlineStr">
+        <is>
+          <t>Per BuildIdaho and a City of Meridian site plan, Promenade Cottages at the SE corner of Fairview Ave &amp; 3rd St (A-Team Consultants) is a 30-unit mix of FOR-SALE townhomes and single-family alley-load cottage homes — not a rental apartment community.</t>
+        </is>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>https://www.buildidaho.com/meridian-homes-for-sale/promenade-cottages/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Meridian OZ Apartments</t>
+        </is>
+      </c>
+      <c r="C17" s="84" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D17" s="84" t="n"/>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="n"/>
+      <c r="G17" s="43" t="inlineStr">
+        <is>
+          <t>CUP H-2022-0073 (Realm Venture Group): 60 units (30x1BR + 30x2BR) in five 3-story 12-plexes at 1475 E Franklin Rd, SWC Franklin &amp; Locust Grove; hearing record indicates the approval motion carried (early 2023) but no construction evidence found. Land-use dossier SM-155.</t>
+        </is>
+      </c>
+      <c r="H17" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2023/01/23/meridian-oz-apartments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>Union 93</t>
+        </is>
+      </c>
+      <c r="C18" s="84" t="n"/>
+      <c r="D18" s="84" t="n"/>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="43" t="inlineStr">
+        <is>
+          <t>Galena Opportunity Fund's two-building ~385-unit Union 93 East/West at Main &amp; Broadway (downtown Meridian) stalled Nov 2022 after contractors went unpaid; the project entered foreclosure amid litigation and no evidence shows construction resumed — CoStar's 'under construction / Q3 2026 delivery' is stale. Demoted to proposed (Bear-case toggle); monitor for a post-foreclosure restart.</t>
+        </is>
+      </c>
+      <c r="H18" s="43" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/ambitious-downtown-meridian-development-foreclosure-160323894.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Victory Flats</t>
+        </is>
+      </c>
+      <c r="C19" s="84" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D19" s="84" t="n"/>
+      <c r="E19" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="n"/>
+      <c r="G19" s="43" t="inlineStr">
+        <is>
+          <t>Welltower's 301-unit apartment/townhome/SFR rental project at 8373 W Victory Rd (former Boise School District land, SW Boise) approved by Boise City Council March 8 2022 with first units once hoped for late 2023; no groundbreaking, permits, or leasing evidence through mid-2026 — CoStar's Q3 2028 delivery is unsupported.</t>
+        </is>
+      </c>
+      <c r="H19" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2022/03/11/mix-of-hundreds-of-housing-units-approved-on-former-school-district-site-in-southwest-boise/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>The Hummingbird</t>
+        </is>
+      </c>
+      <c r="C20" s="84" t="n"/>
+      <c r="D20" s="84" t="n"/>
+      <c r="E20" s="43" t="inlineStr">
+        <is>
+          <t>dead - approval expired spring 2025</t>
+        </is>
+      </c>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="43" t="inlineStr">
+        <is>
+          <t>Approved 2023 at 170 units (reworked from ~200) on the Aquarium of Boise site at Franklin &amp; Cole (60 N Cole Rd); the two-year approval expired spring 2025 and the owner instead proposed an aquarium expansion on the site (Aug 2025) — CoStar's Q3 2028 delivery is not supported.</t>
+        </is>
+      </c>
+      <c r="H20" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/08/18/aquarium-boise-expansion/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>The Gateway at Ten Mile</t>
+        </is>
+      </c>
+      <c r="C21" s="84" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D21" s="84" t="n"/>
+      <c r="E21" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="43" t="inlineStr">
+        <is>
+          <t>Approved unanimously Nov 2024 (H-2024-0010): 390 units (200 1BR/174 2BR/16 3BR) in six 4-story buildings plus townhomes and 15 commercial buildings at Ten Mile &amp; Franklin; the developer said commercial phases come first and residential is 5-7 years out — CoStar's Q4 2028 delivery looks optimistic. Supersedes the old 559-unit 'The 10' on the same site.</t>
+        </is>
+      </c>
+      <c r="H21" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2024/11/20/the-gateway-at-10-mile-meridian/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>Ascent Overland</t>
+        </is>
+      </c>
+      <c r="C22" s="84" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D22" s="84" t="n"/>
+      <c r="E22" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="43" t="inlineStr">
+        <is>
+          <t>MVRK Development (Denver) 138-unit two-building project near Overland &amp; Cloverdale (West Boise, not Meridian) approved 5-1 by Boise City Council Nov 2023; MVRK's own projects page (July 2026) still lists planning-stage 'TBD' timing — no construction reported.</t>
+        </is>
+      </c>
+      <c r="H22" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2023/11/15/boise-city-council-approves-overland-road-apartment-project-over-some-neighborhood-opposition/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>Fairview</t>
+        </is>
+      </c>
+      <c r="C23" s="84" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D23" s="84" t="n"/>
+      <c r="E23" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F23" s="43" t="n"/>
+      <c r="G23" s="43" t="inlineStr">
+        <is>
+          <t>Biltmore Co. / Pivot North Architecture application (Jan 2023) for 150 market-rate units (1-3BR, 797-1,872 sf, 2-3 story buildings) at 1005 E Fairview Ave; still needs Meridian P&amp;Z and City Council approval — no hearing date found, no construction.</t>
+        </is>
+      </c>
+      <c r="H23" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2023/01/11/fairview-apartments-meridian/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>Promenade Cottages II</t>
+        </is>
+      </c>
+      <c r="C24" s="84" t="n"/>
+      <c r="D24" s="84" t="n"/>
+      <c r="E24" s="43" t="inlineStr">
+        <is>
+          <t>not multifamily - for-sale townhomes/cottages (same community as Phase I)</t>
+        </is>
+      </c>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="43" t="inlineStr">
+        <is>
+          <t>Phase II of the Promenade Cottages for-sale townhome/cottage community at Fairview &amp; 3rd (A-Team Consultants) — same for-sale product as Phase I; not rental apartment supply.</t>
+        </is>
+      </c>
+      <c r="H24" s="43" t="inlineStr">
+        <is>
+          <t>https://www.buildidaho.com/meridian-homes-for-sale/promenade-cottages/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="83" t="inlineStr">
+        <is>
+          <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="50" t="inlineStr">
+        <is>
+          <t>Property / Site</t>
+        </is>
+      </c>
+      <c r="C27" s="50" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D27" s="50" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="E27" s="50" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F27" s="50" t="inlineStr">
+        <is>
+          <t>Leasing Pace</t>
+        </is>
+      </c>
+      <c r="G27" s="50" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="H27" s="50" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>Emblem Meridian (Quarterra) / Artisan Victory Market site</t>
+        </is>
+      </c>
+      <c r="C28" s="84" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="43" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-76: ~12-ac BPS Eagle Road LLC assemblage on S Eagle Rd. 'Artisan Victory Market' (H-2022-0066) approved 2023 for 131 build-to-rent units + commercial but never built; superseded by Quarterra's 'Emblem Meridian' ~250-unit concept (pre-application June 2026). Closest large latent MF site to the subject (~1 mi).</t>
+        </is>
+      </c>
+      <c r="H28" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2026/06/10/meridian-emblem-victory-eagle-homes-apartment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>Tanner Creek apartments (Waltman/Johnson Ln)</t>
+        </is>
+      </c>
+      <c r="C29" s="84" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D29" s="84" t="n"/>
+      <c r="E29" s="43" t="n"/>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-15: Tanner Creek (heard Nov 2023; moved forward) — 83 SF homes + 45 townhomes + 280 phased apartments on ~38 ac, paired with ~30-ac Hawkins commercial between I-84 and Waltman Ln. Residential now being built by CBH Homes; the 280-unit apartment component is latent supply not yet in the CoStar/RealPage pipeline.</t>
+        </is>
+      </c>
+      <c r="H29" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2023/11/28/plans-for-two-large-developments-off-i-84-and-meridian-rd-move-forward/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>Graycliff Estates R-40 block</t>
+        </is>
+      </c>
+      <c r="C30" s="84" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D30" s="84" t="n"/>
+      <c r="E30" s="43" t="n"/>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-3: Graycliff Estates (Star Development) approved preliminary plat of ~200 SF homes PLUS 224 apartments (R-40 high-density block) on ~52 ac; SF portion building since 2021. The 224-unit apartment block remains unbuilt latent supply.</t>
+        </is>
+      </c>
+      <c r="H30" s="43" t="inlineStr">
+        <is>
+          <t>https://www.weknowboise.com/graycliff-estates.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>Touchmark Meadow Lake Village expansion</t>
+        </is>
+      </c>
+      <c r="C31" s="84" t="n"/>
+      <c r="D31" s="84" t="n"/>
+      <c r="E31" s="43" t="n"/>
+      <c r="F31" s="43" t="n"/>
+      <c r="G31" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-9: ~64 undeveloped ac of Touchmark's ~121-ac senior community. July 2025 development-modification agreement + rezone + PUD in progress to a broader 'Touchmark Mixed Use' (mixed housing types). Senior-oriented, but adds rental housing capacity 1.5 mi from subject.</t>
+        </is>
+      </c>
+      <c r="H31" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/07/14/touchmark-meridian-meadowlake-mixed-use/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>Ten Mile Crossing residual HDR parcels</t>
+        </is>
+      </c>
+      <c r="C32" s="84" t="n"/>
+      <c r="D32" s="84" t="n"/>
+      <c r="E32" s="43" t="n"/>
+      <c r="F32" s="43" t="n"/>
+      <c r="G32" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-4: residential portion (R-15/R-8) of Brighton's Ten Mile Crossing at SW Overland &amp; Ten Mile — partially built (Cortland South Meridian + CBH SF); remaining High-Density Residential parcels planned/dormant, including an 8.6-ac and a 14.4-ac R-15 vacant parcel (highest-interest sites in the land-use ranking). Note: South Ridge II (164u UC, tracked in the chart) is rising in this same corridor.</t>
+        </is>
+      </c>
+      <c r="H32" s="43" t="inlineStr">
+        <is>
+          <t>https://www.brighton.co/brighton-place/ten-mile-crossing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>Brighton Apex R-15 parcel (Lake Hazel)</t>
+        </is>
+      </c>
+      <c r="C33" s="84" t="n"/>
+      <c r="D33" s="84" t="n"/>
+      <c r="E33" s="43" t="n"/>
+      <c r="F33" s="43" t="n"/>
+      <c r="G33" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-61: 15.1-ac R-15 (med-high-density) parcel on E Lake Hazel Rd inside Brighton's approved Apex/Pinnacle master-plan footprint; adjacent phases actively building. Latent MF-capable ground in the fast-growing S Meridian corridor.</t>
+        </is>
+      </c>
+      <c r="H33" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2024/12/20/brighton-pinnacle-costco-meridian/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>Outer Banks Subdivision (TM Creek / Cobalt Dr)</t>
+        </is>
+      </c>
+      <c r="C34" s="84" t="n"/>
+      <c r="D34" s="84" t="n"/>
+      <c r="E34" s="43" t="n"/>
+      <c r="F34" s="43" t="n"/>
+      <c r="G34" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-1: Ten Mile/I-84 high-density employment/mixed-use core (TMISAP) with heavy MF already delivered (Flats/Lofts/Cortland at Ten Mile). Outer Banks Subdivision approved 2021; balance of the ~198-ac district planned — further MF phases likely alongside the tracked pipeline.</t>
+        </is>
+      </c>
+      <c r="H34" s="43" t="inlineStr">
         <is>
           <t>https://boisedev.com/news/2021/12/17/outer-banks-pera-place/</t>
         </is>
@@ -7888,7 +7904,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B26:H26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
+++ b/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M54"/>
+  <dimension ref="B2:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2166,7 +2166,7 @@
       <c r="B39" s="28" t="n"/>
       <c r="C39" s="29" t="inlineStr">
         <is>
-          <t>PROPOSED (12 properties, 3,014 units)</t>
+          <t>PROPOSED (13 properties, 3,176 units)</t>
         </is>
       </c>
     </row>
@@ -2222,15 +2222,15 @@
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>Victory Flats</t>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
         </is>
       </c>
       <c r="D41" s="32" t="n">
-        <v>301</v>
+        <v>162</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="F41" s="33" t="n"/>
@@ -2241,20 +2241,16 @@
       </c>
       <c r="H41" s="31" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" s="35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J41" s="30" t="inlineStr">
-        <is>
-          <t>Townhome</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="J41" s="30" t="n"/>
       <c r="K41" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
         </is>
       </c>
       <c r="M41">
@@ -2268,15 +2264,15 @@
       </c>
       <c r="C42" s="31" t="inlineStr">
         <is>
-          <t>The Gateway at Ten Mile</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>390</v>
+        <v>301</v>
       </c>
       <c r="E42" s="30" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F42" s="33" t="n"/>
@@ -2287,15 +2283,15 @@
       </c>
       <c r="H42" s="31" t="inlineStr">
         <is>
-          <t>TGI Corp</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="I42" s="35" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K42" s="31" t="inlineStr">
@@ -2314,15 +2310,15 @@
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>138</v>
+        <v>390</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
-          <t>Q1 2029</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F43" s="33" t="n"/>
@@ -2333,11 +2329,11 @@
       </c>
       <c r="H43" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TGI Corp</t>
         </is>
       </c>
       <c r="I43" s="35" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J43" s="30" t="inlineStr">
         <is>
@@ -2360,15 +2356,15 @@
       </c>
       <c r="C44" s="31" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="D44" s="32" t="n">
-        <v>472</v>
+        <v>138</v>
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="F44" s="33" t="n"/>
@@ -2383,7 +2379,7 @@
         </is>
       </c>
       <c r="I44" s="35" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J44" s="30" t="inlineStr">
         <is>
@@ -2392,7 +2388,7 @@
       </c>
       <c r="K44" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M44">
@@ -2406,11 +2402,11 @@
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>322</v>
+        <v>472</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
@@ -2429,7 +2425,7 @@
         </is>
       </c>
       <c r="I45" s="35" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J45" s="30" t="inlineStr">
         <is>
@@ -2452,11 +2448,11 @@
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
@@ -2475,7 +2471,7 @@
         </is>
       </c>
       <c r="I46" s="35" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J46" s="30" t="inlineStr">
         <is>
@@ -2498,11 +2494,11 @@
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="D47" s="32" t="n">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -2521,11 +2517,11 @@
         </is>
       </c>
       <c r="I47" s="35" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J47" s="30" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K47" s="31" t="inlineStr">
@@ -2544,11 +2540,11 @@
       </c>
       <c r="C48" s="31" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>Cobalt Point</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>156</v>
+        <v>264</v>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
@@ -2567,11 +2563,11 @@
         </is>
       </c>
       <c r="I48" s="35" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J48" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K48" s="31" t="inlineStr">
@@ -2590,11 +2586,11 @@
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E49" s="30" t="inlineStr">
         <is>
@@ -2613,11 +2609,11 @@
         </is>
       </c>
       <c r="I49" s="35" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K49" s="31" t="inlineStr">
@@ -2636,11 +2632,11 @@
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
@@ -2659,11 +2655,11 @@
         </is>
       </c>
       <c r="I50" s="35" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J50" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K50" s="31" t="inlineStr">
@@ -2682,11 +2678,11 @@
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
@@ -2701,20 +2697,20 @@
       </c>
       <c r="H51" s="31" t="inlineStr">
         <is>
-          <t>Peak Capital Investments Llc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I51" s="35" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J51" s="30" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K51" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M51">
@@ -2722,8 +2718,54 @@
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="36" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="30" t="n">
+        <v>41</v>
+      </c>
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>Meridian OZ Apartments</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="E52" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F52" s="33" t="n"/>
+      <c r="G52" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="31" t="inlineStr">
+        <is>
+          <t>Peak Capital Investments Llc</t>
+        </is>
+      </c>
+      <c r="I52" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J52" s="30" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K52" s="31" t="inlineStr">
+        <is>
+          <t>Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M52">
+        <f>IFERROR(VALUE(RIGHT(E52,4))*4+MATCH(LEFT(E52,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="36" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Rent ($) = HelloData mix-weighted asking where covered, else market asking (CoStar). Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
@@ -2735,8 +2777,8 @@
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C28:K28"/>
+    <mergeCell ref="B55:K55"/>
     <mergeCell ref="C39:K39"/>
-    <mergeCell ref="B54:K54"/>
     <mergeCell ref="C35:K35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3264,13 +3306,17 @@
       </c>
       <c r="R17" s="43" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
         </is>
       </c>
       <c r="S17" s="44" t="n">
-        <v>156</v>
-      </c>
-      <c r="T17" s="48" t="inlineStr"/>
+        <v>162</v>
+      </c>
+      <c r="T17" s="48" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
       <c r="U17" s="48" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3351,11 +3397,11 @@
       </c>
       <c r="R18" s="43" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="S18" s="44" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="T18" s="48" t="inlineStr"/>
       <c r="U18" s="48" t="inlineStr">
@@ -3401,46 +3447,42 @@
         <v>450</v>
       </c>
       <c r="I19" s="52">
-        <f>SUMIFS('Competitive Analysis'!$D$5:$D$51,'Competitive Analysis'!$M$5:$M$51,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$51,"&lt;="&amp;8105)</f>
+        <f>SUMIFS('Competitive Analysis'!$D$5:$D$52,'Competitive Analysis'!$M$5:$M$52,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$52,"&lt;="&amp;8105)</f>
         <v/>
       </c>
       <c r="J19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,1)+SUMIFS($S$10:$S$21,$W$10:$W$21,1,$X$10:$X$21,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,1)+SUMIFS($S$10:$S$22,$W$10:$W$22,1,$X$10:$X$22,1)</f>
         <v/>
       </c>
       <c r="K19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,2)+SUMIFS($S$10:$S$21,$W$10:$W$21,2,$X$10:$X$21,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,2)+SUMIFS($S$10:$S$22,$W$10:$W$22,2,$X$10:$X$22,1)</f>
         <v/>
       </c>
       <c r="L19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,3)+SUMIFS($S$10:$S$21,$W$10:$W$21,3,$X$10:$X$21,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,3)+SUMIFS($S$10:$S$22,$W$10:$W$22,3,$X$10:$X$22,1)</f>
         <v/>
       </c>
       <c r="M19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,4)+SUMIFS($S$10:$S$21,$W$10:$W$21,4,$X$10:$X$21,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,4)+SUMIFS($S$10:$S$22,$W$10:$W$22,4,$X$10:$X$22,1)</f>
         <v/>
       </c>
       <c r="N19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,5)+SUMIFS($S$10:$S$21,$W$10:$W$21,5,$X$10:$X$21,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,5)+SUMIFS($S$10:$S$22,$W$10:$W$22,5,$X$10:$X$22,1)</f>
         <v/>
       </c>
       <c r="O19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,6)+SUMIFS($S$10:$S$21,$W$10:$W$21,6,$X$10:$X$21,1)</f>
+        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,6)+SUMIFS($S$10:$S$22,$W$10:$W$22,6,$X$10:$X$22,1)</f>
         <v/>
       </c>
       <c r="R19" s="43" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="S19" s="44" t="n">
-        <v>138</v>
-      </c>
-      <c r="T19" s="48" t="inlineStr">
-        <is>
-          <t>Q1 2029</t>
-        </is>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="T19" s="48" t="inlineStr"/>
       <c r="U19" s="48" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3512,13 +3554,17 @@
       </c>
       <c r="R20" s="43" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="S20" s="44" t="n">
-        <v>136</v>
-      </c>
-      <c r="T20" s="48" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="T20" s="48" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
       <c r="U20" s="48" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3591,11 +3637,11 @@
       </c>
       <c r="R21" s="43" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="S21" s="44" t="n">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="T21" s="48" t="inlineStr"/>
       <c r="U21" s="48" t="inlineStr">
@@ -3621,6 +3667,32 @@
         <is>
           <t>SUBJECT (Seasons at Meridian)</t>
         </is>
+      </c>
+      <c r="R22" s="43" t="inlineStr">
+        <is>
+          <t>Meridian OZ Apartments</t>
+        </is>
+      </c>
+      <c r="S22" s="44" t="n">
+        <v>60</v>
+      </c>
+      <c r="T22" s="48" t="inlineStr"/>
+      <c r="U22" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V22">
+        <f>IFERROR(VALUE(RIGHT(T22,4))*4+MATCH(LEFT(T22,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W22">
+        <f>IF(V22="","",IF(V22&lt;=$Z$1,0,MAX(1,INT((V22-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>IF(U22="All",1,IF(U22="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U22="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="14.4" customHeight="1">
@@ -4948,7 +5020,7 @@
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bear only,Bear+Base,All,None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4962,7 +5034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6719,23 +6791,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Union 93</t>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>221-225 E Broadway Ave</t>
+          <t>1770 S Maple Grove Rd, Boise 83704</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>350</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2026</v>
+        <v>162</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Q3 2026</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -6752,28 +6821,36 @@
       <c r="N33" s="82" t="n"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>Union 93</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1475 E Franklin Rd</t>
+          <t>221-225 E Broadway Ave</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>60</v>
+        <v>350</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -6794,23 +6871,23 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Meridian OZ Apartments</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>580 N Cole Rd</t>
+          <t>1475 E Franklin Rd</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -6826,28 +6903,28 @@
       <c r="N35" s="82" t="n"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>E Fairview Ave &amp; N Records Way</t>
+          <t>580 N Cole Rd</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>472</v>
+        <v>136</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -6875,16 +6952,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S Cobalt Point Way &amp; E Copper Point Dr</t>
+          <t>E Fairview Ave &amp; N Records Way</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>264</v>
+        <v>472</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6912,16 +6989,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>Cobalt Point</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1005 E Fairview Ave</t>
+          <t>S Cobalt Point Way &amp; E Copper Point Dr</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>150</v>
+        <v>264</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6933,12 +7010,8 @@
       <c r="J38" s="81" t="n"/>
       <c r="K38" s="82" t="n"/>
       <c r="L38" s="82" t="n"/>
-      <c r="M38" s="82" t="n">
-        <v>1837.580964685616</v>
-      </c>
-      <c r="N38" s="82" t="n">
-        <v>1837.580964685616</v>
-      </c>
+      <c r="M38" s="82" t="n"/>
+      <c r="N38" s="82" t="n"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -6953,16 +7026,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12548 W Overland Rd</t>
+          <t>1005 E Fairview Ave</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6974,8 +7047,12 @@
       <c r="J39" s="81" t="n"/>
       <c r="K39" s="82" t="n"/>
       <c r="L39" s="82" t="n"/>
-      <c r="M39" s="82" t="n"/>
-      <c r="N39" s="82" t="n"/>
+      <c r="M39" s="82" t="n">
+        <v>1837.580964685616</v>
+      </c>
+      <c r="N39" s="82" t="n">
+        <v>1837.580964685616</v>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -6990,16 +7067,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12565 W Fairview Ave</t>
+          <t>12548 W Overland Rd</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>275</v>
+        <v>156</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -7027,16 +7104,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Amity Ave &amp; Meridian Rd</t>
+          <t>12565 W Fairview Ave</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>322</v>
+        <v>275</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -7056,6 +7133,43 @@
         </is>
       </c>
       <c r="P41" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Syringa Crossing</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Amity Ave &amp; Meridian Rd</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>322</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H42" s="81" t="n"/>
+      <c r="I42" s="81" t="n"/>
+      <c r="J42" s="81" t="n"/>
+      <c r="K42" s="82" t="n"/>
+      <c r="L42" s="82" t="n"/>
+      <c r="M42" s="82" t="n"/>
+      <c r="N42" s="82" t="n"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
@@ -7072,7 +7186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -7698,84 +7812,92 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="83" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
+        </is>
+      </c>
+      <c r="C25" s="84" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D25" s="84" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="E25" s="43" t="inlineStr">
+        <is>
+          <t>proposed - equity raise underway; construction targeted Q3 2026</t>
+        </is>
+      </c>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="43" t="inlineStr">
+        <is>
+          <t>Hawkins Companies OM (July 2026, research/oms/): 162-unit Class A garden (75x1BR $1,615 / 60x2BR / 27x3BR, avg $1,787 at 908sf) on 6.13 ac at 1770 S Maple Grove Rd, Boise — 3.4 mi from subject, inside the 5-mi ring. $41.7M TPC, GMP contract, construction targeted Q3 2026; OM lease-up: first occupancy month ~18 (=&gt; ~Q1 2028 first units), 20 units/mo absorption, ~42% occupied Yr 2. NOT tracked by CoStar or RealPage. Land-use analysis site 177: parcel S1124223215 in the developable-vacant set but zoned R-2 (Medium MF-threat, conditional) with 'single-family oriented' FLU — the OM proves the conditional path being exercised; reclassify from latent to tracked pipeline.</t>
+        </is>
+      </c>
+      <c r="H25" s="43" t="inlineStr">
+        <is>
+          <t>Hawkins Capital Markets OM — research/oms/Maple_Grove_Overland_Equity_Hawkins_OM.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="83" t="inlineStr">
         <is>
           <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="50" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="50" t="inlineStr">
         <is>
           <t>Property / Site</t>
         </is>
       </c>
-      <c r="C27" s="50" t="inlineStr">
+      <c r="C28" s="50" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D27" s="50" t="inlineStr">
+      <c r="D28" s="50" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="E27" s="50" t="inlineStr">
+      <c r="E28" s="50" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F27" s="50" t="inlineStr">
+      <c r="F28" s="50" t="inlineStr">
         <is>
           <t>Leasing Pace</t>
         </is>
       </c>
-      <c r="G27" s="50" t="inlineStr">
+      <c r="G28" s="50" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="H27" s="50" t="inlineStr">
+      <c r="H28" s="50" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="43" t="inlineStr">
-        <is>
-          <t>Emblem Meridian (Quarterra) / Artisan Victory Market site</t>
-        </is>
-      </c>
-      <c r="C28" s="84" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="D28" s="84" t="n"/>
-      <c r="E28" s="43" t="n"/>
-      <c r="F28" s="43" t="n"/>
-      <c r="G28" s="43" t="inlineStr">
-        <is>
-          <t>Land-use analysis site SM-76: ~12-ac BPS Eagle Road LLC assemblage on S Eagle Rd. 'Artisan Victory Market' (H-2022-0066) approved 2023 for 131 build-to-rent units + commercial but never built; superseded by Quarterra's 'Emblem Meridian' ~250-unit concept (pre-application June 2026). Closest large latent MF site to the subject (~1 mi).</t>
-        </is>
-      </c>
-      <c r="H28" s="43" t="inlineStr">
-        <is>
-          <t>https://boisedev.com/news/2026/06/10/meridian-emblem-victory-eagle-homes-apartment/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="43" t="inlineStr">
         <is>
-          <t>Tanner Creek apartments (Waltman/Johnson Ln)</t>
+          <t>Emblem Meridian (Quarterra) / Artisan Victory Market site</t>
         </is>
       </c>
       <c r="C29" s="84" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D29" s="84" t="n"/>
@@ -7783,24 +7905,24 @@
       <c r="F29" s="43" t="n"/>
       <c r="G29" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-15: Tanner Creek (heard Nov 2023; moved forward) — 83 SF homes + 45 townhomes + 280 phased apartments on ~38 ac, paired with ~30-ac Hawkins commercial between I-84 and Waltman Ln. Residential now being built by CBH Homes; the 280-unit apartment component is latent supply not yet in the CoStar/RealPage pipeline.</t>
+          <t>Land-use analysis site SM-76: ~12-ac BPS Eagle Road LLC assemblage on S Eagle Rd. 'Artisan Victory Market' (H-2022-0066) approved 2023 for 131 build-to-rent units + commercial but never built; superseded by Quarterra's 'Emblem Meridian' ~250-unit concept (pre-application June 2026). Closest large latent MF site to the subject (~1 mi).</t>
         </is>
       </c>
       <c r="H29" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2023/11/28/plans-for-two-large-developments-off-i-84-and-meridian-rd-move-forward/</t>
+          <t>https://boisedev.com/news/2026/06/10/meridian-emblem-victory-eagle-homes-apartment/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="43" t="inlineStr">
         <is>
-          <t>Graycliff Estates R-40 block</t>
+          <t>Tanner Creek apartments (Waltman/Johnson Ln)</t>
         </is>
       </c>
       <c r="C30" s="84" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>280</t>
         </is>
       </c>
       <c r="D30" s="84" t="n"/>
@@ -7808,40 +7930,44 @@
       <c r="F30" s="43" t="n"/>
       <c r="G30" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-3: Graycliff Estates (Star Development) approved preliminary plat of ~200 SF homes PLUS 224 apartments (R-40 high-density block) on ~52 ac; SF portion building since 2021. The 224-unit apartment block remains unbuilt latent supply.</t>
+          <t>Land-use analysis site SM-15: Tanner Creek (heard Nov 2023; moved forward) — 83 SF homes + 45 townhomes + 280 phased apartments on ~38 ac, paired with ~30-ac Hawkins commercial between I-84 and Waltman Ln. Residential now being built by CBH Homes; the 280-unit apartment component is latent supply not yet in the CoStar/RealPage pipeline.</t>
         </is>
       </c>
       <c r="H30" s="43" t="inlineStr">
         <is>
-          <t>https://www.weknowboise.com/graycliff-estates.php</t>
+          <t>https://boisedev.com/news/2023/11/28/plans-for-two-large-developments-off-i-84-and-meridian-rd-move-forward/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="43" t="inlineStr">
         <is>
-          <t>Touchmark Meadow Lake Village expansion</t>
-        </is>
-      </c>
-      <c r="C31" s="84" t="n"/>
+          <t>Graycliff Estates R-40 block</t>
+        </is>
+      </c>
+      <c r="C31" s="84" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
       <c r="D31" s="84" t="n"/>
       <c r="E31" s="43" t="n"/>
       <c r="F31" s="43" t="n"/>
       <c r="G31" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-9: ~64 undeveloped ac of Touchmark's ~121-ac senior community. July 2025 development-modification agreement + rezone + PUD in progress to a broader 'Touchmark Mixed Use' (mixed housing types). Senior-oriented, but adds rental housing capacity 1.5 mi from subject.</t>
+          <t>Land-use analysis site SM-3: Graycliff Estates (Star Development) approved preliminary plat of ~200 SF homes PLUS 224 apartments (R-40 high-density block) on ~52 ac; SF portion building since 2021. The 224-unit apartment block remains unbuilt latent supply.</t>
         </is>
       </c>
       <c r="H31" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2025/07/14/touchmark-meridian-meadowlake-mixed-use/</t>
+          <t>https://www.weknowboise.com/graycliff-estates.php</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="43" t="inlineStr">
         <is>
-          <t>Ten Mile Crossing residual HDR parcels</t>
+          <t>Touchmark Meadow Lake Village expansion</t>
         </is>
       </c>
       <c r="C32" s="84" t="n"/>
@@ -7850,19 +7976,19 @@
       <c r="F32" s="43" t="n"/>
       <c r="G32" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-4: residential portion (R-15/R-8) of Brighton's Ten Mile Crossing at SW Overland &amp; Ten Mile — partially built (Cortland South Meridian + CBH SF); remaining High-Density Residential parcels planned/dormant, including an 8.6-ac and a 14.4-ac R-15 vacant parcel (highest-interest sites in the land-use ranking). Note: South Ridge II (164u UC, tracked in the chart) is rising in this same corridor.</t>
+          <t>Land-use analysis site SM-9: ~64 undeveloped ac of Touchmark's ~121-ac senior community. July 2025 development-modification agreement + rezone + PUD in progress to a broader 'Touchmark Mixed Use' (mixed housing types). Senior-oriented, but adds rental housing capacity 1.5 mi from subject.</t>
         </is>
       </c>
       <c r="H32" s="43" t="inlineStr">
         <is>
-          <t>https://www.brighton.co/brighton-place/ten-mile-crossing/</t>
+          <t>https://boisedev.com/news/2025/07/14/touchmark-meridian-meadowlake-mixed-use/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="43" t="inlineStr">
         <is>
-          <t>Brighton Apex R-15 parcel (Lake Hazel)</t>
+          <t>Ten Mile Crossing residual HDR parcels</t>
         </is>
       </c>
       <c r="C33" s="84" t="n"/>
@@ -7871,19 +7997,19 @@
       <c r="F33" s="43" t="n"/>
       <c r="G33" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-61: 15.1-ac R-15 (med-high-density) parcel on E Lake Hazel Rd inside Brighton's approved Apex/Pinnacle master-plan footprint; adjacent phases actively building. Latent MF-capable ground in the fast-growing S Meridian corridor.</t>
+          <t>Land-use analysis site SM-4: residential portion (R-15/R-8) of Brighton's Ten Mile Crossing at SW Overland &amp; Ten Mile — partially built (Cortland South Meridian + CBH SF); remaining High-Density Residential parcels planned/dormant, including an 8.6-ac and a 14.4-ac R-15 vacant parcel (highest-interest sites in the land-use ranking). Note: South Ridge II (164u UC, tracked in the chart) is rising in this same corridor.</t>
         </is>
       </c>
       <c r="H33" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2024/12/20/brighton-pinnacle-costco-meridian/</t>
+          <t>https://www.brighton.co/brighton-place/ten-mile-crossing/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="43" t="inlineStr">
         <is>
-          <t>Outer Banks Subdivision (TM Creek / Cobalt Dr)</t>
+          <t>Brighton Apex R-15 parcel (Lake Hazel)</t>
         </is>
       </c>
       <c r="C34" s="84" t="n"/>
@@ -7892,10 +8018,31 @@
       <c r="F34" s="43" t="n"/>
       <c r="G34" s="43" t="inlineStr">
         <is>
+          <t>Land-use analysis site SM-61: 15.1-ac R-15 (med-high-density) parcel on E Lake Hazel Rd inside Brighton's approved Apex/Pinnacle master-plan footprint; adjacent phases actively building. Latent MF-capable ground in the fast-growing S Meridian corridor.</t>
+        </is>
+      </c>
+      <c r="H34" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2024/12/20/brighton-pinnacle-costco-meridian/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="43" t="inlineStr">
+        <is>
+          <t>Outer Banks Subdivision (TM Creek / Cobalt Dr)</t>
+        </is>
+      </c>
+      <c r="C35" s="84" t="n"/>
+      <c r="D35" s="84" t="n"/>
+      <c r="E35" s="43" t="n"/>
+      <c r="F35" s="43" t="n"/>
+      <c r="G35" s="43" t="inlineStr">
+        <is>
           <t>Land-use analysis site SM-1: Ten Mile/I-84 high-density employment/mixed-use core (TMISAP) with heavy MF already delivered (Flats/Lofts/Cortland at Ten Mile). Outer Banks Subdivision approved 2021; balance of the ~198-ac district planned — further MF phases likely alongside the tracked pipeline.</t>
         </is>
       </c>
-      <c r="H34" s="43" t="inlineStr">
+      <c r="H35" s="43" t="inlineStr">
         <is>
           <t>https://boisedev.com/news/2021/12/17/outer-banks-pera-place/</t>
         </is>
@@ -7904,7 +8051,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B27:H27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
+++ b/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
@@ -369,10 +369,10 @@
     <xf numFmtId="3" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M55"/>
+  <dimension ref="B2:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2074,7 +2074,7 @@
       <c r="B35" s="20" t="n"/>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>UNDER CONSTRUCTION (2 properties, 716 units)</t>
+          <t>UNDER CONSTRUCTION (5 properties, 1,213 units)</t>
         </is>
       </c>
     </row>
@@ -2126,15 +2126,15 @@
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>Vanguard Village</t>
+          <t>Dorado Station</t>
         </is>
       </c>
       <c r="D37" s="24" t="n">
-        <v>552</v>
+        <v>212</v>
       </c>
       <c r="E37" s="22" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="F37" s="25" t="n"/>
@@ -2149,66 +2149,142 @@
         </is>
       </c>
       <c r="I37" s="27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J37" s="22" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n"/>
+        <v>4.9</v>
+      </c>
+      <c r="J37" s="22" t="n"/>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
+        </is>
+      </c>
       <c r="M37">
         <f>IFERROR(VALUE(RIGHT(E37,4))*4+MATCH(LEFT(E37,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
     </row>
+    <row r="38">
+      <c r="B38" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>Summertown (remaining phases)</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="n">
+        <v>72</v>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="F38" s="25" t="n"/>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J38" s="22" t="n"/>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
+        </is>
+      </c>
+      <c r="M38">
+        <f>IFERROR(VALUE(RIGHT(E38,4))*4+MATCH(LEFT(E38,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="39">
-      <c r="B39" s="28" t="n"/>
-      <c r="C39" s="29" t="inlineStr">
-        <is>
-          <t>PROPOSED (13 properties, 3,176 units)</t>
-        </is>
+      <c r="B39" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>Vanguard Village</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="n">
+        <v>552</v>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="F39" s="25" t="n"/>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J39" s="22" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="n"/>
+      <c r="M39">
+        <f>IFERROR(VALUE(RIGHT(E39,4))*4+MATCH(LEFT(E39,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="30" t="n">
-        <v>29</v>
-      </c>
-      <c r="C40" s="31" t="inlineStr">
-        <is>
-          <t>Union 93</t>
-        </is>
-      </c>
-      <c r="D40" s="32" t="n">
-        <v>350</v>
-      </c>
-      <c r="E40" s="30" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
-      <c r="F40" s="33" t="n"/>
-      <c r="G40" s="34" t="inlineStr">
+      <c r="B40" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>Centrepoint</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="n">
+        <v>213</v>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="F40" s="25" t="n"/>
+      <c r="G40" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H40" s="31" t="inlineStr">
-        <is>
-          <t>Grey Owl Holdings Llc</t>
-        </is>
-      </c>
-      <c r="I40" s="35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J40" s="30" t="inlineStr">
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>Privately Owned</t>
+        </is>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K40" s="31" t="inlineStr">
-        <is>
-          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: under construction - revived; permits issuing 2026</t>
         </is>
       </c>
       <c r="M40">
@@ -2216,92 +2292,12 @@
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="C41" s="31" t="inlineStr">
-        <is>
-          <t>The Judy (Maple Grove &amp; Overland)</t>
-        </is>
-      </c>
-      <c r="D41" s="32" t="n">
-        <v>162</v>
-      </c>
-      <c r="E41" s="30" t="inlineStr">
-        <is>
-          <t>Q1 2028</t>
-        </is>
-      </c>
-      <c r="F41" s="33" t="n"/>
-      <c r="G41" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J41" s="30" t="n"/>
-      <c r="K41" s="31" t="inlineStr">
-        <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
-        </is>
-      </c>
-      <c r="M41">
-        <f>IFERROR(VALUE(RIGHT(E41,4))*4+MATCH(LEFT(E41,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="42">
-      <c r="B42" s="30" t="n">
-        <v>31</v>
-      </c>
-      <c r="C42" s="31" t="inlineStr">
-        <is>
-          <t>Victory Flats</t>
-        </is>
-      </c>
-      <c r="D42" s="32" t="n">
-        <v>301</v>
-      </c>
-      <c r="E42" s="30" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="F42" s="33" t="n"/>
-      <c r="G42" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="31" t="inlineStr">
-        <is>
-          <t>Welltower Inc.</t>
-        </is>
-      </c>
-      <c r="I42" s="35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J42" s="30" t="inlineStr">
-        <is>
-          <t>Townhome</t>
-        </is>
-      </c>
-      <c r="K42" s="31" t="inlineStr">
-        <is>
-          <t>Diligence: proposed</t>
-        </is>
-      </c>
-      <c r="M42">
-        <f>IFERROR(VALUE(RIGHT(E42,4))*4+MATCH(LEFT(E42,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>PROPOSED (15 properties, 3,646 units)</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2310,15 +2306,15 @@
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>The Gateway at Ten Mile</t>
+          <t>Union 93</t>
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="F43" s="33" t="n"/>
@@ -2329,11 +2325,11 @@
       </c>
       <c r="H43" s="31" t="inlineStr">
         <is>
-          <t>TGI Corp</t>
+          <t>Grey Owl Holdings Llc</t>
         </is>
       </c>
       <c r="I43" s="35" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J43" s="30" t="inlineStr">
         <is>
@@ -2342,7 +2338,7 @@
       </c>
       <c r="K43" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
         </is>
       </c>
       <c r="M43">
@@ -2356,15 +2352,15 @@
       </c>
       <c r="C44" s="31" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
         </is>
       </c>
       <c r="D44" s="32" t="n">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Q1 2029</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="F44" s="33" t="n"/>
@@ -2379,16 +2375,12 @@
         </is>
       </c>
       <c r="I44" s="35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J44" s="30" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="J44" s="30" t="n"/>
       <c r="K44" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
         </is>
       </c>
       <c r="M44">
@@ -2402,15 +2394,15 @@
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>472</v>
+        <v>301</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F45" s="33" t="n"/>
@@ -2421,20 +2413,20 @@
       </c>
       <c r="H45" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="I45" s="35" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J45" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K45" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M45">
@@ -2448,15 +2440,15 @@
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F46" s="33" t="n"/>
@@ -2467,11 +2459,11 @@
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TGI Corp</t>
         </is>
       </c>
       <c r="I46" s="35" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J46" s="30" t="inlineStr">
         <is>
@@ -2480,7 +2472,7 @@
       </c>
       <c r="K46" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M46">
@@ -2494,15 +2486,15 @@
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="D47" s="32" t="n">
-        <v>275</v>
+        <v>138</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="F47" s="33" t="n"/>
@@ -2517,7 +2509,7 @@
         </is>
       </c>
       <c r="I47" s="35" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J47" s="30" t="inlineStr">
         <is>
@@ -2526,7 +2518,7 @@
       </c>
       <c r="K47" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M47">
@@ -2540,11 +2532,11 @@
       </c>
       <c r="C48" s="31" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>264</v>
+        <v>472</v>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
@@ -2563,11 +2555,11 @@
         </is>
       </c>
       <c r="I48" s="35" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J48" s="30" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K48" s="31" t="inlineStr">
@@ -2586,11 +2578,11 @@
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>156</v>
+        <v>322</v>
       </c>
       <c r="E49" s="30" t="inlineStr">
         <is>
@@ -2609,7 +2601,7 @@
         </is>
       </c>
       <c r="I49" s="35" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
@@ -2632,11 +2624,11 @@
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
@@ -2659,7 +2651,7 @@
       </c>
       <c r="J50" s="30" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K50" s="31" t="inlineStr">
@@ -2678,11 +2670,11 @@
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>136</v>
+        <v>270</v>
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
@@ -2701,16 +2693,12 @@
         </is>
       </c>
       <c r="I51" s="35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J51" s="30" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="J51" s="30" t="n"/>
       <c r="K51" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
       <c r="M51">
@@ -2724,11 +2712,11 @@
       </c>
       <c r="C52" s="31" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>Cobalt Point</t>
         </is>
       </c>
       <c r="D52" s="32" t="n">
-        <v>60</v>
+        <v>264</v>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
@@ -2743,11 +2731,11 @@
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
-          <t>Peak Capital Investments Llc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I52" s="35" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J52" s="30" t="inlineStr">
         <is>
@@ -2756,7 +2744,7 @@
       </c>
       <c r="K52" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M52">
@@ -2764,8 +2752,234 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="B53" s="30" t="n">
+        <v>42</v>
+      </c>
+      <c r="C53" s="31" t="inlineStr">
+        <is>
+          <t>Rolling Hill (Assemble Management)</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="n">
+        <v>200</v>
+      </c>
+      <c r="E53" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F53" s="33" t="n"/>
+      <c r="G53" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="30" t="n"/>
+      <c r="K53" s="31" t="inlineStr">
+        <is>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M53">
+        <f>IFERROR(VALUE(RIGHT(E53,4))*4+MATCH(LEFT(E53,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="30" t="n">
+        <v>43</v>
+      </c>
+      <c r="C54" s="31" t="inlineStr">
+        <is>
+          <t>12548 West Overland Road</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="n">
+        <v>156</v>
+      </c>
+      <c r="E54" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F54" s="33" t="n"/>
+      <c r="G54" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J54" s="30" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K54" s="31" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M54">
+        <f>IFERROR(VALUE(RIGHT(E54,4))*4+MATCH(LEFT(E54,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="55">
-      <c r="B55" s="36" t="inlineStr">
+      <c r="B55" s="30" t="n">
+        <v>44</v>
+      </c>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>Fairview</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="n">
+        <v>150</v>
+      </c>
+      <c r="E55" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F55" s="33" t="n"/>
+      <c r="G55" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J55" s="30" t="inlineStr">
+        <is>
+          <t>Townhome</t>
+        </is>
+      </c>
+      <c r="K55" s="31" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M55">
+        <f>IFERROR(VALUE(RIGHT(E55,4))*4+MATCH(LEFT(E55,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="30" t="n">
+        <v>45</v>
+      </c>
+      <c r="C56" s="31" t="inlineStr">
+        <is>
+          <t>The Cole Denton</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="n">
+        <v>136</v>
+      </c>
+      <c r="E56" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F56" s="33" t="n"/>
+      <c r="G56" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J56" s="30" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K56" s="31" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M56">
+        <f>IFERROR(VALUE(RIGHT(E56,4))*4+MATCH(LEFT(E56,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="30" t="n">
+        <v>46</v>
+      </c>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>Meridian OZ Apartments</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="E57" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F57" s="33" t="n"/>
+      <c r="G57" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="31" t="inlineStr">
+        <is>
+          <t>Peak Capital Investments Llc</t>
+        </is>
+      </c>
+      <c r="I57" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J57" s="30" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K57" s="31" t="inlineStr">
+        <is>
+          <t>Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M57">
+        <f>IFERROR(VALUE(RIGHT(E57,4))*4+MATCH(LEFT(E57,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="36" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Rent ($) = HelloData mix-weighted asking where covered, else market asking (CoStar). Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
@@ -2775,11 +2989,11 @@
   <mergeCells count="7">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C42:K42"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C28:K28"/>
-    <mergeCell ref="B55:K55"/>
-    <mergeCell ref="C39:K39"/>
     <mergeCell ref="C35:K35"/>
+    <mergeCell ref="B60:K60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2896,15 +3110,15 @@
         </is>
       </c>
       <c r="R5" s="43">
-        <f>'Competitive Analysis'!C37</f>
+        <f>'Competitive Analysis'!C39</f>
         <v/>
       </c>
       <c r="S5" s="44">
-        <f>'Competitive Analysis'!D37</f>
+        <f>'Competitive Analysis'!D39</f>
         <v/>
       </c>
       <c r="T5" s="45">
-        <f>'Competitive Analysis'!E37</f>
+        <f>'Competitive Analysis'!E39</f>
         <v/>
       </c>
       <c r="V5">
@@ -2926,15 +3140,15 @@
         <v>0.95</v>
       </c>
       <c r="R6" s="43">
-        <f>'Competitive Analysis'!C36</f>
+        <f>'Competitive Analysis'!C40</f>
         <v/>
       </c>
       <c r="S6" s="44">
-        <f>'Competitive Analysis'!D36</f>
+        <f>'Competitive Analysis'!D40</f>
         <v/>
       </c>
       <c r="T6" s="45">
-        <f>'Competitive Analysis'!E36</f>
+        <f>'Competitive Analysis'!E40</f>
         <v/>
       </c>
       <c r="V6">
@@ -2957,6 +3171,26 @@
           <t>Base</t>
         </is>
       </c>
+      <c r="R7" s="43">
+        <f>'Competitive Analysis'!C37</f>
+        <v/>
+      </c>
+      <c r="S7" s="44">
+        <f>'Competitive Analysis'!D37</f>
+        <v/>
+      </c>
+      <c r="T7" s="45">
+        <f>'Competitive Analysis'!E37</f>
+        <v/>
+      </c>
+      <c r="V7">
+        <f>IFERROR(VALUE(RIGHT(T7,4))*4+MATCH(LEFT(T7,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W7">
+        <f>IF(V7="","",IF(V7&lt;=$Z$1,0,MAX(1,INT((V7-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="14.4" customHeight="1">
       <c r="B8" s="38" t="inlineStr">
@@ -2967,10 +3201,25 @@
       <c r="C8" s="47" t="n">
         <v>425</v>
       </c>
-      <c r="R8" s="37" t="inlineStr">
-        <is>
-          <t>PROPOSED PIPELINE (scenario toggle)</t>
-        </is>
+      <c r="R8" s="43">
+        <f>'Competitive Analysis'!C36</f>
+        <v/>
+      </c>
+      <c r="S8" s="44">
+        <f>'Competitive Analysis'!D36</f>
+        <v/>
+      </c>
+      <c r="T8" s="45">
+        <f>'Competitive Analysis'!E36</f>
+        <v/>
+      </c>
+      <c r="V8">
+        <f>IFERROR(VALUE(RIGHT(T8,4))*4+MATCH(LEFT(T8,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W8">
+        <f>IF(V8="","",IF(V8&lt;=$Z$1,0,MAX(1,INT((V8-$Z$2)/4)+1)))</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="14.4" customHeight="1">
@@ -2982,25 +3231,25 @@
       <c r="C9" s="47" t="n">
         <v>850</v>
       </c>
-      <c r="R9" s="41" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="S9" s="41" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="T9" s="41" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="U9" s="41" t="inlineStr">
-        <is>
-          <t>Built In</t>
-        </is>
+      <c r="R9" s="43">
+        <f>'Competitive Analysis'!C38</f>
+        <v/>
+      </c>
+      <c r="S9" s="44">
+        <f>'Competitive Analysis'!D38</f>
+        <v/>
+      </c>
+      <c r="T9" s="45">
+        <f>'Competitive Analysis'!E38</f>
+        <v/>
+      </c>
+      <c r="V9">
+        <f>IFERROR(VALUE(RIGHT(T9,4))*4+MATCH(LEFT(T9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W9">
+        <f>IF(V9="","",IF(V9&lt;=$Z$1,0,MAX(1,INT((V9-$Z$2)/4)+1)))</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="14.4" customHeight="1">
@@ -3017,32 +3266,6 @@
           <t>◂ Base = trailing-3-yr CoStar average (annualized, complete quarters).</t>
         </is>
       </c>
-      <c r="R10" s="43" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="S10" s="44" t="n">
-        <v>472</v>
-      </c>
-      <c r="T10" s="48" t="inlineStr"/>
-      <c r="U10" s="48" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V10">
-        <f>IFERROR(VALUE(RIGHT(T10,4))*4+MATCH(LEFT(T10,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W10">
-        <f>IF(V10="","",IF(V10&lt;=$Z$1,0,MAX(1,INT((V10-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>IF(U10="All",1,IF(U10="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U10="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
-        <v/>
-      </c>
     </row>
     <row r="11" ht="14.4" customHeight="1">
       <c r="B11" s="38" t="inlineStr">
@@ -3050,84 +3273,49 @@
           <t>Selected Annual Demand</t>
         </is>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="48">
         <f>IF($C$7="Bear",$C$8,IF($C$7="Bull",$C$10,$C$9))</f>
         <v/>
       </c>
-      <c r="R11" s="43" t="inlineStr">
-        <is>
-          <t>The Gateway at Ten Mile</t>
-        </is>
-      </c>
-      <c r="S11" s="44" t="n">
-        <v>390</v>
-      </c>
-      <c r="T11" s="48" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
-      <c r="U11" s="48" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V11">
-        <f>IFERROR(VALUE(RIGHT(T11,4))*4+MATCH(LEFT(T11,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W11">
-        <f>IF(V11="","",IF(V11&lt;=$Z$1,0,MAX(1,INT((V11-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>IF(U11="All",1,IF(U11="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U11="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
-        <v/>
+      <c r="R11" s="37" t="inlineStr">
+        <is>
+          <t>PROPOSED PIPELINE (scenario toggle)</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="14.4" customHeight="1">
-      <c r="R12" s="43" t="inlineStr">
-        <is>
-          <t>Union 93</t>
-        </is>
-      </c>
-      <c r="S12" s="44" t="n">
-        <v>350</v>
-      </c>
-      <c r="T12" s="48" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
-      <c r="U12" s="48" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V12">
-        <f>IFERROR(VALUE(RIGHT(T12,4))*4+MATCH(LEFT(T12,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W12">
-        <f>IF(V12="","",IF(V12&lt;=$Z$1,0,MAX(1,INT((V12-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>IF(U12="All",1,IF(U12="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U12="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
-        <v/>
+      <c r="R12" s="41" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S12" s="41" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T12" s="41" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="U12" s="41" t="inlineStr">
+        <is>
+          <t>Built In</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="14.4" customHeight="1">
       <c r="R13" s="43" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="S13" s="44" t="n">
-        <v>322</v>
-      </c>
-      <c r="T13" s="48" t="inlineStr"/>
-      <c r="U13" s="48" t="inlineStr">
+        <v>472</v>
+      </c>
+      <c r="T13" s="49" t="inlineStr"/>
+      <c r="U13" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3148,18 +3336,18 @@
     <row r="14" ht="14.4" customHeight="1">
       <c r="R14" s="43" t="inlineStr">
         <is>
-          <t>Victory Flats</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="S14" s="44" t="n">
-        <v>301</v>
-      </c>
-      <c r="T14" s="48" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U14" s="48" t="inlineStr">
+        <v>390</v>
+      </c>
+      <c r="T14" s="49" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
+      </c>
+      <c r="U14" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3180,14 +3368,18 @@
     <row r="15" ht="14.4" customHeight="1">
       <c r="R15" s="43" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>Union 93</t>
         </is>
       </c>
       <c r="S15" s="44" t="n">
-        <v>275</v>
-      </c>
-      <c r="T15" s="48" t="inlineStr"/>
-      <c r="U15" s="48" t="inlineStr">
+        <v>350</v>
+      </c>
+      <c r="T15" s="49" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="U15" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3208,14 +3400,14 @@
     <row r="16" ht="14.4" customHeight="1">
       <c r="R16" s="43" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="S16" s="44" t="n">
-        <v>264</v>
-      </c>
-      <c r="T16" s="48" t="inlineStr"/>
-      <c r="U16" s="48" t="inlineStr">
+        <v>322</v>
+      </c>
+      <c r="T16" s="49" t="inlineStr"/>
+      <c r="U16" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3306,18 +3498,18 @@
       </c>
       <c r="R17" s="43" t="inlineStr">
         <is>
-          <t>The Judy (Maple Grove &amp; Overland)</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="S17" s="44" t="n">
-        <v>162</v>
-      </c>
-      <c r="T17" s="48" t="inlineStr">
-        <is>
-          <t>Q1 2028</t>
-        </is>
-      </c>
-      <c r="U17" s="48" t="inlineStr">
+        <v>301</v>
+      </c>
+      <c r="T17" s="49" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U17" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3397,14 +3589,14 @@
       </c>
       <c r="R18" s="43" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="S18" s="44" t="n">
-        <v>156</v>
-      </c>
-      <c r="T18" s="48" t="inlineStr"/>
-      <c r="U18" s="48" t="inlineStr">
+        <v>275</v>
+      </c>
+      <c r="T18" s="49" t="inlineStr"/>
+      <c r="U18" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3447,43 +3639,43 @@
         <v>450</v>
       </c>
       <c r="I19" s="52">
-        <f>SUMIFS('Competitive Analysis'!$D$5:$D$52,'Competitive Analysis'!$M$5:$M$52,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$52,"&lt;="&amp;8105)</f>
+        <f>SUMIFS('Competitive Analysis'!$D$5:$D$57,'Competitive Analysis'!$M$5:$M$57,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$57,"&lt;="&amp;8105)</f>
         <v/>
       </c>
       <c r="J19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,1)+SUMIFS($S$10:$S$22,$W$10:$W$22,1,$X$10:$X$22,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,1)+SUMIFS($S$13:$S$27,$W$13:$W$27,1,$X$13:$X$27,1)</f>
         <v/>
       </c>
       <c r="K19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,2)+SUMIFS($S$10:$S$22,$W$10:$W$22,2,$X$10:$X$22,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,2)+SUMIFS($S$13:$S$27,$W$13:$W$27,2,$X$13:$X$27,1)</f>
         <v/>
       </c>
       <c r="L19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,3)+SUMIFS($S$10:$S$22,$W$10:$W$22,3,$X$10:$X$22,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,3)+SUMIFS($S$13:$S$27,$W$13:$W$27,3,$X$13:$X$27,1)</f>
         <v/>
       </c>
       <c r="M19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,4)+SUMIFS($S$10:$S$22,$W$10:$W$22,4,$X$10:$X$22,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,4)+SUMIFS($S$13:$S$27,$W$13:$W$27,4,$X$13:$X$27,1)</f>
         <v/>
       </c>
       <c r="N19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,5)+SUMIFS($S$10:$S$22,$W$10:$W$22,5,$X$10:$X$22,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,5)+SUMIFS($S$13:$S$27,$W$13:$W$27,5,$X$13:$X$27,1)</f>
         <v/>
       </c>
       <c r="O19" s="53">
-        <f>SUMIFS($S$5:$S$6,$W$5:$W$6,6)+SUMIFS($S$10:$S$22,$W$10:$W$22,6,$X$10:$X$22,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,6)+SUMIFS($S$13:$S$27,$W$13:$W$27,6,$X$13:$X$27,1)</f>
         <v/>
       </c>
       <c r="R19" s="43" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
         </is>
       </c>
       <c r="S19" s="44" t="n">
-        <v>150</v>
-      </c>
-      <c r="T19" s="48" t="inlineStr"/>
-      <c r="U19" s="48" t="inlineStr">
+        <v>270</v>
+      </c>
+      <c r="T19" s="49" t="inlineStr"/>
+      <c r="U19" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3554,18 +3746,14 @@
       </c>
       <c r="R20" s="43" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>Cobalt Point</t>
         </is>
       </c>
       <c r="S20" s="44" t="n">
-        <v>138</v>
-      </c>
-      <c r="T20" s="48" t="inlineStr">
-        <is>
-          <t>Q1 2029</t>
-        </is>
-      </c>
-      <c r="U20" s="48" t="inlineStr">
+        <v>264</v>
+      </c>
+      <c r="T20" s="49" t="inlineStr"/>
+      <c r="U20" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3637,14 +3825,14 @@
       </c>
       <c r="R21" s="43" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Rolling Hill (Assemble Management)</t>
         </is>
       </c>
       <c r="S21" s="44" t="n">
-        <v>136</v>
-      </c>
-      <c r="T21" s="48" t="inlineStr"/>
-      <c r="U21" s="48" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="T21" s="49" t="inlineStr"/>
+      <c r="U21" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3670,14 +3858,18 @@
       </c>
       <c r="R22" s="43" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
         </is>
       </c>
       <c r="S22" s="44" t="n">
-        <v>60</v>
-      </c>
-      <c r="T22" s="48" t="inlineStr"/>
-      <c r="U22" s="48" t="inlineStr">
+        <v>162</v>
+      </c>
+      <c r="T22" s="49" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="U22" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -3745,6 +3937,32 @@
       </c>
       <c r="O23" s="57">
         <f>IFERROR('Cash Flow (Annual)'!$P$4,"")</f>
+        <v/>
+      </c>
+      <c r="R23" s="43" t="inlineStr">
+        <is>
+          <t>12548 West Overland Road</t>
+        </is>
+      </c>
+      <c r="S23" s="44" t="n">
+        <v>156</v>
+      </c>
+      <c r="T23" s="49" t="inlineStr"/>
+      <c r="U23" s="49" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V23">
+        <f>IFERROR(VALUE(RIGHT(T23,4))*4+MATCH(LEFT(T23,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W23">
+        <f>IF(V23="","",IF(V23&lt;=$Z$1,0,MAX(1,INT((V23-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>IF(U23="All",1,IF(U23="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U23="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
         <v/>
       </c>
     </row>
@@ -3803,6 +4021,32 @@
         <f>IFERROR(O23/N23-1,"")</f>
         <v/>
       </c>
+      <c r="R24" s="43" t="inlineStr">
+        <is>
+          <t>Fairview</t>
+        </is>
+      </c>
+      <c r="S24" s="44" t="n">
+        <v>150</v>
+      </c>
+      <c r="T24" s="49" t="inlineStr"/>
+      <c r="U24" s="49" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V24">
+        <f>IFERROR(VALUE(RIGHT(T24,4))*4+MATCH(LEFT(T24,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W24">
+        <f>IF(V24="","",IF(V24&lt;=$Z$1,0,MAX(1,INT((V24-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>IF(U24="All",1,IF(U24="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U24="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="14.4" customHeight="1">
       <c r="B25" s="38" t="inlineStr">
@@ -3854,6 +4098,36 @@
       </c>
       <c r="O25" s="57">
         <f>IFERROR('Cash Flow (Annual)'!$P$5,"")</f>
+        <v/>
+      </c>
+      <c r="R25" s="43" t="inlineStr">
+        <is>
+          <t>Ascent Overland</t>
+        </is>
+      </c>
+      <c r="S25" s="44" t="n">
+        <v>138</v>
+      </c>
+      <c r="T25" s="49" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
+      <c r="U25" s="49" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V25">
+        <f>IFERROR(VALUE(RIGHT(T25,4))*4+MATCH(LEFT(T25,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W25">
+        <f>IF(V25="","",IF(V25&lt;=$Z$1,0,MAX(1,INT((V25-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>IF(U25="All",1,IF(U25="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U25="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
         <v/>
       </c>
     </row>
@@ -3910,6 +4184,32 @@
       </c>
       <c r="O26" s="60">
         <f>IFERROR(O25/N25-1,"")</f>
+        <v/>
+      </c>
+      <c r="R26" s="43" t="inlineStr">
+        <is>
+          <t>The Cole Denton</t>
+        </is>
+      </c>
+      <c r="S26" s="44" t="n">
+        <v>136</v>
+      </c>
+      <c r="T26" s="49" t="inlineStr"/>
+      <c r="U26" s="49" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V26">
+        <f>IFERROR(VALUE(RIGHT(T26,4))*4+MATCH(LEFT(T26,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W26">
+        <f>IF(V26="","",IF(V26&lt;=$Z$1,0,MAX(1,INT((V26-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>IF(U26="All",1,IF(U26="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U26="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
         <v/>
       </c>
     </row>
@@ -3953,6 +4253,32 @@
       </c>
       <c r="O27" s="62">
         <f>IFERROR('Cash Flow (Annual)'!$P$14,"")</f>
+        <v/>
+      </c>
+      <c r="R27" s="43" t="inlineStr">
+        <is>
+          <t>Meridian OZ Apartments</t>
+        </is>
+      </c>
+      <c r="S27" s="44" t="n">
+        <v>60</v>
+      </c>
+      <c r="T27" s="49" t="inlineStr"/>
+      <c r="U27" s="49" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V27">
+        <f>IFERROR(VALUE(RIGHT(T27,4))*4+MATCH(LEFT(T27,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W27">
+        <f>IF(V27="","",IF(V27&lt;=$Z$1,0,MAX(1,INT((V27-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>IF(U27="All",1,IF(U27="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U27="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
         <v/>
       </c>
     </row>
@@ -4957,7 +5283,7 @@
       </c>
       <c r="E68" s="79" t="inlineStr">
         <is>
-          <t>716 / 552</t>
+          <t>1,213 / 552</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5346,7 @@
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bear only,Bear+Base,All,None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5034,7 +5360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6615,23 +6941,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>South Ridge II</t>
+          <t>Centrepoint</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1703 S Grand Frk Wy</t>
+          <t>3100 N Centrepoint Way</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>164</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2027</v>
+        <v>213</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -6651,33 +6974,34 @@
           <t>RealPage</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: under construction - revived; permits issuing 2026</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>Dorado Station</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11101 W Overland Rd</t>
+          <t>1500 N Eldorado St, Boise 83704</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>138</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2028</v>
+        <v>212</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Q1 2029</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
       <c r="H30" s="81" t="n"/>
@@ -6689,40 +7013,37 @@
       <c r="N30" s="82" t="n"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>The Gateway at Ten Mile</t>
+          <t>Summertown (remaining phases)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2954 W Franklin Rd</t>
+          <t>3005 N Ridgebury Ln, Meridian 83646</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>390</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2027</v>
+        <v>72</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
       <c r="H31" s="81" t="n"/>
@@ -6734,40 +7055,40 @@
       <c r="N31" s="82" t="n"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Victory Flats</t>
+          <t>South Ridge II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8373 West Victory Rd</t>
+          <t>1703 S Grand Frk Wy</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="D32" t="n">
         <v>2027</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
       <c r="H32" s="81" t="n"/>
@@ -6779,32 +7100,31 @@
       <c r="N32" s="82" t="n"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Diligence: proposed</t>
-        </is>
-      </c>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>The Judy (Maple Grove &amp; Overland)</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1770 S Maple Grove Rd, Boise 83704</t>
+          <t>11101 W Overland Rd</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>162</v>
+        <v>138</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2028</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -6821,35 +7141,35 @@
       <c r="N33" s="82" t="n"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Diligence</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Union 93</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>221-225 E Broadway Ave</t>
+          <t>2954 W Franklin Rd</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="D34" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Q3 2026</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -6866,28 +7186,36 @@
       <c r="N34" s="82" t="n"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1475 E Franklin Rd</t>
+          <t>8373 West Victory Rd</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>60</v>
+        <v>301</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -6915,16 +7243,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>580 N Cole Rd</t>
+          <t>1770 S Maple Grove Rd, Boise 83704</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>136</v>
+        <v>162</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -6940,28 +7273,36 @@
       <c r="N36" s="82" t="n"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Union 93</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>E Fairview Ave &amp; N Records Way</t>
+          <t>221-225 E Broadway Ave</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>472</v>
+        <v>350</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6977,28 +7318,28 @@
       <c r="N37" s="82" t="n"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>Meridian OZ Apartments</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S Cobalt Point Way &amp; E Copper Point Dr</t>
+          <t>1475 E Franklin Rd</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>264</v>
+        <v>60</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -7014,28 +7355,28 @@
       <c r="N38" s="82" t="n"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1005 E Fairview Ave</t>
+          <t>580 N Cole Rd</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -7047,12 +7388,8 @@
       <c r="J39" s="81" t="n"/>
       <c r="K39" s="82" t="n"/>
       <c r="L39" s="82" t="n"/>
-      <c r="M39" s="82" t="n">
-        <v>1837.580964685616</v>
-      </c>
-      <c r="N39" s="82" t="n">
-        <v>1837.580964685616</v>
-      </c>
+      <c r="M39" s="82" t="n"/>
+      <c r="N39" s="82" t="n"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7067,16 +7404,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12548 W Overland Rd</t>
+          <t>E Fairview Ave &amp; N Records Way</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>156</v>
+        <v>472</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -7104,16 +7441,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>Cobalt Point</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12565 W Fairview Ave</t>
+          <t>S Cobalt Point Way &amp; E Copper Point Dr</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -7141,16 +7478,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amity Ave &amp; Meridian Rd</t>
+          <t>1005 E Fairview Ave</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>322</v>
+        <v>150</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -7162,8 +7499,12 @@
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="82" t="n"/>
       <c r="L42" s="82" t="n"/>
-      <c r="M42" s="82" t="n"/>
-      <c r="N42" s="82" t="n"/>
+      <c r="M42" s="82" t="n">
+        <v>1837.580964685616</v>
+      </c>
+      <c r="N42" s="82" t="n">
+        <v>1837.580964685616</v>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7172,6 +7513,191 @@
       <c r="P42" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12548 West Overland Road</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>12548 W Overland Rd</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>156</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H43" s="81" t="n"/>
+      <c r="I43" s="81" t="n"/>
+      <c r="J43" s="81" t="n"/>
+      <c r="K43" s="82" t="n"/>
+      <c r="L43" s="82" t="n"/>
+      <c r="M43" s="82" t="n"/>
+      <c r="N43" s="82" t="n"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12565 West Fairview Avenue</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12565 W Fairview Ave</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>275</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H44" s="81" t="n"/>
+      <c r="I44" s="81" t="n"/>
+      <c r="J44" s="81" t="n"/>
+      <c r="K44" s="82" t="n"/>
+      <c r="L44" s="82" t="n"/>
+      <c r="M44" s="82" t="n"/>
+      <c r="N44" s="82" t="n"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Syringa Crossing</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Amity Ave &amp; Meridian Rd</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>322</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H45" s="81" t="n"/>
+      <c r="I45" s="81" t="n"/>
+      <c r="J45" s="81" t="n"/>
+      <c r="K45" s="82" t="n"/>
+      <c r="L45" s="82" t="n"/>
+      <c r="M45" s="82" t="n"/>
+      <c r="N45" s="82" t="n"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Rolling Hill (Assemble Management)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4270 E Overland Rd, Meridian 83642</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>200</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H46" s="81" t="n"/>
+      <c r="I46" s="81" t="n"/>
+      <c r="J46" s="81" t="n"/>
+      <c r="K46" s="82" t="n"/>
+      <c r="L46" s="82" t="n"/>
+      <c r="M46" s="82" t="n"/>
+      <c r="N46" s="82" t="n"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Diligence</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>E Pine Ave &amp; N Webb Way, Meridian 83642</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>270</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H47" s="81" t="n"/>
+      <c r="I47" s="81" t="n"/>
+      <c r="J47" s="81" t="n"/>
+      <c r="K47" s="82" t="n"/>
+      <c r="L47" s="82" t="n"/>
+      <c r="M47" s="82" t="n"/>
+      <c r="N47" s="82" t="n"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Diligence</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -7303,22 +7829,30 @@
           <t>Centrepoint</t>
         </is>
       </c>
-      <c r="C6" s="84" t="n"/>
-      <c r="D6" s="84" t="n"/>
+      <c r="C6" s="84" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D6" s="84" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
       <c r="E6" s="43" t="inlineStr">
         <is>
-          <t>withdrawn - entitlements terminated (financing)</t>
+          <t>under construction - revived; permits issuing 2026</t>
         </is>
       </c>
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>A 2024 CUP/DA modification approved a 239-unit deed-restricted affordable/workforce development at Centrepoint Way near Eagle &amp; Ustick (earlier iterations 215-295 units), but per the Meridian staff report the applicant terminated entitlements and withdrew due to state-level financing complications — dead. Its parcel (S1105110111) reverts to latent land-use supply.</t>
+          <t>AUDIT CORRECTION (July 2026): previously marked withdrawn per 2024 reporting, but the project was revived — Meridian's June 2026 permit report shows C-MULTI-2026-0007 (Bldg C, 56u) ISSUED 6/25/2026; 213 units in 5 buildings at N Centrepoint Way south of Ustick (Rockefeller; workforce/affordable positioning). Phased delivery est. from permit timing.</t>
         </is>
       </c>
       <c r="H6" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2024/05/30/centrepoint-apartments-meridian-village/</t>
+          <t>https://meridiancity.org/media/f5alu5zs/bldgmonthlypermits.pdf</t>
         </is>
       </c>
     </row>
@@ -7845,213 +8379,450 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>Rolling Hill (Assemble Management)</t>
+        </is>
+      </c>
+      <c r="C26" s="84" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="43" t="inlineStr">
+        <is>
+          <t>AUDIT FIND (July 2026): annexation + DA APPROVED 5-1 on 5/19/2026 (after a 2024 denial of the 154u version) — 200 units in 3-story buildings + ~19.5k sf ground-floor commercial at NE corner Overland Rd &amp; Rolling Hill Dr (4270 E Overland), ~1.0 mi from subject. CA developer; no permits yet; in NEITHER CoStar nor RealPage.</t>
+        </is>
+      </c>
+      <c r="H26" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2026/05/20/ready-for-its-next-phase-meridian-approves-project-bringing-something-new-to-overland-rd/</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="B27" s="83" t="inlineStr">
-        <is>
-          <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
+        </is>
+      </c>
+      <c r="C27" s="84" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D27" s="84" t="n"/>
+      <c r="E27" s="43" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="43" t="inlineStr">
+        <is>
+          <t>AUDIT FIND: CUP H-2024-0071 APPROVED 10/21/2025 — 270 conventional MF units in two buildings (6.28 ac C-G, 76-ft height) at E Pine Ave &amp; N Webb Way; master plan allows up to 904 units + hotel over 10-12 yrs. 2-yr CUP commencement clock; groundbreak &gt;=2027. Distinct from the existing 25u 'Pine 43' comp. Not in CoStar/RealPage.</t>
+        </is>
+      </c>
+      <c r="H27" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/10/22/large-urban-project-gets-green-light-from-meridian-city-council/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="50" t="inlineStr">
-        <is>
-          <t>Property / Site</t>
-        </is>
-      </c>
-      <c r="C28" s="50" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D28" s="50" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="E28" s="50" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F28" s="50" t="inlineStr">
-        <is>
-          <t>Leasing Pace</t>
-        </is>
-      </c>
-      <c r="G28" s="50" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="H28" s="50" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>Dorado Station</t>
+        </is>
+      </c>
+      <c r="C28" s="84" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D28" s="84" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="E28" s="43" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="43" t="inlineStr">
+        <is>
+          <t>AUDIT FIND: J. Fisher Companies 6-story, 100% income-restricted (50-80% AMI, incl. 21 Our Path Home units), $70M, broke ground Oct 2025 at 1500 N Eldorado St (west Boise bench) — 4.9 mi from subject, just inside the ring. Delivery targeted summer 2027. Affordable positioning limits direct rent competition but adds ring supply. Classic CoStar/RealPage-invisible affordable deal.</t>
+        </is>
+      </c>
+      <c r="H28" s="43" t="inlineStr">
+        <is>
+          <t>https://www.cityofboise.org/news/planning-and-development-services/2025/october/dorado-station-apartments-celebrate-groundbreaking/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="43" t="inlineStr">
         <is>
-          <t>Emblem Meridian (Quarterra) / Artisan Victory Market site</t>
+          <t>Summertown (remaining phases)</t>
         </is>
       </c>
       <c r="C29" s="84" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="D29" s="84" t="n"/>
-      <c r="E29" s="43" t="n"/>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D29" s="84" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="E29" s="43" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
       <c r="F29" s="43" t="n"/>
       <c r="G29" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-76: ~12-ac BPS Eagle Road LLC assemblage on S Eagle Rd. 'Artisan Victory Market' (H-2022-0066) approved 2023 for 131 build-to-rent units + commercial but never built; superseded by Quarterra's 'Emblem Meridian' ~250-unit concept (pre-application June 2026). Closest large latent MF site to the subject (~1 mi).</t>
+          <t>AUDIT FIND: Shannon Robnett Industries' 191-unit phased garden/rowhouse community at Ustick &amp; Venable (~3.5 mi); early buildings already leasing but THREE new 24-plex permits issued June 2026 (C-MULTI-2025-0016/-0022/-0023, incl. 3005 N Ridgebury Ln) = 72 units of fresh supply. Not in CoStar/RealPage; verify delivered-vs-remaining split against next vendor pull.</t>
         </is>
       </c>
       <c r="H29" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2026/06/10/meridian-emblem-victory-eagle-homes-apartment/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="43" t="inlineStr">
-        <is>
-          <t>Tanner Creek apartments (Waltman/Johnson Ln)</t>
-        </is>
-      </c>
-      <c r="C30" s="84" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="D30" s="84" t="n"/>
-      <c r="E30" s="43" t="n"/>
-      <c r="F30" s="43" t="n"/>
-      <c r="G30" s="43" t="inlineStr">
-        <is>
-          <t>Land-use analysis site SM-15: Tanner Creek (heard Nov 2023; moved forward) — 83 SF homes + 45 townhomes + 280 phased apartments on ~38 ac, paired with ~30-ac Hawkins commercial between I-84 and Waltman Ln. Residential now being built by CBH Homes; the 280-unit apartment component is latent supply not yet in the CoStar/RealPage pipeline.</t>
-        </is>
-      </c>
-      <c r="H30" s="43" t="inlineStr">
-        <is>
-          <t>https://boisedev.com/news/2023/11/28/plans-for-two-large-developments-off-i-84-and-meridian-rd-move-forward/</t>
+          <t>https://meridiancity.org/media/f5alu5zs/bldgmonthlypermits.pdf</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="43" t="inlineStr">
-        <is>
-          <t>Graycliff Estates R-40 block</t>
-        </is>
-      </c>
-      <c r="C31" s="84" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="D31" s="84" t="n"/>
-      <c r="E31" s="43" t="n"/>
-      <c r="F31" s="43" t="n"/>
-      <c r="G31" s="43" t="inlineStr">
-        <is>
-          <t>Land-use analysis site SM-3: Graycliff Estates (Star Development) approved preliminary plat of ~200 SF homes PLUS 224 apartments (R-40 high-density block) on ~52 ac; SF portion building since 2021. The 224-unit apartment block remains unbuilt latent supply.</t>
-        </is>
-      </c>
-      <c r="H31" s="43" t="inlineStr">
-        <is>
-          <t>https://www.weknowboise.com/graycliff-estates.php</t>
+      <c r="B31" s="83" t="inlineStr">
+        <is>
+          <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="43" t="inlineStr">
-        <is>
-          <t>Touchmark Meadow Lake Village expansion</t>
-        </is>
-      </c>
-      <c r="C32" s="84" t="n"/>
-      <c r="D32" s="84" t="n"/>
-      <c r="E32" s="43" t="n"/>
-      <c r="F32" s="43" t="n"/>
-      <c r="G32" s="43" t="inlineStr">
-        <is>
-          <t>Land-use analysis site SM-9: ~64 undeveloped ac of Touchmark's ~121-ac senior community. July 2025 development-modification agreement + rezone + PUD in progress to a broader 'Touchmark Mixed Use' (mixed housing types). Senior-oriented, but adds rental housing capacity 1.5 mi from subject.</t>
-        </is>
-      </c>
-      <c r="H32" s="43" t="inlineStr">
-        <is>
-          <t>https://boisedev.com/news/2025/07/14/touchmark-meridian-meadowlake-mixed-use/</t>
+      <c r="B32" s="50" t="inlineStr">
+        <is>
+          <t>Property / Site</t>
+        </is>
+      </c>
+      <c r="C32" s="50" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D32" s="50" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="E32" s="50" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F32" s="50" t="inlineStr">
+        <is>
+          <t>Leasing Pace</t>
+        </is>
+      </c>
+      <c r="G32" s="50" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="H32" s="50" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="43" t="inlineStr">
         <is>
-          <t>Ten Mile Crossing residual HDR parcels</t>
-        </is>
-      </c>
-      <c r="C33" s="84" t="n"/>
+          <t>Emblem Meridian (Quarterra) / Artisan Victory Market site</t>
+        </is>
+      </c>
+      <c r="C33" s="84" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
       <c r="D33" s="84" t="n"/>
       <c r="E33" s="43" t="n"/>
       <c r="F33" s="43" t="n"/>
       <c r="G33" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-4: residential portion (R-15/R-8) of Brighton's Ten Mile Crossing at SW Overland &amp; Ten Mile — partially built (Cortland South Meridian + CBH SF); remaining High-Density Residential parcels planned/dormant, including an 8.6-ac and a 14.4-ac R-15 vacant parcel (highest-interest sites in the land-use ranking). Note: South Ridge II (164u UC, tracked in the chart) is rising in this same corridor.</t>
+          <t>Land-use analysis site SM-76: ~12-ac BPS Eagle Road LLC assemblage on S Eagle Rd. 'Artisan Victory Market' (H-2022-0066) approved 2023 for 131 build-to-rent units + commercial but never built; superseded by Quarterra's 'Emblem Meridian' ~250-unit concept (pre-application June 2026). Closest large latent MF site to the subject (~1 mi).</t>
         </is>
       </c>
       <c r="H33" s="43" t="inlineStr">
         <is>
-          <t>https://www.brighton.co/brighton-place/ten-mile-crossing/</t>
+          <t>https://boisedev.com/news/2026/06/10/meridian-emblem-victory-eagle-homes-apartment/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="43" t="inlineStr">
         <is>
-          <t>Brighton Apex R-15 parcel (Lake Hazel)</t>
-        </is>
-      </c>
-      <c r="C34" s="84" t="n"/>
+          <t>Tanner Creek apartments (Waltman/Johnson Ln)</t>
+        </is>
+      </c>
+      <c r="C34" s="84" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
       <c r="D34" s="84" t="n"/>
       <c r="E34" s="43" t="n"/>
       <c r="F34" s="43" t="n"/>
       <c r="G34" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-61: 15.1-ac R-15 (med-high-density) parcel on E Lake Hazel Rd inside Brighton's approved Apex/Pinnacle master-plan footprint; adjacent phases actively building. Latent MF-capable ground in the fast-growing S Meridian corridor.</t>
+          <t>Land-use analysis site SM-15: Tanner Creek (heard Nov 2023; moved forward) — 83 SF homes + 45 townhomes + 280 phased apartments on ~38 ac, paired with ~30-ac Hawkins commercial between I-84 and Waltman Ln. Residential now being built by CBH Homes; the 280-unit apartment component is latent supply not yet in the CoStar/RealPage pipeline.</t>
         </is>
       </c>
       <c r="H34" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2024/12/20/brighton-pinnacle-costco-meridian/</t>
+          <t>https://boisedev.com/news/2023/11/28/plans-for-two-large-developments-off-i-84-and-meridian-rd-move-forward/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="43" t="inlineStr">
         <is>
-          <t>Outer Banks Subdivision (TM Creek / Cobalt Dr)</t>
-        </is>
-      </c>
-      <c r="C35" s="84" t="n"/>
+          <t>Graycliff Estates R-40 block</t>
+        </is>
+      </c>
+      <c r="C35" s="84" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
       <c r="D35" s="84" t="n"/>
       <c r="E35" s="43" t="n"/>
       <c r="F35" s="43" t="n"/>
       <c r="G35" s="43" t="inlineStr">
         <is>
+          <t>Land-use analysis site SM-3: Graycliff Estates (Star Development) approved preliminary plat of ~200 SF homes PLUS 224 apartments (R-40 high-density block) on ~52 ac; SF portion building since 2021. The 224-unit apartment block remains unbuilt latent supply.</t>
+        </is>
+      </c>
+      <c r="H35" s="43" t="inlineStr">
+        <is>
+          <t>https://www.weknowboise.com/graycliff-estates.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="43" t="inlineStr">
+        <is>
+          <t>Touchmark Meadow Lake Village expansion</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="43" t="n"/>
+      <c r="F36" s="43" t="n"/>
+      <c r="G36" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-9: ~64 undeveloped ac of Touchmark's ~121-ac senior community. July 2025 development-modification agreement + rezone + PUD in progress to a broader 'Touchmark Mixed Use' (mixed housing types). Senior-oriented, but adds rental housing capacity 1.5 mi from subject.</t>
+        </is>
+      </c>
+      <c r="H36" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/07/14/touchmark-meridian-meadowlake-mixed-use/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>Ten Mile Crossing residual HDR parcels</t>
+        </is>
+      </c>
+      <c r="C37" s="84" t="n"/>
+      <c r="D37" s="84" t="n"/>
+      <c r="E37" s="43" t="n"/>
+      <c r="F37" s="43" t="n"/>
+      <c r="G37" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-4: residential portion (R-15/R-8) of Brighton's Ten Mile Crossing at SW Overland &amp; Ten Mile — partially built (Cortland South Meridian + CBH SF); remaining High-Density Residential parcels planned/dormant, including an 8.6-ac and a 14.4-ac R-15 vacant parcel (highest-interest sites in the land-use ranking). Note: South Ridge II (164u UC, tracked in the chart) is rising in this same corridor.</t>
+        </is>
+      </c>
+      <c r="H37" s="43" t="inlineStr">
+        <is>
+          <t>https://www.brighton.co/brighton-place/ten-mile-crossing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>Brighton Apex R-15 parcel (Lake Hazel)</t>
+        </is>
+      </c>
+      <c r="C38" s="84" t="n"/>
+      <c r="D38" s="84" t="n"/>
+      <c r="E38" s="43" t="n"/>
+      <c r="F38" s="43" t="n"/>
+      <c r="G38" s="43" t="inlineStr">
+        <is>
+          <t>Land-use analysis site SM-61: 15.1-ac R-15 (med-high-density) parcel on E Lake Hazel Rd inside Brighton's approved Apex/Pinnacle master-plan footprint; adjacent phases actively building. Latent MF-capable ground in the fast-growing S Meridian corridor.</t>
+        </is>
+      </c>
+      <c r="H38" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2024/12/20/brighton-pinnacle-costco-meridian/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>Outer Banks Subdivision (TM Creek / Cobalt Dr)</t>
+        </is>
+      </c>
+      <c r="C39" s="84" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="43" t="n"/>
+      <c r="F39" s="43" t="n"/>
+      <c r="G39" s="43" t="inlineStr">
+        <is>
           <t>Land-use analysis site SM-1: Ten Mile/I-84 high-density employment/mixed-use core (TMISAP) with heavy MF already delivered (Flats/Lofts/Cortland at Ten Mile). Outer Banks Subdivision approved 2021; balance of the ~198-ac district planned — further MF phases likely alongside the tracked pipeline.</t>
         </is>
       </c>
-      <c r="H35" s="43" t="inlineStr">
+      <c r="H39" s="43" t="inlineStr">
         <is>
           <t>https://boisedev.com/news/2021/12/17/outer-banks-pera-place/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>Grandview Communities (Lake Hazel &amp; Linder)</t>
+        </is>
+      </c>
+      <c r="C40" s="84" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="43" t="n"/>
+      <c r="F40" s="43" t="n"/>
+      <c r="G40" s="43" t="inlineStr">
+        <is>
+          <t>AUDIT WATCH: 79-ac pre-application (July 2025) at NE corner Lake Hazel &amp; Linder — ~510 homes incl. ~130 apartments + 176 TH/cluster; no formal H-file or hearing yet; sits near the southern ring edge (~4.5 mi).</t>
+        </is>
+      </c>
+      <c r="H40" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2025/07/07/hundreds-of-homes-apartments-planned-for-lake-hazel-and-linder/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Discovery project (Lake Hazel &amp; Locust Grove)</t>
+        </is>
+      </c>
+      <c r="C41" s="84" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="43" t="n"/>
+      <c r="F41" s="43" t="n"/>
+      <c r="G41" s="43" t="inlineStr">
+        <is>
+          <t>AUDIT WATCH: April 2024 pre-application for 200+ units (nine 3-story buildings + TH/SFR) on ~20 ac by Discovery Park; no formal application since — dormant but the land is teed up (~3.5 mi).</t>
+        </is>
+      </c>
+      <c r="H41" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2024/04/12/200-apartments-meridian-discovery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>709 N Cole Rd (city land trust)</t>
+        </is>
+      </c>
+      <c r="C42" s="84" t="n"/>
+      <c r="D42" s="84" t="n"/>
+      <c r="E42" s="43" t="n"/>
+      <c r="F42" s="43" t="n"/>
+      <c r="G42" s="43" t="inlineStr">
+        <is>
+          <t>AUDIT WATCH: City of Boise closing (July 2026) on 1.64 ac by Boise Towne Square for future affordable housing (prior owner proposed 71 micro-units in 2021); no developer or program yet — 2029+ speculative. Same parcel as the excluded 'Cole Road' RealPage entry.</t>
+        </is>
+      </c>
+      <c r="H42" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2026/06/01/709-cole-boise/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="43" t="inlineStr">
+        <is>
+          <t>Aren east phase (verify)</t>
+        </is>
+      </c>
+      <c r="C43" s="84" t="n"/>
+      <c r="D43" s="84" t="n"/>
+      <c r="E43" s="43" t="n"/>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="inlineStr">
+        <is>
+          <t>AUDIT WATCH: The Aren (396u, delivered 2024) was planned as two phases at Eagle View Landing; verify whether the east-phase (~200u) buildings are fully delivered within the tracked 396 or represent additional untracked pipeline.</t>
+        </is>
+      </c>
+      <c r="H43" s="43" t="inlineStr">
+        <is>
+          <t>https://arenmeridian.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>Murio Farms MF phases (SW Boise)</t>
+        </is>
+      </c>
+      <c r="C44" s="84" t="n"/>
+      <c r="D44" s="84" t="n"/>
+      <c r="E44" s="43" t="n"/>
+      <c r="F44" s="43" t="n"/>
+      <c r="G44" s="43" t="inlineStr">
+        <is>
+          <t>AUDIT WATCH: 380-ac, 3,500-home master plan approved 2024 between Maple Grove &amp; Cole at the New York Canal; apartments in later phases (15-20 yr buildout) — long-dated only.</t>
+        </is>
+      </c>
+      <c r="H44" s="43" t="inlineStr">
+        <is>
+          <t>https://www.ktvb.com/article/news/local/idaho-press/city-council-approves-murio-farms-3500-homes-southwest-boise/277-eb746dad-15bb-4c8e-868d-ca9d6c1e355e</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
+++ b/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M60"/>
+  <dimension ref="B2:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -902,7 +902,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>STABILIZED / STABILIZING (21 properties, 2,519 units)</t>
+          <t>STABILIZED / STABILIZING (22 properties, 2,879 units)</t>
         </is>
       </c>
     </row>
@@ -1792,94 +1792,94 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Springtree Apartments</t>
+          <t>★ Seasons at Meridian  (SUBJECT)</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>42</v>
+        <v>360</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Q4 2024</t>
+          <t>Q3 2024</t>
         </is>
       </c>
       <c r="F26" s="9" t="n">
-        <v>0.952381</v>
+        <v>0.955556</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>1514</v>
+        <v>1911.119099448338</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Commercial Northwest Property Management</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="I26" s="11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Low-Rise</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n"/>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Year built: 2024/2025; SUBJECT — this deal; Occ: CoStar 96% vs RealPage 99%</t>
+        </is>
+      </c>
       <c r="M26">
         <f>IFERROR(VALUE(RIGHT(E26,4))*4+MATCH(LEFT(E26,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="13" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Springtree Apartments</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>0.952381</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>1514</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Commercial Northwest Property Management</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Low-Rise</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="n"/>
+      <c r="M27">
+        <f>IFERROR(VALUE(RIGHT(E27,4))*4+MATCH(LEFT(E27,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>LEASING UP (5 properties, 815 units)</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>Village Apartments</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>336</v>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Q2 2024</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="n">
-        <v>0.119047619047619</v>
-      </c>
-      <c r="G29" s="18" t="n">
-        <v>1747.513661202186</v>
-      </c>
-      <c r="H29" s="15" t="inlineStr">
-        <is>
-          <t>Rockworth Companies</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K29" s="15" t="inlineStr">
-        <is>
-          <t>Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
-        </is>
-      </c>
-      <c r="M29">
-        <f>IFERROR(VALUE(RIGHT(E29,4))*4+MATCH(LEFT(E29,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -1888,11 +1888,11 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Wesley Apartments and Townhomes</t>
+          <t>Village Apartments</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>191</v>
+        <v>336</v>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
@@ -1900,27 +1900,27 @@
         </is>
       </c>
       <c r="F30" s="17" t="n">
-        <v>0.4764397905759162</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>1994.484728234728</v>
+        <v>1747.513661202186</v>
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Executive Management Services, LLC</t>
+          <t>Rockworth Companies</t>
         </is>
       </c>
       <c r="I30" s="19" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K30" s="15" t="inlineStr">
         <is>
-          <t>Occ: CoStar 28% vs RealPage 84%; Rent: CoStar ask $1,716 vs RealPage eff $2,004; Rent: HD mix-wtd $1,994 vs CoStar ask $1,716; Occ: HD ~48% (CoStar/RP showed 28%); HD (90d): occ ~48% (units leased), ~22 leases/mo</t>
+          <t>Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
         </is>
       </c>
       <c r="M30">
@@ -1934,41 +1934,39 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Shamrock Apartments</t>
+          <t>Wesley Apartments and Townhomes</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>0.833333</v>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.4764397905759162</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>1994.484728234728</v>
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>Dc Fairview Llc</t>
+          <t>Executive Management Services, LLC</t>
         </is>
       </c>
       <c r="I31" s="19" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>Low-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>Verify rent/occ w/ HelloData</t>
+          <t>Occ: CoStar 28% vs RealPage 84%; Rent: CoStar ask $1,716 vs RealPage eff $2,004; Rent: HD mix-wtd $1,994 vs CoStar ask $1,716; Occ: HD ~48% (CoStar/RP showed 28%); HD (90d): occ ~48% (units leased), ~22 leases/mo</t>
         </is>
       </c>
       <c r="M31">
@@ -1982,39 +1980,41 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Tauri Apartments</t>
+          <t>Shamrock Apartments</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="F32" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="18" t="n">
-        <v>1833.726076373041</v>
+        <v>0.833333</v>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Dc Fairview Llc</t>
         </is>
       </c>
       <c r="I32" s="19" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Low-Rise</t>
         </is>
       </c>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>Units: CoStar 156 vs RealPage 128; Year built: 2026/2027; Occ: CoStar 25% vs RealPage 18%; Rent: CoStar ask $1,862 vs RealPage eff $1,684; Occ: HD ~100% (CoStar/RP showed 25%); HD (90d): occ ~100% (units leased), ~20 leases/mo</t>
+          <t>Verify rent/occ w/ HelloData</t>
         </is>
       </c>
       <c r="M32">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Delano</t>
+          <t>Tauri Apartments</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
@@ -2040,29 +2040,27 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>1833.726076373041</v>
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>CBH Homes</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="I33" s="19" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData; RealPage-only — not in CoStar's 5-mi series</t>
+          <t>Units: CoStar 156 vs RealPage 128; Year built: 2026/2027; Occ: CoStar 25% vs RealPage 18%; Rent: CoStar ask $1,862 vs RealPage eff $1,684; Occ: HD ~100% (CoStar/RP showed 25%); HD (90d): occ ~100% (units leased), ~20 leases/mo</t>
         </is>
       </c>
       <c r="M33">
@@ -2070,54 +2068,60 @@
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="20" t="n"/>
-      <c r="C35" s="21" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Delano</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>CBH Homes</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData; RealPage-only — not in CoStar's 5-mi series</t>
+        </is>
+      </c>
+      <c r="M34">
+        <f>IFERROR(VALUE(RIGHT(E34,4))*4+MATCH(LEFT(E34,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>UNDER CONSTRUCTION (5 properties, 1,213 units)</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="22" t="n">
-        <v>27</v>
-      </c>
-      <c r="C36" s="23" t="inlineStr">
-        <is>
-          <t>South Ridge II</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="n">
-        <v>164</v>
-      </c>
-      <c r="E36" s="22" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="F36" s="25" t="n"/>
-      <c r="G36" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J36" s="22" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n"/>
-      <c r="M36">
-        <f>IFERROR(VALUE(RIGHT(E36,4))*4+MATCH(LEFT(E36,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
       </c>
     </row>
     <row r="37">
@@ -2126,15 +2130,15 @@
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>Dorado Station</t>
+          <t>South Ridge II</t>
         </is>
       </c>
       <c r="D37" s="24" t="n">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="E37" s="22" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F37" s="25" t="n"/>
@@ -2149,14 +2153,14 @@
         </is>
       </c>
       <c r="I37" s="27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J37" s="22" t="n"/>
-      <c r="K37" s="23" t="inlineStr">
-        <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
-        </is>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="n"/>
       <c r="M37">
         <f>IFERROR(VALUE(RIGHT(E37,4))*4+MATCH(LEFT(E37,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
@@ -2168,11 +2172,11 @@
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>Summertown (remaining phases)</t>
+          <t>Dorado Station</t>
         </is>
       </c>
       <c r="D38" s="24" t="n">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
@@ -2191,7 +2195,7 @@
         </is>
       </c>
       <c r="I38" s="27" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J38" s="22" t="n"/>
       <c r="K38" s="23" t="inlineStr">
@@ -2210,15 +2214,15 @@
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>Vanguard Village</t>
+          <t>Summertown (remaining phases)</t>
         </is>
       </c>
       <c r="D39" s="24" t="n">
-        <v>552</v>
+        <v>72</v>
       </c>
       <c r="E39" s="22" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="F39" s="25" t="n"/>
@@ -2233,14 +2237,14 @@
         </is>
       </c>
       <c r="I39" s="27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J39" s="22" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="n"/>
+        <v>3.5</v>
+      </c>
+      <c r="J39" s="22" t="n"/>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
+        </is>
+      </c>
       <c r="M39">
         <f>IFERROR(VALUE(RIGHT(E39,4))*4+MATCH(LEFT(E39,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
@@ -2252,11 +2256,11 @@
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>Centrepoint</t>
+          <t>Vanguard Village</t>
         </is>
       </c>
       <c r="D40" s="24" t="n">
-        <v>213</v>
+        <v>552</v>
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
@@ -2271,79 +2275,75 @@
       </c>
       <c r="H40" s="23" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I40" s="27" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J40" s="22" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: under construction - revived; permits issuing 2026</t>
-        </is>
-      </c>
+      <c r="K40" s="23" t="n"/>
       <c r="M40">
         <f>IFERROR(VALUE(RIGHT(E40,4))*4+MATCH(LEFT(E40,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="28" t="n"/>
-      <c r="C42" s="29" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>Centrepoint</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="n">
+        <v>213</v>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="n"/>
+      <c r="G41" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>Privately Owned</t>
+        </is>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J41" s="22" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: under construction - revived; permits issuing 2026</t>
+        </is>
+      </c>
+      <c r="M41">
+        <f>IFERROR(VALUE(RIGHT(E41,4))*4+MATCH(LEFT(E41,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="28" t="n"/>
+      <c r="C43" s="29" t="inlineStr">
         <is>
           <t>PROPOSED (15 properties, 3,646 units)</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="C43" s="31" t="inlineStr">
-        <is>
-          <t>Union 93</t>
-        </is>
-      </c>
-      <c r="D43" s="32" t="n">
-        <v>350</v>
-      </c>
-      <c r="E43" s="30" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
-      <c r="F43" s="33" t="n"/>
-      <c r="G43" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="31" t="inlineStr">
-        <is>
-          <t>Grey Owl Holdings Llc</t>
-        </is>
-      </c>
-      <c r="I43" s="35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J43" s="30" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K43" s="31" t="inlineStr">
-        <is>
-          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
-        </is>
-      </c>
-      <c r="M43">
-        <f>IFERROR(VALUE(RIGHT(E43,4))*4+MATCH(LEFT(E43,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
       </c>
     </row>
     <row r="44">
@@ -2352,15 +2352,15 @@
       </c>
       <c r="C44" s="31" t="inlineStr">
         <is>
-          <t>The Judy (Maple Grove &amp; Overland)</t>
+          <t>Union 93</t>
         </is>
       </c>
       <c r="D44" s="32" t="n">
-        <v>162</v>
+        <v>350</v>
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="F44" s="33" t="n"/>
@@ -2371,16 +2371,20 @@
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grey Owl Holdings Llc</t>
         </is>
       </c>
       <c r="I44" s="35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J44" s="30" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="J44" s="30" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
       <c r="K44" s="31" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
+          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
         </is>
       </c>
       <c r="M44">
@@ -2394,15 +2398,15 @@
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>Victory Flats</t>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>301</v>
+        <v>162</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="F45" s="33" t="n"/>
@@ -2413,20 +2417,16 @@
       </c>
       <c r="H45" s="31" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I45" s="35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J45" s="30" t="inlineStr">
-        <is>
-          <t>Townhome</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="J45" s="30" t="n"/>
       <c r="K45" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
         </is>
       </c>
       <c r="M45">
@@ -2440,15 +2440,15 @@
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>The Gateway at Ten Mile</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>390</v>
+        <v>301</v>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F46" s="33" t="n"/>
@@ -2459,15 +2459,15 @@
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>TGI Corp</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="I46" s="35" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J46" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K46" s="31" t="inlineStr">
@@ -2486,15 +2486,15 @@
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="D47" s="32" t="n">
-        <v>138</v>
+        <v>390</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
-          <t>Q1 2029</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F47" s="33" t="n"/>
@@ -2505,11 +2505,11 @@
       </c>
       <c r="H47" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TGI Corp</t>
         </is>
       </c>
       <c r="I47" s="35" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J47" s="30" t="inlineStr">
         <is>
@@ -2532,15 +2532,15 @@
       </c>
       <c r="C48" s="31" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>472</v>
+        <v>138</v>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="F48" s="33" t="n"/>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I48" s="35" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J48" s="30" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K48" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
       <c r="M48">
@@ -2578,11 +2578,11 @@
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>322</v>
+        <v>472</v>
       </c>
       <c r="E49" s="30" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="I49" s="35" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
@@ -2624,11 +2624,11 @@
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="I50" s="35" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J50" s="30" t="inlineStr">
         <is>
@@ -2670,11 +2670,11 @@
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
@@ -2693,12 +2693,16 @@
         </is>
       </c>
       <c r="I51" s="35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J51" s="30" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="J51" s="30" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
       <c r="K51" s="31" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M51">
@@ -2712,11 +2716,11 @@
       </c>
       <c r="C52" s="31" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
         </is>
       </c>
       <c r="D52" s="32" t="n">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
@@ -2735,16 +2739,12 @@
         </is>
       </c>
       <c r="I52" s="35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J52" s="30" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="J52" s="30" t="n"/>
       <c r="K52" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
       <c r="M52">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>Rolling Hill (Assemble Management)</t>
+          <t>Cobalt Point</t>
         </is>
       </c>
       <c r="D53" s="32" t="n">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="E53" s="30" t="inlineStr">
         <is>
@@ -2781,12 +2781,16 @@
         </is>
       </c>
       <c r="I53" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="30" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="J53" s="30" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
       <c r="K53" s="31" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M53">
@@ -2800,11 +2804,11 @@
       </c>
       <c r="C54" s="31" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>Rolling Hill (Assemble Management)</t>
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
@@ -2823,16 +2827,12 @@
         </is>
       </c>
       <c r="I54" s="35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J54" s="30" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J54" s="30" t="n"/>
       <c r="K54" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
       <c r="M54">
@@ -2846,11 +2846,11 @@
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="D55" s="32" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
@@ -2869,11 +2869,11 @@
         </is>
       </c>
       <c r="I55" s="35" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J55" s="30" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K55" s="31" t="inlineStr">
@@ -2892,11 +2892,11 @@
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
@@ -2915,11 +2915,11 @@
         </is>
       </c>
       <c r="I56" s="35" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J56" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K56" s="31" t="inlineStr">
@@ -2938,11 +2938,11 @@
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="D57" s="32" t="n">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E57" s="30" t="inlineStr">
         <is>
@@ -2957,20 +2957,20 @@
       </c>
       <c r="H57" s="31" t="inlineStr">
         <is>
-          <t>Peak Capital Investments Llc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I57" s="35" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J57" s="30" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K57" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
       <c r="M57">
@@ -2978,8 +2978,54 @@
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="36" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="30" t="n">
+        <v>47</v>
+      </c>
+      <c r="C58" s="31" t="inlineStr">
+        <is>
+          <t>Meridian OZ Apartments</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="E58" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F58" s="33" t="n"/>
+      <c r="G58" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="31" t="inlineStr">
+        <is>
+          <t>Peak Capital Investments Llc</t>
+        </is>
+      </c>
+      <c r="I58" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J58" s="30" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K58" s="31" t="inlineStr">
+        <is>
+          <t>Diligence: proposed</t>
+        </is>
+      </c>
+      <c r="M58">
+        <f>IFERROR(VALUE(RIGHT(E58,4))*4+MATCH(LEFT(E58,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="36" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Rent ($) = HelloData mix-weighted asking where covered, else market asking (CoStar). Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
@@ -2988,12 +3034,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B61:K61"/>
     <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="C36:K36"/>
     <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C28:K28"/>
-    <mergeCell ref="C35:K35"/>
-    <mergeCell ref="B60:K60"/>
+    <mergeCell ref="C43:K43"/>
+    <mergeCell ref="C29:K29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3110,15 +3156,15 @@
         </is>
       </c>
       <c r="R5" s="43">
-        <f>'Competitive Analysis'!C39</f>
+        <f>'Competitive Analysis'!C40</f>
         <v/>
       </c>
       <c r="S5" s="44">
-        <f>'Competitive Analysis'!D39</f>
+        <f>'Competitive Analysis'!D40</f>
         <v/>
       </c>
       <c r="T5" s="45">
-        <f>'Competitive Analysis'!E39</f>
+        <f>'Competitive Analysis'!E40</f>
         <v/>
       </c>
       <c r="V5">
@@ -3140,15 +3186,15 @@
         <v>0.95</v>
       </c>
       <c r="R6" s="43">
-        <f>'Competitive Analysis'!C40</f>
+        <f>'Competitive Analysis'!C41</f>
         <v/>
       </c>
       <c r="S6" s="44">
-        <f>'Competitive Analysis'!D40</f>
+        <f>'Competitive Analysis'!D41</f>
         <v/>
       </c>
       <c r="T6" s="45">
-        <f>'Competitive Analysis'!E40</f>
+        <f>'Competitive Analysis'!E41</f>
         <v/>
       </c>
       <c r="V6">
@@ -3172,15 +3218,15 @@
         </is>
       </c>
       <c r="R7" s="43">
-        <f>'Competitive Analysis'!C37</f>
+        <f>'Competitive Analysis'!C38</f>
         <v/>
       </c>
       <c r="S7" s="44">
-        <f>'Competitive Analysis'!D37</f>
+        <f>'Competitive Analysis'!D38</f>
         <v/>
       </c>
       <c r="T7" s="45">
-        <f>'Competitive Analysis'!E37</f>
+        <f>'Competitive Analysis'!E38</f>
         <v/>
       </c>
       <c r="V7">
@@ -3202,15 +3248,15 @@
         <v>425</v>
       </c>
       <c r="R8" s="43">
-        <f>'Competitive Analysis'!C36</f>
+        <f>'Competitive Analysis'!C37</f>
         <v/>
       </c>
       <c r="S8" s="44">
-        <f>'Competitive Analysis'!D36</f>
+        <f>'Competitive Analysis'!D37</f>
         <v/>
       </c>
       <c r="T8" s="45">
-        <f>'Competitive Analysis'!E36</f>
+        <f>'Competitive Analysis'!E37</f>
         <v/>
       </c>
       <c r="V8">
@@ -3232,15 +3278,15 @@
         <v>850</v>
       </c>
       <c r="R9" s="43">
-        <f>'Competitive Analysis'!C38</f>
+        <f>'Competitive Analysis'!C39</f>
         <v/>
       </c>
       <c r="S9" s="44">
-        <f>'Competitive Analysis'!D38</f>
+        <f>'Competitive Analysis'!D39</f>
         <v/>
       </c>
       <c r="T9" s="45">
-        <f>'Competitive Analysis'!E38</f>
+        <f>'Competitive Analysis'!E39</f>
         <v/>
       </c>
       <c r="V9">
@@ -3639,7 +3685,7 @@
         <v>450</v>
       </c>
       <c r="I19" s="52">
-        <f>SUMIFS('Competitive Analysis'!$D$5:$D$57,'Competitive Analysis'!$M$5:$M$57,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$57,"&lt;="&amp;8105)</f>
+        <f>SUMIFS('Competitive Analysis'!$D$5:$D$58,'Competitive Analysis'!$M$5:$M$58,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$58,"&lt;="&amp;8105)</f>
         <v/>
       </c>
       <c r="J19" s="53">
@@ -3890,24 +3936,14 @@
     <row r="23" ht="14.4" customHeight="1">
       <c r="B23" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Market Rent  (CoStar→HD)</t>
-        </is>
-      </c>
-      <c r="C23" s="56" t="n">
-        <v>1660</v>
-      </c>
-      <c r="D23" s="56" t="n">
-        <v>1703</v>
-      </c>
-      <c r="E23" s="56" t="n">
-        <v>1759</v>
-      </c>
-      <c r="F23" s="56" t="n">
-        <v>1802</v>
-      </c>
-      <c r="G23" s="56" t="n">
-        <v>1835</v>
-      </c>
+          <t xml:space="preserve">  Market Rent  (HelloData mix-wtd)</t>
+        </is>
+      </c>
+      <c r="C23" s="56" t="n"/>
+      <c r="D23" s="56" t="n"/>
+      <c r="E23" s="56" t="n"/>
+      <c r="F23" s="56" t="n"/>
+      <c r="G23" s="56" t="n"/>
       <c r="H23" s="56" t="n">
         <v>1777</v>
       </c>
@@ -4054,21 +4090,11 @@
           <t xml:space="preserve">  Effective Rent</t>
         </is>
       </c>
-      <c r="C25" s="56" t="n">
-        <v>1643</v>
-      </c>
-      <c r="D25" s="56" t="n">
-        <v>1691</v>
-      </c>
-      <c r="E25" s="56" t="n">
-        <v>1742</v>
-      </c>
-      <c r="F25" s="56" t="n">
-        <v>1785</v>
-      </c>
-      <c r="G25" s="56" t="n">
-        <v>1835</v>
-      </c>
+      <c r="C25" s="56" t="n"/>
+      <c r="D25" s="56" t="n"/>
+      <c r="E25" s="56" t="n"/>
+      <c r="F25" s="56" t="n"/>
+      <c r="G25" s="56" t="n"/>
       <c r="H25" s="56" t="n">
         <v>1619</v>
       </c>
@@ -5199,7 +5225,7 @@
       </c>
       <c r="E61" s="79" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5237,7 @@
       </c>
       <c r="E62" s="79" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5249,7 @@
       </c>
       <c r="E63" s="79" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5261,7 @@
       </c>
       <c r="E64" s="79" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5273,7 @@
       </c>
       <c r="E65" s="79" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5344,7 @@
     <row r="73" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="B73" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    -Y1: roster (CoStar-tracked) 90 + subj 360 vs CoStar 450   (tie ✓)</t>
+          <t xml:space="preserve">    -Y1: roster (CoStar-tracked) 450 vs CoStar 450   (tie ✓)</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5516,23 +5542,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>The Aren</t>
+          <t>Seasons at Meridian</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1066 S Silverstone Way</t>
+          <t>2700 E Overland Rd</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>396</v>
+        <v>360</v>
       </c>
       <c r="D3" t="n">
         <v>2024</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q3 2024</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5546,23 +5572,23 @@
         </is>
       </c>
       <c r="H3" s="81" t="n">
-        <v>0.969697</v>
+        <v>0.955556</v>
       </c>
       <c r="I3" s="81" t="n">
-        <v>0.998</v>
+        <v>0.989</v>
       </c>
       <c r="J3" s="81" t="n"/>
       <c r="K3" s="82" t="n">
-        <v>1762</v>
+        <v>1951</v>
       </c>
       <c r="L3" s="82" t="n">
-        <v>1841</v>
+        <v>1884</v>
       </c>
       <c r="M3" s="82" t="n">
-        <v>1739.209026472431</v>
+        <v>1911.119099448338</v>
       </c>
       <c r="N3" s="82" t="n">
-        <v>1663.812235275689</v>
+        <v>1879.261597336116</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -5571,30 +5597,30 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Year built: 2024/2025; Occ: CoStar 97% vs RealPage 100%</t>
+          <t>Year built: 2024/2025; SUBJECT — this deal; Occ: CoStar 96% vs RealPage 99%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Viera at Pinnacle</t>
+          <t>The Aren</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6269 S Aspiration Ave</t>
+          <t>1066 S Silverstone Way</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>396</v>
       </c>
       <c r="D4" t="n">
         <v>2024</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Q1 2024</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5608,40 +5634,48 @@
         </is>
       </c>
       <c r="H4" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="81" t="n"/>
+        <v>0.969697</v>
+      </c>
+      <c r="I4" s="81" t="n">
+        <v>0.998</v>
+      </c>
       <c r="J4" s="81" t="n"/>
       <c r="K4" s="82" t="n">
-        <v>2595</v>
-      </c>
-      <c r="L4" s="82" t="n"/>
+        <v>1762</v>
+      </c>
+      <c r="L4" s="82" t="n">
+        <v>1841</v>
+      </c>
       <c r="M4" s="82" t="n">
-        <v>2489.375</v>
+        <v>1739.209026472431</v>
       </c>
       <c r="N4" s="82" t="n">
-        <v>2395.895833333333</v>
+        <v>1663.812235275689</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>CoStar</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>CoStar+RealPage</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Year built: 2024/2025; Occ: CoStar 97% vs RealPage 100%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Movado Village</t>
+          <t>Viera at Pinnacle</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1711 S Movado Way</t>
+          <t>6269 S Aspiration Ave</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
         <v>2024</v>
@@ -5662,19 +5696,19 @@
         </is>
       </c>
       <c r="H5" s="81" t="n">
-        <v>0.933333</v>
+        <v>1</v>
       </c>
       <c r="I5" s="81" t="n"/>
       <c r="J5" s="81" t="n"/>
       <c r="K5" s="82" t="n">
-        <v>2070</v>
+        <v>2595</v>
       </c>
       <c r="L5" s="82" t="n"/>
       <c r="M5" s="82" t="n">
-        <v>1995</v>
+        <v>2489.375</v>
       </c>
       <c r="N5" s="82" t="n">
-        <v>1995</v>
+        <v>2395.895833333333</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -5686,23 +5720,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Telluride</t>
+          <t>Movado Village</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>597 N Maple Grove Rd</t>
+          <t>1711 S Movado Way</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Q2 2023</t>
+          <t>Q1 2024</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5716,19 +5750,19 @@
         </is>
       </c>
       <c r="H6" s="81" t="n">
-        <v>0.990196</v>
+        <v>0.933333</v>
       </c>
       <c r="I6" s="81" t="n"/>
       <c r="J6" s="81" t="n"/>
       <c r="K6" s="82" t="n">
-        <v>1898</v>
+        <v>2070</v>
       </c>
       <c r="L6" s="82" t="n"/>
       <c r="M6" s="82" t="n">
-        <v>1884.446808510638</v>
+        <v>1995</v>
       </c>
       <c r="N6" s="82" t="n">
-        <v>1884.446808510638</v>
+        <v>1995</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -5740,16 +5774,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Altair</t>
+          <t>Telluride</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2743 W Peak Cloud Ln</t>
+          <t>597 N Maple Grove Rd</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>240</v>
+        <v>102</v>
       </c>
       <c r="D7" t="n">
         <v>2023</v>
@@ -5770,44 +5804,36 @@
         </is>
       </c>
       <c r="H7" s="81" t="n">
-        <v>0.945833</v>
-      </c>
-      <c r="I7" s="81" t="n">
-        <v>0.996</v>
-      </c>
+        <v>0.990196</v>
+      </c>
+      <c r="I7" s="81" t="n"/>
       <c r="J7" s="81" t="n"/>
       <c r="K7" s="82" t="n">
-        <v>1689</v>
-      </c>
-      <c r="L7" s="82" t="n">
-        <v>1754</v>
-      </c>
+        <v>1898</v>
+      </c>
+      <c r="L7" s="82" t="n"/>
       <c r="M7" s="82" t="n">
-        <v>1624.407772304324</v>
+        <v>1884.446808510638</v>
       </c>
       <c r="N7" s="82" t="n">
-        <v>1573.192255062945</v>
+        <v>1884.446808510638</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Occ: CoStar 95% vs RealPage 100%</t>
-        </is>
-      </c>
+          <t>CoStar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dovetail</t>
+          <t>Altair</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1350 N Webb Way</t>
+          <t>2743 W Peak Cloud Ln</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5832,20 +5858,24 @@
         </is>
       </c>
       <c r="H8" s="81" t="n">
-        <v>0.958333</v>
+        <v>0.945833</v>
       </c>
       <c r="I8" s="81" t="n">
-        <v>0.992</v>
+        <v>0.996</v>
       </c>
       <c r="J8" s="81" t="n"/>
       <c r="K8" s="82" t="n">
-        <v>1832</v>
+        <v>1689</v>
       </c>
       <c r="L8" s="82" t="n">
-        <v>1856</v>
-      </c>
-      <c r="M8" s="82" t="n"/>
-      <c r="N8" s="82" t="n"/>
+        <v>1754</v>
+      </c>
+      <c r="M8" s="82" t="n">
+        <v>1624.407772304324</v>
+      </c>
+      <c r="N8" s="82" t="n">
+        <v>1573.192255062945</v>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -5853,23 +5883,23 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Units: CoStar 240 vs RealPage 480; Year built: 2020/2023; Occ: CoStar 96% vs RealPage 99%</t>
+          <t>Occ: CoStar 95% vs RealPage 100%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Yellowstone Apartments</t>
+          <t>Dovetail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3500 West Pine Avenue</t>
+          <t>1350 N Webb Way</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
         <v>2023</v>
@@ -5890,24 +5920,20 @@
         </is>
       </c>
       <c r="H9" s="81" t="n">
-        <v>0.763889</v>
+        <v>0.958333</v>
       </c>
       <c r="I9" s="81" t="n">
-        <v>0.944</v>
+        <v>0.992</v>
       </c>
       <c r="J9" s="81" t="n"/>
       <c r="K9" s="82" t="n">
-        <v>1707</v>
+        <v>1832</v>
       </c>
       <c r="L9" s="82" t="n">
-        <v>1691</v>
-      </c>
-      <c r="M9" s="82" t="n">
-        <v>1735.469387755102</v>
-      </c>
-      <c r="N9" s="82" t="n">
-        <v>1735.469387755102</v>
-      </c>
+        <v>1856</v>
+      </c>
+      <c r="M9" s="82" t="n"/>
+      <c r="N9" s="82" t="n"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -5915,30 +5941,30 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Year built: 2023/2025; Occ: CoStar 76% vs RealPage 94%</t>
+          <t>Units: CoStar 240 vs RealPage 480; Year built: 2020/2023; Occ: CoStar 96% vs RealPage 99%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alante Homes at Hazelwood</t>
+          <t>Yellowstone Apartments</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6222 S Gloriosa Ln</t>
+          <t>3500 West Pine Avenue</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
         <v>2023</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Q1 2023</t>
+          <t>Q2 2023</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5952,36 +5978,48 @@
         </is>
       </c>
       <c r="H10" s="81" t="n">
-        <v>0.96875</v>
-      </c>
-      <c r="I10" s="81" t="n"/>
+        <v>0.763889</v>
+      </c>
+      <c r="I10" s="81" t="n">
+        <v>0.944</v>
+      </c>
       <c r="J10" s="81" t="n"/>
       <c r="K10" s="82" t="n">
-        <v>2276</v>
-      </c>
-      <c r="L10" s="82" t="n"/>
-      <c r="M10" s="82" t="n"/>
-      <c r="N10" s="82" t="n"/>
+        <v>1707</v>
+      </c>
+      <c r="L10" s="82" t="n">
+        <v>1691</v>
+      </c>
+      <c r="M10" s="82" t="n">
+        <v>1735.469387755102</v>
+      </c>
+      <c r="N10" s="82" t="n">
+        <v>1735.469387755102</v>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>CoStar</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+          <t>CoStar+RealPage</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Year built: 2023/2025; Occ: CoStar 76% vs RealPage 94%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Modern Craftsman Ten Mile</t>
+          <t>Alante Homes at Hazelwood</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3233 W Littleton Ln</t>
+          <t>6222 S Gloriosa Ln</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
         <v>2023</v>
@@ -6002,48 +6040,36 @@
         </is>
       </c>
       <c r="H11" s="81" t="n">
-        <v>0.948148</v>
-      </c>
-      <c r="I11" s="81" t="n">
-        <v>0.993</v>
-      </c>
+        <v>0.96875</v>
+      </c>
+      <c r="I11" s="81" t="n"/>
       <c r="J11" s="81" t="n"/>
       <c r="K11" s="82" t="n">
-        <v>2229</v>
-      </c>
-      <c r="L11" s="82" t="n">
-        <v>2243</v>
-      </c>
-      <c r="M11" s="82" t="n">
-        <v>2164.319806763285</v>
-      </c>
-      <c r="N11" s="82" t="n">
-        <v>2140.342028985508</v>
-      </c>
+        <v>2276</v>
+      </c>
+      <c r="L11" s="82" t="n"/>
+      <c r="M11" s="82" t="n"/>
+      <c r="N11" s="82" t="n"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Year built: 2022/2023; Occ: CoStar 95% vs RealPage 99%</t>
-        </is>
-      </c>
+          <t>CoStar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WaterWalk Boise – Meridian</t>
+          <t>Modern Craftsman Ten Mile</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88 n Olson Ave</t>
+          <t>3233 W Littleton Ln</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>2023</v>
@@ -6064,43 +6090,55 @@
         </is>
       </c>
       <c r="H12" s="81" t="n">
-        <v>0.947368</v>
-      </c>
-      <c r="I12" s="81" t="n"/>
+        <v>0.948148</v>
+      </c>
+      <c r="I12" s="81" t="n">
+        <v>0.993</v>
+      </c>
       <c r="J12" s="81" t="n"/>
       <c r="K12" s="82" t="n">
-        <v>1655</v>
-      </c>
-      <c r="L12" s="82" t="n"/>
-      <c r="M12" s="82" t="n"/>
-      <c r="N12" s="82" t="n"/>
+        <v>2229</v>
+      </c>
+      <c r="L12" s="82" t="n">
+        <v>2243</v>
+      </c>
+      <c r="M12" s="82" t="n">
+        <v>2164.319806763285</v>
+      </c>
+      <c r="N12" s="82" t="n">
+        <v>2140.342028985508</v>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>CoStar</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
+          <t>CoStar+RealPage</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Year built: 2022/2023; Occ: CoStar 95% vs RealPage 99%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>The Prospect</t>
+          <t>WaterWalk Boise – Meridian</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8002 W Overland Rd</t>
+          <t>88 n Olson Ave</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Q4 2022</t>
+          <t>Q1 2023</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6114,20 +6152,16 @@
         </is>
       </c>
       <c r="H13" s="81" t="n">
-        <v>0.989011</v>
+        <v>0.947368</v>
       </c>
       <c r="I13" s="81" t="n"/>
       <c r="J13" s="81" t="n"/>
       <c r="K13" s="82" t="n">
-        <v>1189</v>
+        <v>1655</v>
       </c>
       <c r="L13" s="82" t="n"/>
-      <c r="M13" s="82" t="n">
-        <v>1165.555555555556</v>
-      </c>
-      <c r="N13" s="82" t="n">
-        <v>1156.326599326599</v>
-      </c>
+      <c r="M13" s="82" t="n"/>
+      <c r="N13" s="82" t="n"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -6138,16 +6172,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Etheridge Lane</t>
+          <t>The Prospect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1428 N Etheridge Ln</t>
+          <t>8002 W Overland Rd</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>2022</v>
@@ -6167,13 +6201,21 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H14" s="81" t="n"/>
+      <c r="H14" s="81" t="n">
+        <v>0.989011</v>
+      </c>
       <c r="I14" s="81" t="n"/>
       <c r="J14" s="81" t="n"/>
-      <c r="K14" s="82" t="n"/>
+      <c r="K14" s="82" t="n">
+        <v>1189</v>
+      </c>
       <c r="L14" s="82" t="n"/>
-      <c r="M14" s="82" t="n"/>
-      <c r="N14" s="82" t="n"/>
+      <c r="M14" s="82" t="n">
+        <v>1165.555555555556</v>
+      </c>
+      <c r="N14" s="82" t="n">
+        <v>1156.326599326599</v>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -6184,23 +6226,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Old Town Lofts</t>
+          <t>Etheridge Lane</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>33 E Idaho Ave</t>
+          <t>1428 N Etheridge Ln</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>2022</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Q3 2022</t>
+          <t>Q4 2022</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -6213,49 +6255,33 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H15" s="81" t="n">
-        <v>0.990196</v>
-      </c>
-      <c r="I15" s="81" t="n">
-        <v>0.99</v>
-      </c>
+      <c r="H15" s="81" t="n"/>
+      <c r="I15" s="81" t="n"/>
       <c r="J15" s="81" t="n"/>
-      <c r="K15" s="82" t="n">
-        <v>1683</v>
-      </c>
-      <c r="L15" s="82" t="n">
-        <v>1661</v>
-      </c>
-      <c r="M15" s="82" t="n">
-        <v>1665.511627906977</v>
-      </c>
-      <c r="N15" s="82" t="n">
-        <v>1665.511627906977</v>
-      </c>
+      <c r="K15" s="82" t="n"/>
+      <c r="L15" s="82" t="n"/>
+      <c r="M15" s="82" t="n"/>
+      <c r="N15" s="82" t="n"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Year built: 2022/2023</t>
-        </is>
-      </c>
+          <t>CoStar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lavender Village</t>
+          <t>Old Town Lofts</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2607-2615 N Linda Vista Ln</t>
+          <t>33 E Idaho Ave</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
         <v>2022</v>
@@ -6275,50 +6301,56 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H16" s="81" t="n"/>
-      <c r="I16" s="81" t="n"/>
+      <c r="H16" s="81" t="n">
+        <v>0.990196</v>
+      </c>
+      <c r="I16" s="81" t="n">
+        <v>0.99</v>
+      </c>
       <c r="J16" s="81" t="n"/>
       <c r="K16" s="82" t="n">
-        <v>2110</v>
-      </c>
-      <c r="L16" s="82" t="n"/>
+        <v>1683</v>
+      </c>
+      <c r="L16" s="82" t="n">
+        <v>1661</v>
+      </c>
       <c r="M16" s="82" t="n">
-        <v>1747.513661202186</v>
+        <v>1665.511627906977</v>
       </c>
       <c r="N16" s="82" t="n">
-        <v>1747.513661202186</v>
+        <v>1665.511627906977</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rent: HD mix-wtd $1,748 vs CoStar ask $2,110</t>
+          <t>Year built: 2022/2023</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Meritage West</t>
+          <t>Lavender Village</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13450 W Baldcypress St</t>
+          <t>2607-2615 N Linda Vista Ln</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>2022</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Q2 2022</t>
+          <t>Q3 2022</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -6331,45 +6363,43 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H17" s="81" t="n">
-        <v>0.9879520000000001</v>
-      </c>
-      <c r="I17" s="81" t="n">
-        <v>0.976</v>
-      </c>
+      <c r="H17" s="81" t="n"/>
+      <c r="I17" s="81" t="n"/>
       <c r="J17" s="81" t="n"/>
       <c r="K17" s="82" t="n">
-        <v>1664</v>
-      </c>
-      <c r="L17" s="82" t="n">
-        <v>1641</v>
-      </c>
+        <v>2110</v>
+      </c>
+      <c r="L17" s="82" t="n"/>
       <c r="M17" s="82" t="n">
-        <v>1651.435028248588</v>
+        <v>1747.513661202186</v>
       </c>
       <c r="N17" s="82" t="n">
-        <v>1651.435028248588</v>
+        <v>1747.513661202186</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>CoStar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rent: HD mix-wtd $1,748 vs CoStar ask $2,110</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Celebration Acres</t>
+          <t>Meritage West</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10881 W Florence Dr</t>
+          <t>13450 W Baldcypress St</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D18" t="n">
         <v>2022</v>
@@ -6390,17 +6420,27 @@
         </is>
       </c>
       <c r="H18" s="81" t="n">
-        <v>0.964286</v>
-      </c>
-      <c r="I18" s="81" t="n"/>
+        <v>0.9879520000000001</v>
+      </c>
+      <c r="I18" s="81" t="n">
+        <v>0.976</v>
+      </c>
       <c r="J18" s="81" t="n"/>
-      <c r="K18" s="82" t="n"/>
-      <c r="L18" s="82" t="n"/>
-      <c r="M18" s="82" t="n"/>
-      <c r="N18" s="82" t="n"/>
+      <c r="K18" s="82" t="n">
+        <v>1664</v>
+      </c>
+      <c r="L18" s="82" t="n">
+        <v>1641</v>
+      </c>
+      <c r="M18" s="82" t="n">
+        <v>1651.435028248588</v>
+      </c>
+      <c r="N18" s="82" t="n">
+        <v>1651.435028248588</v>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -6408,16 +6448,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ambleside Townhomes</t>
+          <t>Celebration Acres</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1890 N Shamrock Ave</t>
+          <t>10881 W Florence Dr</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>2022</v>
@@ -6438,13 +6478,11 @@
         </is>
       </c>
       <c r="H19" s="81" t="n">
-        <v>0.970149</v>
+        <v>0.964286</v>
       </c>
       <c r="I19" s="81" t="n"/>
       <c r="J19" s="81" t="n"/>
-      <c r="K19" s="82" t="n">
-        <v>2130</v>
-      </c>
+      <c r="K19" s="82" t="n"/>
       <c r="L19" s="82" t="n"/>
       <c r="M19" s="82" t="n"/>
       <c r="N19" s="82" t="n"/>
@@ -6458,16 +6496,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pine 43</t>
+          <t>Ambleside Townhomes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1301 N Meadowglen Ave</t>
+          <t>1890 N Shamrock Ave</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D20" t="n">
         <v>2022</v>
@@ -6487,11 +6525,13 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H20" s="81" t="n"/>
+      <c r="H20" s="81" t="n">
+        <v>0.970149</v>
+      </c>
       <c r="I20" s="81" t="n"/>
       <c r="J20" s="81" t="n"/>
       <c r="K20" s="82" t="n">
-        <v>2236</v>
+        <v>2130</v>
       </c>
       <c r="L20" s="82" t="n"/>
       <c r="M20" s="82" t="n"/>
@@ -6506,16 +6546,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>South Ridge I</t>
+          <t>Pine 43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1703 S Grand Frk Wy</t>
+          <t>1301 N Meadowglen Ave</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>476</v>
+        <v>25</v>
       </c>
       <c r="D21" t="n">
         <v>2022</v>
@@ -6525,58 +6565,52 @@
           <t>Q2 2022</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CoStar property analytics</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
       <c r="H21" s="81" t="n"/>
-      <c r="I21" s="81" t="n">
-        <v>0.994</v>
-      </c>
+      <c r="I21" s="81" t="n"/>
       <c r="J21" s="81" t="n"/>
-      <c r="K21" s="82" t="n"/>
-      <c r="L21" s="82" t="n">
-        <v>1672</v>
-      </c>
+      <c r="K21" s="82" t="n">
+        <v>2236</v>
+      </c>
+      <c r="L21" s="82" t="n"/>
       <c r="M21" s="82" t="n"/>
       <c r="N21" s="82" t="n"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Delivery quarter estimated; RealPage-only — not in CoStar's 5-mi series</t>
-        </is>
-      </c>
+          <t>CoStar</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>The Lost Rapid Townhomes</t>
+          <t>South Ridge I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3400 W Chinden Blvd</t>
+          <t>1703 S Grand Frk Wy</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>72</v>
+        <v>476</v>
       </c>
       <c r="D22" t="n">
         <v>2022</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Q1 2022</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>CoStar property analytics</t>
+          <t>Q2 2022</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6584,42 +6618,48 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="H22" s="81" t="n">
-        <v>0.944444</v>
-      </c>
-      <c r="I22" s="81" t="n"/>
+      <c r="H22" s="81" t="n"/>
+      <c r="I22" s="81" t="n">
+        <v>0.994</v>
+      </c>
       <c r="J22" s="81" t="n"/>
       <c r="K22" s="82" t="n"/>
-      <c r="L22" s="82" t="n"/>
+      <c r="L22" s="82" t="n">
+        <v>1672</v>
+      </c>
       <c r="M22" s="82" t="n"/>
       <c r="N22" s="82" t="n"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>CoStar</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Delivery quarter estimated; RealPage-only — not in CoStar's 5-mi series</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tauri Apartments</t>
+          <t>The Lost Rapid Townhomes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12673 W Ashcreek St</t>
+          <t>3400 W Chinden Blvd</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="D23" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q1 2022</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -6629,54 +6669,38 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LEASING UP</t>
+          <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
       <c r="H23" s="81" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I23" s="81" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J23" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="82" t="n">
-        <v>1862</v>
-      </c>
-      <c r="L23" s="82" t="n">
-        <v>1684</v>
-      </c>
-      <c r="M23" s="82" t="n">
-        <v>1833.726076373041</v>
-      </c>
-      <c r="N23" s="82" t="n">
-        <v>1813.154621177544</v>
-      </c>
+        <v>0.944444</v>
+      </c>
+      <c r="I23" s="81" t="n"/>
+      <c r="J23" s="81" t="n"/>
+      <c r="K23" s="82" t="n"/>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82" t="n"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Units: CoStar 156 vs RealPage 128; Year built: 2026/2027; Occ: CoStar 25% vs RealPage 18%; Rent: CoStar ask $1,862 vs RealPage eff $1,684; Occ: HD ~100% (CoStar/RP showed 25%); HD (90d): occ ~100% (units leased), ~20 leases/mo</t>
-        </is>
-      </c>
+          <t>CoStar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Delano</t>
+          <t>Tauri Apartments</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3858 N Centrepoint Way</t>
+          <t>12673 W Ashcreek St</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="D24" t="n">
         <v>2026</v>
@@ -6686,58 +6710,68 @@
           <t>Q2 2026</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CoStar property analytics</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="H24" s="81" t="n"/>
+      <c r="H24" s="81" t="n">
+        <v>0.25</v>
+      </c>
       <c r="I24" s="81" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="J24" s="81" t="n"/>
-      <c r="K24" s="82" t="n"/>
+        <v>0.18</v>
+      </c>
+      <c r="J24" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="82" t="n">
+        <v>1862</v>
+      </c>
       <c r="L24" s="82" t="n">
-        <v>1491</v>
-      </c>
-      <c r="M24" s="82" t="n"/>
-      <c r="N24" s="82" t="n"/>
+        <v>1684</v>
+      </c>
+      <c r="M24" s="82" t="n">
+        <v>1833.726076373041</v>
+      </c>
+      <c r="N24" s="82" t="n">
+        <v>1813.154621177544</v>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData; RealPage-only — not in CoStar's 5-mi series</t>
+          <t>Units: CoStar 156 vs RealPage 128; Year built: 2026/2027; Occ: CoStar 25% vs RealPage 18%; Rent: CoStar ask $1,862 vs RealPage eff $1,684; Occ: HD ~100% (CoStar/RP showed 25%); HD (90d): occ ~100% (units leased), ~20 leases/mo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shamrock Apartments</t>
+          <t>Delano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1590 N Shamrock St</t>
+          <t>3858 N Centrepoint Way</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="D25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>CoStar property analytics</t>
+          <t>Q2 2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -6745,46 +6779,48 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="H25" s="81" t="n">
-        <v>0.833333</v>
-      </c>
-      <c r="I25" s="81" t="n"/>
+      <c r="H25" s="81" t="n"/>
+      <c r="I25" s="81" t="n">
+        <v>0.452</v>
+      </c>
       <c r="J25" s="81" t="n"/>
       <c r="K25" s="82" t="n"/>
-      <c r="L25" s="82" t="n"/>
+      <c r="L25" s="82" t="n">
+        <v>1491</v>
+      </c>
       <c r="M25" s="82" t="n"/>
       <c r="N25" s="82" t="n"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>RealPage</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData; RealPage-only — not in CoStar's 5-mi series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Village Apartments</t>
+          <t>Shamrock Apartments</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2651 N Records Ave</t>
+          <t>1590 N Shamrock St</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>336</v>
+        <v>48</v>
       </c>
       <c r="D26" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -6798,50 +6834,38 @@
         </is>
       </c>
       <c r="H26" s="81" t="n">
-        <v>0.803571</v>
-      </c>
-      <c r="I26" s="81" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="J26" s="81" t="n">
-        <v>0.119047619047619</v>
-      </c>
-      <c r="K26" s="82" t="n">
-        <v>1742</v>
-      </c>
-      <c r="L26" s="82" t="n">
-        <v>1677</v>
-      </c>
-      <c r="M26" s="82" t="n">
-        <v>1747.513661202186</v>
-      </c>
-      <c r="N26" s="82" t="n">
-        <v>1747.513661202186</v>
-      </c>
+        <v>0.833333</v>
+      </c>
+      <c r="I26" s="81" t="n"/>
+      <c r="J26" s="81" t="n"/>
+      <c r="K26" s="82" t="n"/>
+      <c r="L26" s="82" t="n"/>
+      <c r="M26" s="82" t="n"/>
+      <c r="N26" s="82" t="n"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
+          <t>Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wesley Apartments and Townhomes</t>
+          <t>Village Apartments</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3104 N Venable Ln</t>
+          <t>2651 N Records Ave</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>191</v>
+        <v>336</v>
       </c>
       <c r="D27" t="n">
         <v>2024</v>
@@ -6862,25 +6886,25 @@
         </is>
       </c>
       <c r="H27" s="81" t="n">
-        <v>0.277487</v>
+        <v>0.803571</v>
       </c>
       <c r="I27" s="81" t="n">
-        <v>0.838</v>
+        <v>0.113</v>
       </c>
       <c r="J27" s="81" t="n">
-        <v>0.4764397905759162</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="K27" s="82" t="n">
-        <v>1716</v>
+        <v>1742</v>
       </c>
       <c r="L27" s="82" t="n">
-        <v>2004</v>
+        <v>1677</v>
       </c>
       <c r="M27" s="82" t="n">
-        <v>1994.484728234728</v>
+        <v>1747.513661202186</v>
       </c>
       <c r="N27" s="82" t="n">
-        <v>1994.484728234728</v>
+        <v>1747.513661202186</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -6889,68 +6913,90 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Occ: CoStar 28% vs RealPage 84%; Rent: CoStar ask $1,716 vs RealPage eff $2,004; Rent: HD mix-wtd $1,994 vs CoStar ask $1,716; Occ: HD ~48% (CoStar/RP showed 28%); HD (90d): occ ~48% (units leased), ~22 leases/mo</t>
+          <t>Occ: CoStar 80% vs RealPage 11%; Occ: HD ~12% (CoStar/RP showed 80%); HD (90d): occ ~12% (units leased), ~13 leases/mo</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vanguard Village</t>
+          <t>Wesley Apartments and Townhomes</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1085 S 10 Mile Rd</t>
+          <t>3104 N Venable Ln</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>552</v>
+        <v>191</v>
       </c>
       <c r="D28" t="n">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q2 2024</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CoStar property analytics</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNDER CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="H28" s="81" t="n"/>
-      <c r="I28" s="81" t="n"/>
-      <c r="J28" s="81" t="n"/>
-      <c r="K28" s="82" t="n"/>
-      <c r="L28" s="82" t="n"/>
+          <t>LEASING UP</t>
+        </is>
+      </c>
+      <c r="H28" s="81" t="n">
+        <v>0.277487</v>
+      </c>
+      <c r="I28" s="81" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="J28" s="81" t="n">
+        <v>0.4764397905759162</v>
+      </c>
+      <c r="K28" s="82" t="n">
+        <v>1716</v>
+      </c>
+      <c r="L28" s="82" t="n">
+        <v>2004</v>
+      </c>
       <c r="M28" s="82" t="n">
-        <v>1747.513661202186</v>
+        <v>1994.484728234728</v>
       </c>
       <c r="N28" s="82" t="n">
-        <v>1747.513661202186</v>
+        <v>1994.484728234728</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>CoStar</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
+          <t>CoStar+RealPage</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Occ: CoStar 28% vs RealPage 84%; Rent: CoStar ask $1,716 vs RealPage eff $2,004; Rent: HD mix-wtd $1,994 vs CoStar ask $1,716; Occ: HD ~48% (CoStar/RP showed 28%); HD (90d): occ ~48% (units leased), ~22 leases/mo</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Centrepoint</t>
+          <t>Vanguard Village</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3100 N Centrepoint Way</t>
+          <t>1085 S 10 Mile Rd</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>213</v>
+        <v>552</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2027</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -6967,36 +7013,36 @@
       <c r="J29" s="81" t="n"/>
       <c r="K29" s="82" t="n"/>
       <c r="L29" s="82" t="n"/>
-      <c r="M29" s="82" t="n"/>
-      <c r="N29" s="82" t="n"/>
+      <c r="M29" s="82" t="n">
+        <v>1747.513661202186</v>
+      </c>
+      <c r="N29" s="82" t="n">
+        <v>1747.513661202186</v>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: under construction - revived; permits issuing 2026</t>
-        </is>
-      </c>
+          <t>CoStar</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dorado Station</t>
+          <t>Centrepoint</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1500 N Eldorado St, Boise 83704</t>
+          <t>3100 N Centrepoint Way</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7013,28 +7059,28 @@
       <c r="N30" s="82" t="n"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Diligence</t>
+          <t>RealPage</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: under construction - revived; permits issuing 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Summertown (remaining phases)</t>
+          <t>Dorado Station</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3005 N Ridgebury Ln, Meridian 83646</t>
+          <t>1500 N Eldorado St, Boise 83704</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -7067,23 +7113,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>South Ridge II</t>
+          <t>Summertown (remaining phases)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1703 S Grand Frk Wy</t>
+          <t>3005 N Ridgebury Ln, Meridian 83646</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>164</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2027</v>
+        <v>72</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7100,36 +7143,40 @@
       <c r="N32" s="82" t="n"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>Diligence</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: under construction</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>South Ridge II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11101 W Overland Rd</t>
+          <t>1703 S Grand Frk Wy</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="D33" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Q1 2029</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
       <c r="H33" s="81" t="n"/>
@@ -7141,35 +7188,31 @@
       <c r="N33" s="82" t="n"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>CoStar</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Diligence: proposed</t>
-        </is>
-      </c>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>The Gateway at Ten Mile</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2954 W Franklin Rd</t>
+          <t>11101 W Overland Rd</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>390</v>
+        <v>138</v>
       </c>
       <c r="D34" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7198,23 +7241,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Victory Flats</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8373 West Victory Rd</t>
+          <t>2954 W Franklin Rd</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="D35" t="n">
         <v>2027</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7231,7 +7274,7 @@
       <c r="N35" s="82" t="n"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -7243,20 +7286,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The Judy (Maple Grove &amp; Overland)</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1770 S Maple Grove Rd, Boise 83704</t>
+          <t>8373 West Victory Rd</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>162</v>
+        <v>301</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2027</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7273,35 +7319,32 @@
       <c r="N36" s="82" t="n"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Diligence</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Union 93</t>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>221-225 E Broadway Ave</t>
+          <t>1770 S Maple Grove Rd, Boise 83704</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>350</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2026</v>
+        <v>162</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Q3 2026</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7318,28 +7361,36 @@
       <c r="N37" s="82" t="n"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>Union 93</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1475 E Franklin Rd</t>
+          <t>221-225 E Broadway Ave</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>60</v>
+        <v>350</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -7360,23 +7411,23 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Meridian OZ Apartments</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>580 N Cole Rd</t>
+          <t>1475 E Franklin Rd</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -7392,28 +7443,28 @@
       <c r="N39" s="82" t="n"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>E Fairview Ave &amp; N Records Way</t>
+          <t>580 N Cole Rd</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>472</v>
+        <v>136</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -7441,16 +7492,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S Cobalt Point Way &amp; E Copper Point Dr</t>
+          <t>E Fairview Ave &amp; N Records Way</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>264</v>
+        <v>472</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -7478,16 +7529,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>Cobalt Point</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1005 E Fairview Ave</t>
+          <t>S Cobalt Point Way &amp; E Copper Point Dr</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>150</v>
+        <v>264</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -7499,12 +7550,8 @@
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="82" t="n"/>
       <c r="L42" s="82" t="n"/>
-      <c r="M42" s="82" t="n">
-        <v>1837.580964685616</v>
-      </c>
-      <c r="N42" s="82" t="n">
-        <v>1837.580964685616</v>
-      </c>
+      <c r="M42" s="82" t="n"/>
+      <c r="N42" s="82" t="n"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7519,16 +7566,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12548 W Overland Rd</t>
+          <t>1005 E Fairview Ave</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -7540,8 +7587,12 @@
       <c r="J43" s="81" t="n"/>
       <c r="K43" s="82" t="n"/>
       <c r="L43" s="82" t="n"/>
-      <c r="M43" s="82" t="n"/>
-      <c r="N43" s="82" t="n"/>
+      <c r="M43" s="82" t="n">
+        <v>1837.580964685616</v>
+      </c>
+      <c r="N43" s="82" t="n">
+        <v>1837.580964685616</v>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7556,16 +7607,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12565 W Fairview Ave</t>
+          <t>12548 W Overland Rd</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>275</v>
+        <v>156</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7593,16 +7644,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Amity Ave &amp; Meridian Rd</t>
+          <t>12565 W Fairview Ave</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>322</v>
+        <v>275</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7630,16 +7681,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rolling Hill (Assemble Management)</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4270 E Overland Rd, Meridian 83642</t>
+          <t>Amity Ave &amp; Meridian Rd</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>200</v>
+        <v>322</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7655,28 +7706,28 @@
       <c r="N46" s="82" t="n"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Diligence</t>
+          <t>RealPage</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
+          <t>Rolling Hill (Assemble Management)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>E Pine Ave &amp; N Webb Way, Meridian 83642</t>
+          <t>4270 E Overland Rd, Meridian 83642</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7696,6 +7747,43 @@
         </is>
       </c>
       <c r="P47" t="inlineStr">
+        <is>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>E Pine Ave &amp; N Webb Way, Meridian 83642</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>270</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="H48" s="81" t="n"/>
+      <c r="I48" s="81" t="n"/>
+      <c r="J48" s="81" t="n"/>
+      <c r="K48" s="82" t="n"/>
+      <c r="L48" s="82" t="n"/>
+      <c r="M48" s="82" t="n"/>
+      <c r="N48" s="82" t="n"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Diligence</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>

--- a/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
+++ b/SeasonsMeridian/supply/Seasons_at_Meridian__Supply_Chart.xlsx
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M61"/>
+  <dimension ref="B2:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2342,7 +2342,7 @@
       <c r="B43" s="28" t="n"/>
       <c r="C43" s="29" t="inlineStr">
         <is>
-          <t>PROPOSED (15 properties, 3,646 units)</t>
+          <t>PROPOSED (13 properties, 3,172 units)</t>
         </is>
       </c>
     </row>
@@ -2352,15 +2352,15 @@
       </c>
       <c r="C44" s="31" t="inlineStr">
         <is>
-          <t>Union 93</t>
+          <t>The Judy (Maple Grove &amp; Overland)</t>
         </is>
       </c>
       <c r="D44" s="32" t="n">
-        <v>350</v>
+        <v>162</v>
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Q3 2026</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="F44" s="33" t="n"/>
@@ -2371,20 +2371,16 @@
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
-          <t>Grey Owl Holdings Llc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I44" s="35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J44" s="30" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="J44" s="30" t="n"/>
       <c r="K44" s="31" t="inlineStr">
         <is>
-          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
         </is>
       </c>
       <c r="M44">
@@ -2398,15 +2394,15 @@
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>The Judy (Maple Grove &amp; Overland)</t>
+          <t>Heritage Square (ex-Union 93)</t>
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>162</v>
+        <v>250</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="F45" s="33" t="n"/>
@@ -2421,12 +2417,12 @@
         </is>
       </c>
       <c r="I45" s="35" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J45" s="30" t="n"/>
       <c r="K45" s="31" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - equity raise underway; construction targeted Q3 2026</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - announced Jul 13 2026; Union 93 skeleton repurposed</t>
         </is>
       </c>
       <c r="M45">
@@ -2440,15 +2436,15 @@
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>Victory Flats</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="F46" s="33" t="n"/>
@@ -2459,20 +2455,20 @@
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I46" s="35" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="J46" s="30" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K46" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - refiled May/Jun 2026 as 6-story 200+ units (PLN26-00493)</t>
         </is>
       </c>
       <c r="M46">
@@ -2486,15 +2482,15 @@
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>The Gateway at Ten Mile</t>
+          <t>Rolling Hill (Assemble Management)</t>
         </is>
       </c>
       <c r="D47" s="32" t="n">
-        <v>390</v>
+        <v>200</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="F47" s="33" t="n"/>
@@ -2505,20 +2501,16 @@
       </c>
       <c r="H47" s="31" t="inlineStr">
         <is>
-          <t>TGI Corp</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I47" s="35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J47" s="30" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J47" s="30" t="n"/>
       <c r="K47" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
       <c r="M47">
@@ -2532,15 +2524,15 @@
       </c>
       <c r="C48" s="31" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>138</v>
+        <v>472</v>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Q1 2029</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F48" s="33" t="n"/>
@@ -2555,7 +2547,7 @@
         </is>
       </c>
       <c r="I48" s="35" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J48" s="30" t="inlineStr">
         <is>
@@ -2564,7 +2556,7 @@
       </c>
       <c r="K48" s="31" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; CUP likely lapsed - Brighton silent 4+ years</t>
         </is>
       </c>
       <c r="M48">
@@ -2578,11 +2570,11 @@
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>472</v>
+        <v>390</v>
       </c>
       <c r="E49" s="30" t="inlineStr">
         <is>
@@ -2597,11 +2589,11 @@
       </c>
       <c r="H49" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TGI Corp</t>
         </is>
       </c>
       <c r="I49" s="35" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
@@ -2610,7 +2602,7 @@
       </c>
       <c r="K49" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed - long-dated; residential 5-7 yrs out per developer</t>
         </is>
       </c>
       <c r="M49">
@@ -2670,11 +2662,11 @@
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
@@ -2689,20 +2681,20 @@
       </c>
       <c r="H51" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="I51" s="35" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J51" s="30" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K51" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed - stalled; Jan 2024 start extension lapsed unbuilt</t>
         </is>
       </c>
       <c r="M51">
@@ -2716,11 +2708,11 @@
       </c>
       <c r="C52" s="31" t="inlineStr">
         <is>
-          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="D52" s="32" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
@@ -2739,12 +2731,16 @@
         </is>
       </c>
       <c r="I52" s="35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J52" s="30" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="J52" s="30" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
       <c r="K52" s="31" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; pre-application only - silent since Apr 2025</t>
         </is>
       </c>
       <c r="M52">
@@ -2758,11 +2754,11 @@
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
         </is>
       </c>
       <c r="D53" s="32" t="n">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E53" s="30" t="inlineStr">
         <is>
@@ -2781,16 +2777,12 @@
         </is>
       </c>
       <c r="I53" s="35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J53" s="30" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="J53" s="30" t="n"/>
       <c r="K53" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
       <c r="M53">
@@ -2804,11 +2796,11 @@
       </c>
       <c r="C54" s="31" t="inlineStr">
         <is>
-          <t>Rolling Hill (Assemble Management)</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
@@ -2827,12 +2819,16 @@
         </is>
       </c>
       <c r="I54" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="30" t="n"/>
+        <v>1.1</v>
+      </c>
+      <c r="J54" s="30" t="inlineStr">
+        <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
       <c r="K54" s="31" t="inlineStr">
         <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; PUD likely lapsed ~Mar 2026 - RV storage still operating</t>
         </is>
       </c>
       <c r="M54">
@@ -2846,11 +2842,11 @@
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="D55" s="32" t="n">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
@@ -2869,7 +2865,7 @@
         </is>
       </c>
       <c r="I55" s="35" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J55" s="30" t="inlineStr">
         <is>
@@ -2878,7 +2874,7 @@
       </c>
       <c r="K55" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed - stalled; entitled site for sale via CBRE at $5.0M</t>
         </is>
       </c>
       <c r="M55">
@@ -2892,11 +2888,11 @@
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>Meridian OZ Apartments</t>
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
@@ -2911,20 +2907,20 @@
       </c>
       <c r="H56" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Peak Capital Investments Llc</t>
         </is>
       </c>
       <c r="I56" s="35" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J56" s="30" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K56" s="31" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed - stalled; downsized to 36u Oct 2024 - entitled site listed then off-market</t>
         </is>
       </c>
       <c r="M56">
@@ -2932,100 +2928,8 @@
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="30" t="n">
-        <v>46</v>
-      </c>
-      <c r="C57" s="31" t="inlineStr">
-        <is>
-          <t>The Cole Denton</t>
-        </is>
-      </c>
-      <c r="D57" s="32" t="n">
-        <v>136</v>
-      </c>
-      <c r="E57" s="30" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F57" s="33" t="n"/>
-      <c r="G57" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J57" s="30" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K57" s="31" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
-        </is>
-      </c>
-      <c r="M57">
-        <f>IFERROR(VALUE(RIGHT(E57,4))*4+MATCH(LEFT(E57,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="30" t="n">
-        <v>47</v>
-      </c>
-      <c r="C58" s="31" t="inlineStr">
-        <is>
-          <t>Meridian OZ Apartments</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="n">
-        <v>60</v>
-      </c>
-      <c r="E58" s="30" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F58" s="33" t="n"/>
-      <c r="G58" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="31" t="inlineStr">
-        <is>
-          <t>Peak Capital Investments Llc</t>
-        </is>
-      </c>
-      <c r="I58" s="35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J58" s="30" t="inlineStr">
-        <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K58" s="31" t="inlineStr">
-        <is>
-          <t>Diligence: proposed</t>
-        </is>
-      </c>
-      <c r="M58">
-        <f>IFERROR(VALUE(RIGHT(E58,4))*4+MATCH(LEFT(E58,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="36" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="36" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Rent ($) = HelloData mix-weighted asking where covered, else market asking (CoStar). Proximity (mi) = straight-line distance from the subject. Est. Delivery drives the Supply &amp; Absorption tab's per-window supply (edit it there or here — they are linked). See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
@@ -3034,11 +2938,11 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B61:K61"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C36:K36"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C43:K43"/>
+    <mergeCell ref="B59:K59"/>
     <mergeCell ref="C29:K29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3388,11 +3292,7 @@
       <c r="S14" s="44" t="n">
         <v>390</v>
       </c>
-      <c r="T14" s="49" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
+      <c r="T14" s="49" t="inlineStr"/>
       <c r="U14" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3414,17 +3314,13 @@
     <row r="15" ht="14.4" customHeight="1">
       <c r="R15" s="43" t="inlineStr">
         <is>
-          <t>Union 93</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="S15" s="44" t="n">
-        <v>350</v>
-      </c>
-      <c r="T15" s="49" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="T15" s="49" t="inlineStr"/>
       <c r="U15" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3446,11 +3342,11 @@
     <row r="16" ht="14.4" customHeight="1">
       <c r="R16" s="43" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="S16" s="44" t="n">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="T16" s="49" t="inlineStr"/>
       <c r="U16" s="49" t="inlineStr">
@@ -3544,17 +3440,13 @@
       </c>
       <c r="R17" s="43" t="inlineStr">
         <is>
-          <t>Victory Flats</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="S17" s="44" t="n">
-        <v>301</v>
-      </c>
-      <c r="T17" s="49" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="T17" s="49" t="inlineStr"/>
       <c r="U17" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3635,11 +3527,11 @@
       </c>
       <c r="R18" s="43" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
         </is>
       </c>
       <c r="S18" s="44" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="T18" s="49" t="inlineStr"/>
       <c r="U18" s="49" t="inlineStr">
@@ -3685,42 +3577,46 @@
         <v>450</v>
       </c>
       <c r="I19" s="52">
-        <f>SUMIFS('Competitive Analysis'!$D$5:$D$58,'Competitive Analysis'!$M$5:$M$58,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$58,"&lt;="&amp;8105)</f>
+        <f>SUMIFS('Competitive Analysis'!$D$5:$D$56,'Competitive Analysis'!$M$5:$M$56,"&gt;="&amp;8102,'Competitive Analysis'!$M$5:$M$56,"&lt;="&amp;8105)</f>
         <v/>
       </c>
       <c r="J19" s="53">
-        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,1)+SUMIFS($S$13:$S$27,$W$13:$W$27,1,$X$13:$X$27,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,1)+SUMIFS($S$13:$S$25,$W$13:$W$25,1,$X$13:$X$25,1)</f>
         <v/>
       </c>
       <c r="K19" s="53">
-        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,2)+SUMIFS($S$13:$S$27,$W$13:$W$27,2,$X$13:$X$27,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,2)+SUMIFS($S$13:$S$25,$W$13:$W$25,2,$X$13:$X$25,1)</f>
         <v/>
       </c>
       <c r="L19" s="53">
-        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,3)+SUMIFS($S$13:$S$27,$W$13:$W$27,3,$X$13:$X$27,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,3)+SUMIFS($S$13:$S$25,$W$13:$W$25,3,$X$13:$X$25,1)</f>
         <v/>
       </c>
       <c r="M19" s="53">
-        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,4)+SUMIFS($S$13:$S$27,$W$13:$W$27,4,$X$13:$X$27,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,4)+SUMIFS($S$13:$S$25,$W$13:$W$25,4,$X$13:$X$25,1)</f>
         <v/>
       </c>
       <c r="N19" s="53">
-        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,5)+SUMIFS($S$13:$S$27,$W$13:$W$27,5,$X$13:$X$27,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,5)+SUMIFS($S$13:$S$25,$W$13:$W$25,5,$X$13:$X$25,1)</f>
         <v/>
       </c>
       <c r="O19" s="53">
-        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,6)+SUMIFS($S$13:$S$27,$W$13:$W$27,6,$X$13:$X$27,1)</f>
+        <f>SUMIFS($S$5:$S$9,$W$5:$W$9,6)+SUMIFS($S$13:$S$25,$W$13:$W$25,6,$X$13:$X$25,1)</f>
         <v/>
       </c>
       <c r="R19" s="43" t="inlineStr">
         <is>
-          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
+          <t>Heritage Square (ex-Union 93)</t>
         </is>
       </c>
       <c r="S19" s="44" t="n">
-        <v>270</v>
-      </c>
-      <c r="T19" s="49" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="T19" s="49" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
       <c r="U19" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3792,13 +3688,17 @@
       </c>
       <c r="R20" s="43" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="S20" s="44" t="n">
-        <v>264</v>
-      </c>
-      <c r="T20" s="49" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="T20" s="49" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
       <c r="U20" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -3877,7 +3777,11 @@
       <c r="S21" s="44" t="n">
         <v>200</v>
       </c>
-      <c r="T21" s="49" t="inlineStr"/>
+      <c r="T21" s="49" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
       <c r="U21" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -4059,11 +3963,11 @@
       </c>
       <c r="R24" s="43" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="S24" s="44" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="T24" s="49" t="inlineStr"/>
       <c r="U24" s="49" t="inlineStr">
@@ -4128,17 +4032,13 @@
       </c>
       <c r="R25" s="43" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>Meridian OZ Apartments</t>
         </is>
       </c>
       <c r="S25" s="44" t="n">
-        <v>138</v>
-      </c>
-      <c r="T25" s="49" t="inlineStr">
-        <is>
-          <t>Q1 2029</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T25" s="49" t="inlineStr"/>
       <c r="U25" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
@@ -4210,32 +4110,6 @@
       </c>
       <c r="O26" s="60">
         <f>IFERROR(O25/N25-1,"")</f>
-        <v/>
-      </c>
-      <c r="R26" s="43" t="inlineStr">
-        <is>
-          <t>The Cole Denton</t>
-        </is>
-      </c>
-      <c r="S26" s="44" t="n">
-        <v>136</v>
-      </c>
-      <c r="T26" s="49" t="inlineStr"/>
-      <c r="U26" s="49" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V26">
-        <f>IFERROR(VALUE(RIGHT(T26,4))*4+MATCH(LEFT(T26,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W26">
-        <f>IF(V26="","",IF(V26&lt;=$Z$1,0,MAX(1,INT((V26-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>IF(U26="All",1,IF(U26="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U26="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
         <v/>
       </c>
     </row>
@@ -4279,32 +4153,6 @@
       </c>
       <c r="O27" s="62">
         <f>IFERROR('Cash Flow (Annual)'!$P$14,"")</f>
-        <v/>
-      </c>
-      <c r="R27" s="43" t="inlineStr">
-        <is>
-          <t>Meridian OZ Apartments</t>
-        </is>
-      </c>
-      <c r="S27" s="44" t="n">
-        <v>60</v>
-      </c>
-      <c r="T27" s="49" t="inlineStr"/>
-      <c r="U27" s="49" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V27">
-        <f>IFERROR(VALUE(RIGHT(T27,4))*4+MATCH(LEFT(T27,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W27">
-        <f>IF(V27="","",IF(V27&lt;=$Z$1,0,MAX(1,INT((V27-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>IF(U27="All",1,IF(U27="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U27="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
         <v/>
       </c>
     </row>
@@ -5372,7 +5220,7 @@
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bear only,Bear+Base,All,None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5386,7 +5234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7196,19 +7044,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ascent Overland</t>
+          <t>The Cole Denton</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11101 W Overland Rd</t>
+          <t>580 N Cole Rd</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>138</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2028</v>
+        <v>200</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -7229,35 +7074,32 @@
       <c r="N34" s="82" t="n"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>RealPage</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - refiled May/Jun 2026 as 6-story 200+ units (PLN26-00493)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>The Gateway at Ten Mile</t>
+          <t>Rolling Hill (Assemble Management)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2954 W Franklin Rd</t>
+          <t>4270 E Overland Rd, Meridian 83642</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>390</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2027</v>
+        <v>200</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7274,35 +7116,32 @@
       <c r="N35" s="82" t="n"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Victory Flats</t>
+          <t>Heritage Square (ex-Union 93)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8373 West Victory Rd</t>
+          <t>SE corner Main St &amp; Broadway Ave, Meridian 83642</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>301</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2027</v>
+        <v>250</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q1 2029</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7319,12 +7158,12 @@
       <c r="N36" s="82" t="n"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed - announced Jul 13 2026; Union 93 skeleton repurposed</t>
         </is>
       </c>
     </row>
@@ -7373,25 +7212,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Union 93</t>
+          <t>Meridian OZ Apartments</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>221-225 E Broadway Ave</t>
+          <t>1475 E Franklin Rd</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>350</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7411,24 +7243,28 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Diligence: stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
+          <t>Diligence: proposed - stalled; downsized to 36u Oct 2024 - entitled site listed then off-market</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Meridian OZ Apartments</t>
+          <t>The Gateway at Ten Mile</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1475 E Franklin Rd</t>
+          <t>2954 W Franklin Rd</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>60</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7443,29 +7279,33 @@
       <c r="N39" s="82" t="n"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Diligence: proposed</t>
+          <t>Diligence: proposed - long-dated; residential 5-7 yrs out per developer</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>The Cole Denton</t>
+          <t>Ascent Overland</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>580 N Cole Rd</t>
+          <t>11101 W Overland Rd</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>136</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7480,29 +7320,33 @@
       <c r="N40" s="82" t="n"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed - stalled; entitled site for sale via CBRE at $5.0M</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Victory Flats</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>E Fairview Ave &amp; N Records Way</t>
+          <t>8373 West Victory Rd</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>472</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7517,29 +7361,30 @@
       <c r="N41" s="82" t="n"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>Diligence: proposed - stalled; Jan 2024 start extension lapsed unbuilt</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cobalt Point</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S Cobalt Point Way &amp; E Copper Point Dr</t>
+          <t>E Fairview Ave &amp; N Records Way</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>264</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7559,24 +7404,25 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; CUP likely lapsed - Brighton silent 4+ years</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>12548 West Overland Road</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1005 E Fairview Ave</t>
+          <t>12548 W Overland Rd</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>150</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7587,12 +7433,8 @@
       <c r="J43" s="81" t="n"/>
       <c r="K43" s="82" t="n"/>
       <c r="L43" s="82" t="n"/>
-      <c r="M43" s="82" t="n">
-        <v>1837.580964685616</v>
-      </c>
-      <c r="N43" s="82" t="n">
-        <v>1837.580964685616</v>
-      </c>
+      <c r="M43" s="82" t="n"/>
+      <c r="N43" s="82" t="n"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7600,24 +7442,25 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; PUD likely lapsed ~Mar 2026 - RV storage still operating</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12548 West Overland Road</t>
+          <t>12565 West Fairview Avenue</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12548 W Overland Rd</t>
+          <t>12565 W Fairview Ave</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>156</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7637,23 +7480,23 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
+          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed - stalled; pre-application only - silent since Apr 2025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12565 West Fairview Avenue</t>
+          <t>Syringa Crossing</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12565 W Fairview Ave</t>
+          <t>Amity Ave &amp; Meridian Rd</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7681,16 +7524,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Syringa Crossing</t>
+          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amity Ave &amp; Meridian Rd</t>
+          <t>E Pine Ave &amp; N Webb Way, Meridian 83642</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7706,84 +7549,10 @@
       <c r="N46" s="82" t="n"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar); Diligence: proposed</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Rolling Hill (Assemble Management)</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>4270 E Overland Rd, Meridian 83642</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>200</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="H47" s="81" t="n"/>
-      <c r="I47" s="81" t="n"/>
-      <c r="J47" s="81" t="n"/>
-      <c r="K47" s="82" t="n"/>
-      <c r="L47" s="82" t="n"/>
-      <c r="M47" s="82" t="n"/>
-      <c r="N47" s="82" t="n"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Diligence</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Pine 43 Multifamily (Pine &amp; Webb)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>E Pine Ave &amp; N Webb Way, Meridian 83642</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>270</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="H48" s="81" t="n"/>
-      <c r="I48" s="81" t="n"/>
-      <c r="J48" s="81" t="n"/>
-      <c r="K48" s="82" t="n"/>
-      <c r="L48" s="82" t="n"/>
-      <c r="M48" s="82" t="n"/>
-      <c r="N48" s="82" t="n"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Diligence</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
         <is>
           <t>Analyst-sourced deal (not in CoStar/RealPage); Diligence: proposed</t>
         </is>
@@ -7800,7 +7569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H44"/>
+  <dimension ref="B2:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -7893,16 +7662,20 @@
           <t>472</t>
         </is>
       </c>
-      <c r="D5" s="84" t="n"/>
+      <c r="D5" s="84" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E5" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; CUP likely lapsed - Brighton silent 4+ years</t>
         </is>
       </c>
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>Brighton Corporation's 'Records': 472 urban-style units (84 studio/208 1BR/168 2BR/12 3BR) on ~10 ac at the NE corner of Fairview Ave &amp; Records Way adjacent to CarMax, proposed Feb 2022, two phases; Brighton's leasing site lists it 'coming soon' but no construction start could be independently confirmed.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). CUP H-2022-0008 heard Apr 7 2022 (staff conditioned approval on cutting to ~40 du/ac ≈ 398u vs 472 proposed); NO CZC, permit, extension, or hearing step since, and Meridian permit reports through Apr 2026 show nothing at Records Way. Under Meridian's 2-yr CUP commencement rule the entitlement has very likely expired — would need re-entitlement. Brighton's page has said 'coming soon' for 4+ years while its news feed promotes everything else. Not verifiably dead (no site sale found) — Bear-only, undated.</t>
         </is>
       </c>
       <c r="H5" s="43" t="inlineStr">
@@ -7958,13 +7731,13 @@
       <c r="D7" s="84" t="n"/>
       <c r="E7" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>withdrawn - applicant withdrew CUP H-2022-0042 on Dec 1 2022; never re-filed</t>
         </is>
       </c>
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>264 units on ~13 ac east of E Copper Point Dr &amp; S Cobalt Point Way (Silverstone Park area near Eagle/Overland — NOT Ten Mile Crossing as RealPage implies), application prepared by The Land Group (BoiseDev June 2022); a marketing domain is indexed but the current stage could not be verified.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). DEAD: The Land Group's 264u CUP (H-2022-0042, 11.95 ac C-G parcel R7909850396 east of S Cobalt Point Way) was continued from 10/20/2022 and formally WITHDRAWN by the applicant at the 12/1/2022 P&amp;Z meeting — never approved. No re-application in 3.5 years, no permits, cobaltpointmeridian.com no longer resolves (DNS dead, verified 7/16/2026), and the land was marketed for office/mixed-use. RealPage's Ten Mile framing confuses it with Flats/Lofts at Ten Mile on W Cobalt Dr. Dropped; at most Bear-case shadow LAND, not a project.'</t>
         </is>
       </c>
       <c r="H7" s="43" t="inlineStr">
@@ -8018,7 +7791,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>Hawkins Companies' plan at Amity &amp; Meridian Rd is still in hearings: P&amp;Z recommended denial April 2026, and on June 17 2026 City Council unanimously remanded the revised plan (more office/retail, fewer homes) back to P&amp;Z — no final approval; the 322-unit count may shrink. Bear-case supply only. Land-use dossier SM-12 covers the adjacent block.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Status unchanged and current: P&amp;Z recommended denial Apr 2 2026; council unanimously REMANDED the revised plan (up to 400 homes, more office/retail, ITD right-in/right-out granted on SH-69) back to P&amp;Z on 6/17/2026; no re-hearing outcome as of 7/16/2026 and staff still say revisions don't cure comp-plan inconsistencies. Hawkins still markets the corners as a 'proposed' shopping center. No annexation, plat, or permits — Bear-case only with elevated kill risk; earliest delivery ~2029 if it survives. Land-use dossier SM-12 covers the adjacent block.</t>
         </is>
       </c>
       <c r="H9" s="43" t="inlineStr">
@@ -8035,19 +7808,23 @@
       </c>
       <c r="C10" s="84" t="inlineStr">
         <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="D10" s="84" t="n"/>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D10" s="84" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
       <c r="E10" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - refiled May/Jun 2026 as 6-story 200+ units (PLN26-00493)</t>
         </is>
       </c>
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>136-unit five-story mixed-use (retail/self-storage/apartments) approved May 2021 as Boise's first Housing Bonus Ordinance project; the building permit submitted Sept 2022 was still 'in corrections' Jan 2023 and the 2.13-ac site is now listed for sale — stalled. Distinct from the delivered 191-unit Denton Apartments (Pacific Companies, Curtis Rd, opened Dec 2025).</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Stale in BOTH directions: the 136u plan got further than believed — $11.2M foundation/podium permit BLD22-03293 was ISSUED 4/5/2024 — but was never built and EXPIRED 3/31/2026 (parcel S1007325725 still vacant land, $2.78M, on the 2026 roll). Then in May/Jun 2026 a NEW filing appeared on the same 2.13-ac MX-3/DA parcel: PLN26-00493 '580 N COLE RD - DRH', a six-story mixed-use building with 200+ apartments (sponsor almost certainly Kal Pacific), at neighborhood-meeting/design-review stage (tracker 6/15/2026). LoopNet listing off-market. Live early-stage ~200u proposal; delivery 2029+; do NOT promote to UC. City separately buying neighboring 709 N Cole for affordable housing.</t>
         </is>
       </c>
       <c r="H10" s="43" t="inlineStr">
@@ -8067,16 +7844,20 @@
           <t>275</t>
         </is>
       </c>
-      <c r="D11" s="84" t="n"/>
+      <c r="D11" s="84" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E11" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; pre-application only - silent since Apr 2025</t>
         </is>
       </c>
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>275 units in 4-5 story buildings over a ground-floor garage proposed on the 4.7-ac stalled AutoNation USA dealership site (AutoNation still owner; PivotNorth architect); early application / neighborhood-meeting stage per April 2025 reporting — no approval, permit, or construction as of July 2026. Sits on land-use developable parcel S1109110516.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Never verifiably advanced past pre-application/neighborhood-meeting stage (Apr 2025); no application, hearing, approval, or permit since — ~15 months of silence. Mar 2026 city permit report shows nothing at the address; absent from BoiseDev's Feb 2026 zoning-year recap of 2025 approvals. AutoNation still owner, site not re-listed. Bear-only shadow. Sits on land-use developable parcel S1109110516.</t>
         </is>
       </c>
       <c r="H11" s="43" t="inlineStr">
@@ -8096,16 +7877,20 @@
           <t>156</t>
         </is>
       </c>
-      <c r="D12" s="84" t="n"/>
+      <c r="D12" s="84" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E12" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; PUD likely lapsed ~Mar 2026 - RV storage still operating</t>
         </is>
       </c>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>Hook Family Trust (San Clemente CA) won PUD approval ~March 2024 to replace Overland RV Storage with five 4-story buildings, 156 units (84 1BR/72 2BR) + ~6,000 sf retail; as of mid-2026 the RV storage still operates and the entitled site is marketed for sale on LoopNet — no construction start.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Built-to-sell entitlement drifting toward dead: PUD approved 3/12/2024 and the site was listed on LoopNet THE SAME WEEK (3/4/2024); listing since pulled with no evidence of sale (Ada Cty roll still bare 5.4-ac commercial parcel, $2.66M). Boise PUD approvals lapse 24 months absent construction =&gt; likely expired ~Mar 2026; no permit through June 2026. Overland RV Storage still operating with active waiting lists (site live; Yelp updated Jun 2026). Bear-only.</t>
         </is>
       </c>
       <c r="H12" s="43" t="inlineStr">
@@ -8222,19 +8007,23 @@
       </c>
       <c r="C17" s="84" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D17" s="84" t="n"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D17" s="84" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E17" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; downsized to 36u Oct 2024 - entitled site listed then off-market</t>
         </is>
       </c>
       <c r="F17" s="43" t="n"/>
       <c r="G17" s="43" t="inlineStr">
         <is>
-          <t>CUP H-2022-0073 (Realm Venture Group): 60 units (30x1BR + 30x2BR) in five 3-story 12-plexes at 1475 E Franklin Rd, SWC Franklin &amp; Locust Grove; hearing record indicates the approval motion carried (early 2023) but no construction evidence found. Land-use dossier SM-155.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). 60u plan never built; entitlement MODIFIED DOWN to 36 units Oct 2024 (MCU-2024-0002, Pivot North; findings adopted 10/17/2024). Owner then listed the 2.39-ac site at $1.7M as a 'fully entitled' OZ development opportunity (IMLS 98949803); listing went PENDING, now off-market as of 7/16/2026 — sale closed or withdrawn, no new owner/permit surfaced; no building permit in Meridian reports. Sponsor Realm's other Meridian project was denied Nov 2024 (winding down). Bear-only at 36u, undated.</t>
         </is>
       </c>
       <c r="H17" s="43" t="inlineStr">
@@ -8253,18 +8042,18 @@
       <c r="D18" s="84" t="n"/>
       <c r="E18" s="43" t="inlineStr">
         <is>
-          <t>stalled - foreclosure since Nov 2022; no restart as of Jul 2026</t>
+          <t>dead - foreclosed &amp; sold at auction Oct 2025; superseded by Heritage Square</t>
         </is>
       </c>
       <c r="F18" s="43" t="n"/>
       <c r="G18" s="43" t="inlineStr">
         <is>
-          <t>Galena Opportunity Fund's two-building ~385-unit Union 93 East/West at Main &amp; Broadway (downtown Meridian) stalled Nov 2022 after contractors went unpaid; the project entered foreclosure amid litigation and no evidence shows construction resumed — CoStar's 'under construction / Q3 2026 delivery' is stale. Demoted to proposed (Bear-case toggle); monitor for a post-foreclosure restart.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Union 93 is definitively dead: Galena's project stalled late 2022 under $20M+ contractor liens, went through foreclosure, and the property was SOLD at an Ada County Sheriff's auction Oct 2025 to Ahlquist (Gray Owl) + Pacific Companies. Dropped from the competitive set; the successor project is tracked as 'Heritage Square (ex-Union 93)' — ~250u, announced 7/13/2026.</t>
         </is>
       </c>
       <c r="H18" s="43" t="inlineStr">
         <is>
-          <t>https://www.yahoo.com/news/ambitious-downtown-meridian-development-foreclosure-160323894.html</t>
+          <t>https://boisedev.com/news/2025/10/09/ahlquist-pacific-companies-union-93-meridian/</t>
         </is>
       </c>
     </row>
@@ -8279,16 +8068,20 @@
           <t>301</t>
         </is>
       </c>
-      <c r="D19" s="84" t="n"/>
+      <c r="D19" s="84" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E19" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; Jan 2024 start extension lapsed unbuilt</t>
         </is>
       </c>
       <c r="F19" s="43" t="n"/>
       <c r="G19" s="43" t="inlineStr">
         <is>
-          <t>Welltower's 301-unit apartment/townhome/SFR rental project at 8373 W Victory Rd (former Boise School District land, SW Boise) approved by Boise City Council March 8 2022 with first units once hoped for late 2023; no groundbreaking, permits, or leasing evidence through mid-2026 — CoStar's Q3 2028 delivery is unsupported.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Approved Mar 2022; real permitting-stage effort followed (submittals, Idaho Power payments, ACHD/Veolia coordination) but Jan 2024 Welltower took a cost-driven TWO-YEAR extension to start construction — that window has now run out with no permit ever issued at 8373 W Victory Rd (city open-data through June 2026). BoiseDev tracker stale since Feb 2022; Welltower still owns. Bear-only; CoStar's Q3 2028 has no support.</t>
         </is>
       </c>
       <c r="H19" s="43" t="inlineStr">
@@ -8333,16 +8126,20 @@
           <t>390</t>
         </is>
       </c>
-      <c r="D21" s="84" t="n"/>
+      <c r="D21" s="84" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E21" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - long-dated; residential 5-7 yrs out per developer</t>
         </is>
       </c>
       <c r="F21" s="43" t="n"/>
       <c r="G21" s="43" t="inlineStr">
         <is>
-          <t>Approved unanimously Nov 2024 (H-2024-0010): 390 units (200 1BR/174 2BR/16 3BR) in six 4-story buildings plus townhomes and 15 commercial buildings at Ten Mile &amp; Franklin; the developer said commercial phases come first and residential is 5-7 years out — CoStar's Q4 2028 delivery looks optimistic. Supersedes the old 559-unit 'The 10' on the same site.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Entitlement live (H-2024-0010, Nov 2024) and the COMMERCIAL phase is being marketed (MJPCRE retail pad ground-lease campaign, Nov 2025) — but developer told council residential is 'at least five to seven years out' (~2030-2032) and no residential permits/plats exist through June 2026. IDENTITY WARNING: the June 2026 C-MULTI-2025-0023/24/25 permits at Franklin &amp; Ten Mile are OUTER BANKS (516u, SW corner) — do NOT attribute to Gateway. Bear-only; discard CoStar's Q4 2028.</t>
         </is>
       </c>
       <c r="H21" s="43" t="inlineStr">
@@ -8362,16 +8159,20 @@
           <t>138</t>
         </is>
       </c>
-      <c r="D22" s="84" t="n"/>
+      <c r="D22" s="84" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="E22" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed - stalled; entitled site for sale via CBRE at $5.0M</t>
         </is>
       </c>
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>MVRK Development (Denver) 138-unit two-building project near Overland &amp; Cloverdale (West Boise, not Meridian) approved 5-1 by Boise City Council Nov 2023; MVRK's own projects page (July 2026) still lists planning-stage 'TBD' timing — no construction reported.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Approved 5-1 Nov 2023 (11880 W Overland Rd, ~3.5 ac); 2.5+ yrs later no permit, no groundbreaking, and MVRK's own projects page still says 'TBD' (checked 7/16/2026). The site is marketed FOR SALE as a 'fully entitled development opportunity' at $4,999,999 with CBRE (MLS 98945418) — sponsor exiting, not building. Feb 2025 ConstructConnect record still 'Design' stage. Bear-only; delivery depends on a hypothetical buyer.</t>
         </is>
       </c>
       <c r="H22" s="43" t="inlineStr">
@@ -8394,13 +8195,13 @@
       <c r="D23" s="84" t="n"/>
       <c r="E23" s="43" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>withdrawn - CUP H-2023-0001 withdrawn Jun 15 2023; site re-tenanted as RV dealership Apr 2024</t>
         </is>
       </c>
       <c r="F23" s="43" t="n"/>
       <c r="G23" s="43" t="inlineStr">
         <is>
-          <t>Biltmore Co. / Pivot North Architecture application (Jan 2023) for 150 market-rate units (1-3BR, 797-1,872 sf, 2-3 story buildings) at 1005 E Fairview Ave; still needs Meridian P&amp;Z and City Council approval — no hearing date found, no construction.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). DEAD: Biltmore/Pivot North's 150u CUP (H-2023-0001, 8.25 ac C-G at 1005 E Fairview) was WITHDRAWN by the applicant at the 6/15/2023 P&amp;Z hearing before any vote. The 20k sf ex-dealership building was marketed for retail lease Jan 2024 and the city issued occupancy permit C-CO-2024-0029 on 4/10/2024 to Uncharted Recreation (RV/golf-cart dealership), still operating mid-2026. Biltmore's 'coming soon' page is a stale placeholder. Dropped; C-G zoning would allow a future resubmittal — shadow footnote only.</t>
         </is>
       </c>
       <c r="H23" s="43" t="inlineStr">
@@ -8458,7 +8259,7 @@
       <c r="F25" s="43" t="n"/>
       <c r="G25" s="43" t="inlineStr">
         <is>
-          <t>Hawkins Companies OM (July 2026, research/oms/): 162-unit Class A garden (75x1BR $1,615 / 60x2BR / 27x3BR, avg $1,787 at 908sf) on 6.13 ac at 1770 S Maple Grove Rd, Boise — 3.4 mi from subject, inside the 5-mi ring. $41.7M TPC, GMP contract, construction targeted Q3 2026; OM lease-up: first occupancy month ~18 (=&gt; ~Q1 2028 first units), 20 units/mo absorption, ~42% occupied Yr 2. NOT tracked by CoStar or RealPage. Land-use analysis site 177: parcel S1124223215 in the developable-vacant set but zoned R-2 (Medium MF-threat, conditional) with 'single-family oriented' FLU — the OM proves the conditional path being exercised; reclassify from latent to tracked pipeline.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Fully entitled (council Sep 2024; DRH24-00090 refined 174→162u per city Aug 2025 Development Trends). Hawkins closed land Oct 2024, CDs complete Apr 2026, live $12.4M LP equity raise targeting Q3 2026 start. OM schedule: building permit ESTIMATED TO ISSUE ~7/21/2026; first CofO Aug 2027, last Apr 2028; 20u/mo lease-up =&gt; ~Q1 2028 first meaningful units. No permit in city lists through 6/30/2026 — stays PROPOSED. RE-CHECK Aug-Sep 2026: likely UC promotion if the raise closes. Capitalization is the timing risk. Land-use site 177 / parcel S1124223215 — conditional R-2 path being exercised.</t>
         </is>
       </c>
       <c r="H25" s="43" t="inlineStr">
@@ -8478,7 +8279,11 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D26" s="84" t="n"/>
+      <c r="D26" s="84" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
       <c r="E26" s="43" t="inlineStr">
         <is>
           <t>proposed</t>
@@ -8487,7 +8292,7 @@
       <c r="F26" s="43" t="n"/>
       <c r="G26" s="43" t="inlineStr">
         <is>
-          <t>AUDIT FIND (July 2026): annexation + DA APPROVED 5-1 on 5/19/2026 (after a 2024 denial of the 154u version) — 200 units in 3-story buildings + ~19.5k sf ground-floor commercial at NE corner Overland Rd &amp; Rolling Hill Dr (4270 E Overland), ~1.0 mi from subject. CA developer; no permits yet; in NEITHER CoStar nor RealPage.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Annexation + rezone + DA approved 5-1 on 5/19/2026 (200u over ~19.5-20k sf commercial, four 3-story bldgs; up from the 184u resubmittal after the 2024 denial). DA recording + CZC/design review still ahead of permits =&gt; vertical realistically late 2026 at earliest, first units unlikely before late 2028 (~Q1 2029). Old LoopNet land listing inactive (assemblage complete); 7 of 10 adjacent owners gave letters of intent to sell. Keep PROPOSED — live pipeline.</t>
         </is>
       </c>
       <c r="H26" s="43" t="inlineStr">
@@ -8516,7 +8321,7 @@
       <c r="F27" s="43" t="n"/>
       <c r="G27" s="43" t="inlineStr">
         <is>
-          <t>AUDIT FIND: CUP H-2024-0071 APPROVED 10/21/2025 — 270 conventional MF units in two buildings (6.28 ac C-G, 76-ft height) at E Pine Ave &amp; N Webb Way; master plan allows up to 904 units + hotel over 10-12 yrs. 2-yr CUP commencement clock; groundbreak &gt;=2027. Distinct from the existing 25u 'Pine 43' comp. Not in CoStar/RealPage.</t>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). CUP H-2024-0071 live (approved 10/21/2025; commencement clock to ~Oct 2027); no appeal, foreclosure, or listing. DRB Investments says no groundbreak before 2027, townhomes first, ~$1B/900+u build-out phased 10-12 yrs. Only 2026 Pine 43 permits are SF/townhome + a monument sign — no MF permit through June 2026. Keep PROPOSED, undated; earliest plausible MF delivery ~2029. Distinct from the existing 25u 'Pine 43' comp.</t>
         </is>
       </c>
       <c r="H27" s="43" t="inlineStr">
@@ -8591,84 +8396,92 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="83" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>Heritage Square (ex-Union 93)</t>
+        </is>
+      </c>
+      <c r="C30" s="84" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D30" s="84" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
+      <c r="E30" s="43" t="inlineStr">
+        <is>
+          <t>proposed - announced Jul 13 2026; Union 93 skeleton repurposed</t>
+        </is>
+      </c>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="43" t="inlineStr">
+        <is>
+          <t>DEEP-DIVE VERIFIED 7/16/2026 (all verdicts survived 3-lens adversarial check). Tommy Ahlquist (Gray Owl Holdings) + The Pacific Companies bought the failed Union 93 block at the Ada County Sheriff's foreclosure auction Oct 2025 and on 7/13/2026 announced Heritage Square: the existing concrete skeleton repurposed into TWO residential towers totaling ~250 units + 120k sf Class A office + 32k sf retail (Babcock Design; McAlvain GC). Owners hope to start late 2026/early 2027, 20-24 mo buildout =&gt; ~Q1 2029. No permits issued yet — PROPOSED. Replaces the dead Union 93 row (dropped; see its diligence entry).</t>
+        </is>
+      </c>
+      <c r="H30" s="43" t="inlineStr">
+        <is>
+          <t>https://boisedev.com/news/2026/07/13/union-93-heritage-square-meridian-ahlquist-pacific-companies/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="83" t="inlineStr">
         <is>
           <t>SHADOW SUPPLY (latent / untracked — watch list)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="50" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="50" t="inlineStr">
         <is>
           <t>Property / Site</t>
         </is>
       </c>
-      <c r="C32" s="50" t="inlineStr">
+      <c r="C33" s="50" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D32" s="50" t="inlineStr">
+      <c r="D33" s="50" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="E32" s="50" t="inlineStr">
+      <c r="E33" s="50" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F32" s="50" t="inlineStr">
+      <c r="F33" s="50" t="inlineStr">
         <is>
           <t>Leasing Pace</t>
         </is>
       </c>
-      <c r="G32" s="50" t="inlineStr">
+      <c r="G33" s="50" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="H32" s="50" t="inlineStr">
+      <c r="H33" s="50" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="43" t="inlineStr">
-        <is>
-          <t>Emblem Meridian (Quarterra) / Artisan Victory Market site</t>
-        </is>
-      </c>
-      <c r="C33" s="84" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="D33" s="84" t="n"/>
-      <c r="E33" s="43" t="n"/>
-      <c r="F33" s="43" t="n"/>
-      <c r="G33" s="43" t="inlineStr">
-        <is>
-          <t>Land-use analysis site SM-76: ~12-ac BPS Eagle Road LLC assemblage on S Eagle Rd. 'Artisan Victory Market' (H-2022-0066) approved 2023 for 131 build-to-rent units + commercial but never built; superseded by Quarterra's 'Emblem Meridian' ~250-unit concept (pre-application June 2026). Closest large latent MF site to the subject (~1 mi).</t>
-        </is>
-      </c>
-      <c r="H33" s="43" t="inlineStr">
-        <is>
-          <t>https://boisedev.com/news/2026/06/10/meridian-emblem-victory-eagle-homes-apartment/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="43" t="inlineStr">
         <is>
-          <t>Tanner Creek apartments (Waltman/Johnson Ln)</t>
+          <t>Emblem Meridian (Quarterra) / Artisan Victory Market site</t>
         </is>
       </c>
       <c r="C34" s="84" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D34" s="84" t="n"/>
@@ -8676,24 +8489,24 @@
       <c r="F34" s="43" t="n"/>
       <c r="G34" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-15: Tanner Creek (heard Nov 2023; moved forward) — 83 SF homes + 45 townhomes + 280 phased apartments on ~38 ac, paired with ~30-ac Hawkins commercial between I-84 and Waltman Ln. Residential now being built by CBH Homes; the 280-unit apartment component is latent supply not yet in the CoStar/RealPage pipeline.</t>
+          <t>Land-use analysis site SM-76: ~12-ac BPS Eagle Road LLC assemblage on S Eagle Rd. 'Artisan Victory Market' (H-2022-0066) approved 2023 for 131 build-to-rent units + commercial but never built; superseded by Quarterra's 'Emblem Meridian' ~250-unit concept (pre-application June 2026). Closest large latent MF site to the subject (~1 mi).</t>
         </is>
       </c>
       <c r="H34" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2023/11/28/plans-for-two-large-developments-off-i-84-and-meridian-rd-move-forward/</t>
+          <t>https://boisedev.com/news/2026/06/10/meridian-emblem-victory-eagle-homes-apartment/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="43" t="inlineStr">
         <is>
-          <t>Graycliff Estates R-40 block</t>
+          <t>Tanner Creek apartments (Waltman/Johnson Ln)</t>
         </is>
       </c>
       <c r="C35" s="84" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>280</t>
         </is>
       </c>
       <c r="D35" s="84" t="n"/>
@@ -8701,40 +8514,44 @@
       <c r="F35" s="43" t="n"/>
       <c r="G35" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-3: Graycliff Estates (Star Development) approved preliminary plat of ~200 SF homes PLUS 224 apartments (R-40 high-density block) on ~52 ac; SF portion building since 2021. The 224-unit apartment block remains unbuilt latent supply.</t>
+          <t>Land-use analysis site SM-15: Tanner Creek (heard Nov 2023; moved forward) — 83 SF homes + 45 townhomes + 280 phased apartments on ~38 ac, paired with ~30-ac Hawkins commercial between I-84 and Waltman Ln. Residential now being built by CBH Homes; the 280-unit apartment component is latent supply not yet in the CoStar/RealPage pipeline.</t>
         </is>
       </c>
       <c r="H35" s="43" t="inlineStr">
         <is>
-          <t>https://www.weknowboise.com/graycliff-estates.php</t>
+          <t>https://boisedev.com/news/2023/11/28/plans-for-two-large-developments-off-i-84-and-meridian-rd-move-forward/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="43" t="inlineStr">
         <is>
-          <t>Touchmark Meadow Lake Village expansion</t>
-        </is>
-      </c>
-      <c r="C36" s="84" t="n"/>
+          <t>Graycliff Estates R-40 block</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
       <c r="D36" s="84" t="n"/>
       <c r="E36" s="43" t="n"/>
       <c r="F36" s="43" t="n"/>
       <c r="G36" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-9: ~64 undeveloped ac of Touchmark's ~121-ac senior community. July 2025 development-modification agreement + rezone + PUD in progress to a broader 'Touchmark Mixed Use' (mixed housing types). Senior-oriented, but adds rental housing capacity 1.5 mi from subject.</t>
+          <t>Land-use analysis site SM-3: Graycliff Estates (Star Development) approved preliminary plat of ~200 SF homes PLUS 224 apartments (R-40 high-density block) on ~52 ac; SF portion building since 2021. The 224-unit apartment block remains unbuilt latent supply.</t>
         </is>
       </c>
       <c r="H36" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2025/07/14/touchmark-meridian-meadowlake-mixed-use/</t>
+          <t>https://www.weknowboise.com/graycliff-estates.php</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="43" t="inlineStr">
         <is>
-          <t>Ten Mile Crossing residual HDR parcels</t>
+          <t>Touchmark Meadow Lake Village expansion</t>
         </is>
       </c>
       <c r="C37" s="84" t="n"/>
@@ -8743,19 +8560,19 @@
       <c r="F37" s="43" t="n"/>
       <c r="G37" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-4: residential portion (R-15/R-8) of Brighton's Ten Mile Crossing at SW Overland &amp; Ten Mile — partially built (Cortland South Meridian + CBH SF); remaining High-Density Residential parcels planned/dormant, including an 8.6-ac and a 14.4-ac R-15 vacant parcel (highest-interest sites in the land-use ranking). Note: South Ridge II (164u UC, tracked in the chart) is rising in this same corridor.</t>
+          <t>Land-use analysis site SM-9: ~64 undeveloped ac of Touchmark's ~121-ac senior community. July 2025 development-modification agreement + rezone + PUD in progress to a broader 'Touchmark Mixed Use' (mixed housing types). Senior-oriented, but adds rental housing capacity 1.5 mi from subject.</t>
         </is>
       </c>
       <c r="H37" s="43" t="inlineStr">
         <is>
-          <t>https://www.brighton.co/brighton-place/ten-mile-crossing/</t>
+          <t>https://boisedev.com/news/2025/07/14/touchmark-meridian-meadowlake-mixed-use/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="43" t="inlineStr">
         <is>
-          <t>Brighton Apex R-15 parcel (Lake Hazel)</t>
+          <t>Ten Mile Crossing residual HDR parcels</t>
         </is>
       </c>
       <c r="C38" s="84" t="n"/>
@@ -8764,19 +8581,19 @@
       <c r="F38" s="43" t="n"/>
       <c r="G38" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-61: 15.1-ac R-15 (med-high-density) parcel on E Lake Hazel Rd inside Brighton's approved Apex/Pinnacle master-plan footprint; adjacent phases actively building. Latent MF-capable ground in the fast-growing S Meridian corridor.</t>
+          <t>Land-use analysis site SM-4: residential portion (R-15/R-8) of Brighton's Ten Mile Crossing at SW Overland &amp; Ten Mile — partially built (Cortland South Meridian + CBH SF); remaining High-Density Residential parcels planned/dormant, including an 8.6-ac and a 14.4-ac R-15 vacant parcel (highest-interest sites in the land-use ranking). Note: South Ridge II (164u UC, tracked in the chart) is rising in this same corridor.</t>
         </is>
       </c>
       <c r="H38" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2024/12/20/brighton-pinnacle-costco-meridian/</t>
+          <t>https://www.brighton.co/brighton-place/ten-mile-crossing/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="43" t="inlineStr">
         <is>
-          <t>Outer Banks Subdivision (TM Creek / Cobalt Dr)</t>
+          <t>Brighton Apex R-15 parcel (Lake Hazel)</t>
         </is>
       </c>
       <c r="C39" s="84" t="n"/>
@@ -8785,49 +8602,45 @@
       <c r="F39" s="43" t="n"/>
       <c r="G39" s="43" t="inlineStr">
         <is>
-          <t>Land-use analysis site SM-1: Ten Mile/I-84 high-density employment/mixed-use core (TMISAP) with heavy MF already delivered (Flats/Lofts/Cortland at Ten Mile). Outer Banks Subdivision approved 2021; balance of the ~198-ac district planned — further MF phases likely alongside the tracked pipeline.</t>
+          <t>Land-use analysis site SM-61: 15.1-ac R-15 (med-high-density) parcel on E Lake Hazel Rd inside Brighton's approved Apex/Pinnacle master-plan footprint; adjacent phases actively building. Latent MF-capable ground in the fast-growing S Meridian corridor.</t>
         </is>
       </c>
       <c r="H39" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2021/12/17/outer-banks-pera-place/</t>
+          <t>https://boisedev.com/news/2024/12/20/brighton-pinnacle-costco-meridian/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="43" t="inlineStr">
         <is>
-          <t>Grandview Communities (Lake Hazel &amp; Linder)</t>
-        </is>
-      </c>
-      <c r="C40" s="84" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>Outer Banks Subdivision (TM Creek / Cobalt Dr)</t>
+        </is>
+      </c>
+      <c r="C40" s="84" t="n"/>
       <c r="D40" s="84" t="n"/>
       <c r="E40" s="43" t="n"/>
       <c r="F40" s="43" t="n"/>
       <c r="G40" s="43" t="inlineStr">
         <is>
-          <t>AUDIT WATCH: 79-ac pre-application (July 2025) at NE corner Lake Hazel &amp; Linder — ~510 homes incl. ~130 apartments + 176 TH/cluster; no formal H-file or hearing yet; sits near the southern ring edge (~4.5 mi).</t>
+          <t>Land-use analysis site SM-1: Ten Mile/I-84 high-density employment/mixed-use core (TMISAP) with heavy MF already delivered (Flats/Lofts/Cortland at Ten Mile). Outer Banks Subdivision approved 2021; balance of the ~198-ac district planned — further MF phases likely alongside the tracked pipeline.</t>
         </is>
       </c>
       <c r="H40" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2025/07/07/hundreds-of-homes-apartments-planned-for-lake-hazel-and-linder/</t>
+          <t>https://boisedev.com/news/2021/12/17/outer-banks-pera-place/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="43" t="inlineStr">
         <is>
-          <t>Discovery project (Lake Hazel &amp; Locust Grove)</t>
+          <t>Grandview Communities (Lake Hazel &amp; Linder)</t>
         </is>
       </c>
       <c r="C41" s="84" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D41" s="84" t="n"/>
@@ -8835,40 +8648,44 @@
       <c r="F41" s="43" t="n"/>
       <c r="G41" s="43" t="inlineStr">
         <is>
-          <t>AUDIT WATCH: April 2024 pre-application for 200+ units (nine 3-story buildings + TH/SFR) on ~20 ac by Discovery Park; no formal application since — dormant but the land is teed up (~3.5 mi).</t>
+          <t>AUDIT WATCH: 79-ac pre-application (July 2025) at NE corner Lake Hazel &amp; Linder — ~510 homes incl. ~130 apartments + 176 TH/cluster; no formal H-file or hearing yet; sits near the southern ring edge (~4.5 mi).</t>
         </is>
       </c>
       <c r="H41" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2024/04/12/200-apartments-meridian-discovery/</t>
+          <t>https://boisedev.com/news/2025/07/07/hundreds-of-homes-apartments-planned-for-lake-hazel-and-linder/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="43" t="inlineStr">
         <is>
-          <t>709 N Cole Rd (city land trust)</t>
-        </is>
-      </c>
-      <c r="C42" s="84" t="n"/>
+          <t>Discovery project (Lake Hazel &amp; Locust Grove)</t>
+        </is>
+      </c>
+      <c r="C42" s="84" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="D42" s="84" t="n"/>
       <c r="E42" s="43" t="n"/>
       <c r="F42" s="43" t="n"/>
       <c r="G42" s="43" t="inlineStr">
         <is>
-          <t>AUDIT WATCH: City of Boise closing (July 2026) on 1.64 ac by Boise Towne Square for future affordable housing (prior owner proposed 71 micro-units in 2021); no developer or program yet — 2029+ speculative. Same parcel as the excluded 'Cole Road' RealPage entry.</t>
+          <t>AUDIT WATCH: April 2024 pre-application for 200+ units (nine 3-story buildings + TH/SFR) on ~20 ac by Discovery Park; no formal application since — dormant but the land is teed up (~3.5 mi).</t>
         </is>
       </c>
       <c r="H42" s="43" t="inlineStr">
         <is>
-          <t>https://boisedev.com/news/2026/06/01/709-cole-boise/</t>
+          <t>https://boisedev.com/news/2024/04/12/200-apartments-meridian-discovery/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="43" t="inlineStr">
         <is>
-          <t>Aren east phase (verify)</t>
+          <t>709 N Cole Rd (city land trust)</t>
         </is>
       </c>
       <c r="C43" s="84" t="n"/>
@@ -8877,19 +8694,19 @@
       <c r="F43" s="43" t="n"/>
       <c r="G43" s="43" t="inlineStr">
         <is>
-          <t>AUDIT WATCH: The Aren (396u, delivered 2024) was planned as two phases at Eagle View Landing; verify whether the east-phase (~200u) buildings are fully delivered within the tracked 396 or represent additional untracked pipeline.</t>
+          <t>AUDIT WATCH: City of Boise closing (July 2026) on 1.64 ac by Boise Towne Square for future affordable housing (prior owner proposed 71 micro-units in 2021); no developer or program yet — 2029+ speculative. Same parcel as the excluded 'Cole Road' RealPage entry.</t>
         </is>
       </c>
       <c r="H43" s="43" t="inlineStr">
         <is>
-          <t>https://arenmeridian.com/</t>
+          <t>https://boisedev.com/news/2026/06/01/709-cole-boise/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="43" t="inlineStr">
         <is>
-          <t>Murio Farms MF phases (SW Boise)</t>
+          <t>Aren east phase (verify)</t>
         </is>
       </c>
       <c r="C44" s="84" t="n"/>
@@ -8898,10 +8715,31 @@
       <c r="F44" s="43" t="n"/>
       <c r="G44" s="43" t="inlineStr">
         <is>
+          <t>AUDIT WATCH: The Aren (396u, delivered 2024) was planned as two phases at Eagle View Landing; verify whether the east-phase (~200u) buildings are fully delivered within the tracked 396 or represent additional untracked pipeline.</t>
+        </is>
+      </c>
+      <c r="H44" s="43" t="inlineStr">
+        <is>
+          <t>https://arenmeridian.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="43" t="inlineStr">
+        <is>
+          <t>Murio Farms MF phases (SW Boise)</t>
+        </is>
+      </c>
+      <c r="C45" s="84" t="n"/>
+      <c r="D45" s="84" t="n"/>
+      <c r="E45" s="43" t="n"/>
+      <c r="F45" s="43" t="n"/>
+      <c r="G45" s="43" t="inlineStr">
+        <is>
           <t>AUDIT WATCH: 380-ac, 3,500-home master plan approved 2024 between Maple Grove &amp; Cole at the New York Canal; apartments in later phases (15-20 yr buildout) — long-dated only.</t>
         </is>
       </c>
-      <c r="H44" s="43" t="inlineStr">
+      <c r="H45" s="43" t="inlineStr">
         <is>
           <t>https://www.ktvb.com/article/news/local/idaho-press/city-council-approves-murio-farms-3500-homes-southwest-boise/277-eb746dad-15bb-4c8e-868d-ca9d6c1e355e</t>
         </is>
@@ -8909,8 +8747,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="B32:H32"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
